--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -1270,7 +1270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA22"/>
+  <dimension ref="A1:BA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,8 +4761,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="H21" s="2" t="n">
+        <v>-1.762</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -4816,8 +4822,12 @@
       <c r="Z21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA21" s="2" t="n"/>
-      <c r="AB21" s="2" t="n"/>
+      <c r="AA21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC21" s="2" t="n"/>
       <c r="AD21" s="2" t="n"/>
       <c r="AE21" s="2" t="n"/>
@@ -4842,7 +4852,9 @@
       <c r="AX21" s="2" t="n"/>
       <c r="AY21" s="2" t="n"/>
       <c r="AZ21" s="2" t="n"/>
-      <c r="BA21" s="2" t="n"/>
+      <c r="BA21" s="2" t="n">
+        <v>0.00346</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4874,8 +4886,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="H22" s="2" t="n">
+        <v>-1.138</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -4929,33 +4947,200 @@
       <c r="Z22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA22" s="2" t="n"/>
-      <c r="AB22" s="2" t="n"/>
-      <c r="AC22" s="2" t="n"/>
-      <c r="AD22" s="2" t="n"/>
-      <c r="AE22" s="2" t="n"/>
-      <c r="AF22" s="2" t="n"/>
-      <c r="AG22" s="2" t="n"/>
-      <c r="AH22" s="2" t="n"/>
-      <c r="AI22" s="2" t="n"/>
-      <c r="AJ22" s="2" t="n"/>
-      <c r="AK22" s="2" t="n"/>
-      <c r="AL22" s="2" t="n"/>
-      <c r="AM22" s="2" t="n"/>
-      <c r="AN22" s="2" t="n"/>
-      <c r="AO22" s="2" t="n"/>
-      <c r="AP22" s="2" t="n"/>
-      <c r="AQ22" s="2" t="n"/>
-      <c r="AR22" s="2" t="n"/>
-      <c r="AS22" s="2" t="n"/>
-      <c r="AT22" s="2" t="n"/>
-      <c r="AU22" s="2" t="n"/>
-      <c r="AV22" s="2" t="n"/>
-      <c r="AW22" s="2" t="n"/>
-      <c r="AX22" s="2" t="n"/>
-      <c r="AY22" s="2" t="n"/>
-      <c r="AZ22" s="2" t="n"/>
-      <c r="BA22" s="2" t="n"/>
+      <c r="AA22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI22" s="2" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="AJ22" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="AN22" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AO22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" s="2" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="AR22" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AS22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" s="2" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="AV22" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AW22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="2" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="AZ22" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="BA22" s="2" t="n">
+        <v>0.00122</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GFR</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:36:00-04:00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0.0654574056569432</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0.0078863900148797</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1.498700262832116</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0.009098990004164901</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0.0037009791291449</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>-0.006617658092901</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>1.910282988353823</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0.0003085095451269</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2" t="n"/>
+      <c r="AB23" s="2" t="n"/>
+      <c r="AC23" s="2" t="n"/>
+      <c r="AD23" s="2" t="n"/>
+      <c r="AE23" s="2" t="n"/>
+      <c r="AF23" s="2" t="n"/>
+      <c r="AG23" s="2" t="n"/>
+      <c r="AH23" s="2" t="n"/>
+      <c r="AI23" s="2" t="n"/>
+      <c r="AJ23" s="2" t="n"/>
+      <c r="AK23" s="2" t="n"/>
+      <c r="AL23" s="2" t="n"/>
+      <c r="AM23" s="2" t="n"/>
+      <c r="AN23" s="2" t="n"/>
+      <c r="AO23" s="2" t="n"/>
+      <c r="AP23" s="2" t="n"/>
+      <c r="AQ23" s="2" t="n"/>
+      <c r="AR23" s="2" t="n"/>
+      <c r="AS23" s="2" t="n"/>
+      <c r="AT23" s="2" t="n"/>
+      <c r="AU23" s="2" t="n"/>
+      <c r="AV23" s="2" t="n"/>
+      <c r="AW23" s="2" t="n"/>
+      <c r="AX23" s="2" t="n"/>
+      <c r="AY23" s="2" t="n"/>
+      <c r="AZ23" s="2" t="n"/>
+      <c r="BA23" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,6 +1256,311 @@
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Bull flag: 3.7% pole, 0.9% flag on light vol, broke 8.07 | news: [Google News] Is Alignment Healthcare (ALHC) Cheap Following</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>GFR</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOD squeeze: +6.5%, within 1% of HOD 6.80, hold to next open | news: [Newswire] SCIENTURE Reports Approximately $1.22 Million in </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>GFR</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOD squeeze: +6.5%, within 1% of HOD 6.80, hold to next open | news: [Newswire] SCIENTURE Reports Approximately $1.22 Million in </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 10.29, closed back over 9 EMA | news: [Benzinga] FDA Approves ImmunityBio's Anktiva To Treat Adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 3.0% pole, 1.2% flag on light vol, broke 10.36 | news: [Benzinga] FDA Approves ImmunityBio's Anktiva To Treat Adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +31.7%, dipped to VWAP 1.26, reclaimed with green bar | news: [Benzinga] MaxCyte Reports Preliminary Q3 Core Revenue Of ~$</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA23"/>
+  <dimension ref="A1:BA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5059,8 +5364,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="H23" s="2" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -5114,33 +5425,1846 @@
       <c r="Z23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" s="2" t="n"/>
-      <c r="AB23" s="2" t="n"/>
-      <c r="AC23" s="2" t="n"/>
-      <c r="AD23" s="2" t="n"/>
-      <c r="AE23" s="2" t="n"/>
-      <c r="AF23" s="2" t="n"/>
-      <c r="AG23" s="2" t="n"/>
-      <c r="AH23" s="2" t="n"/>
-      <c r="AI23" s="2" t="n"/>
-      <c r="AJ23" s="2" t="n"/>
-      <c r="AK23" s="2" t="n"/>
-      <c r="AL23" s="2" t="n"/>
-      <c r="AM23" s="2" t="n"/>
-      <c r="AN23" s="2" t="n"/>
-      <c r="AO23" s="2" t="n"/>
-      <c r="AP23" s="2" t="n"/>
-      <c r="AQ23" s="2" t="n"/>
-      <c r="AR23" s="2" t="n"/>
-      <c r="AS23" s="2" t="n"/>
-      <c r="AT23" s="2" t="n"/>
-      <c r="AU23" s="2" t="n"/>
-      <c r="AV23" s="2" t="n"/>
-      <c r="AW23" s="2" t="n"/>
-      <c r="AX23" s="2" t="n"/>
-      <c r="AY23" s="2" t="n"/>
-      <c r="AZ23" s="2" t="n"/>
-      <c r="BA23" s="2" t="n"/>
+      <c r="AA23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI23" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="AJ23" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL23" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AO23" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP23" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ23" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="AR23" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS23" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="AV23" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW23" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AX23" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY23" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="AZ23" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA23" s="2" t="n">
+        <v>0.00148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:32:00-04:00</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0.3174273843527664</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0.2707469302989209</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>3.998392262277589</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0.0049784209318419</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0.0236220325803686</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>-0.0451128271073669</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0.2390168854520066</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>-0.0122235056699204</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI24" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AJ24" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AN24" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO24" s="2" t="n"/>
+      <c r="AP24" s="2" t="n"/>
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="2" t="n"/>
+      <c r="AS24" s="2" t="n"/>
+      <c r="AT24" s="2" t="n"/>
+      <c r="AU24" s="2" t="n"/>
+      <c r="AV24" s="2" t="n"/>
+      <c r="AW24" s="2" t="n"/>
+      <c r="AX24" s="2" t="n"/>
+      <c r="AY24" s="2" t="n"/>
+      <c r="AZ24" s="2" t="n"/>
+      <c r="BA24" s="2" t="n">
+        <v>0.00784</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:38:00-04:00</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>-1.368</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0.0456103004993004</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0.0246252182525501</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1.359333642620841</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0.0006247880014953</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0.0026623351664919</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>-0.0194778598567527</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>3.888344915572128</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>-0.0124484228185076</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" s="2" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI25" s="2" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AJ25" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="2" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AN25" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AO25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" s="2" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AR25" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AS25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" s="2" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AV25" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="2" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AZ25" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA25" s="2" t="n">
+        <v>0.00061</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:38:00-04:00</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>-1.174</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0.0535713886033002</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>-0.0112245518582294</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>1.062099175402153</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0.0488767111425205</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0.0092009502198623</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>-0.0110059085437701</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>2.334568120373986</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>-0.0124484228185076</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="AN26" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AO26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ26" s="2" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="AR26" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AS26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" s="2" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="AV26" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AW26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY26" s="2" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="AZ26" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="BA26" s="2" t="n">
+        <v>0.0009700000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:41:00-04:00</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>-1.444</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0.3268671773539939</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0.2707469302989209</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>3.967763547844457</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0.0121365157692752</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0.0227503264718634</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>-0.0382707518941952</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0.2461566596953398</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>-0.0128533050661038</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI27" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AJ27" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AN27" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AO27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AR27" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AV27" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY27" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="AZ27" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA27" s="2" t="n">
+        <v>0.00784</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:44:00-04:00</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>-1.118</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0.0602040960311092</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-0.0112245518582294</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1.060583449946848</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0.0543389980682877</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0.0153994550563782</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>-0.0047797443489004</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>2.340843838154711</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>-0.0125191065823293</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI28" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AJ28" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AN28" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AR28" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AS28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AV28" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY28" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AZ28" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA28" s="2" t="n">
+        <v>0.00096</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CANG</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:12:00-04:00</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0.0857142720903669</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>0.0171428407941545</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>2.806767859017679</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0.025434212595651</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0.0131578823536055</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>-0.0142672027198642</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>1.335001054183994</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>-0.0132324555994564</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI29" s="2" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="AJ29" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM29" s="2" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="AN29" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AO29" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ29" s="2" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="AR29" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AS29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" s="2" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="AV29" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AW29" s="2" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="AX29" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY29" s="2" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="AZ29" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="BA29" s="2" t="n">
+        <v>0.00528</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:20:00-04:00</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>-1.146</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.0458243973166423</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0.0246252182525501</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>1.319878607715998</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0.0014688340818449</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.0083947614927713</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>-0.019277090344978</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>3.888549652366744</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>-0.0125191065823293</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI30" s="2" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AJ30" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM30" s="2" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AN30" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AO30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="2" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AR30" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AS30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" s="2" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AV30" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AW30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY30" s="2" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AZ30" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BA30" s="2" t="n">
+        <v>0.00041</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>BSP</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:28:00-04:00</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0.4125726011640367</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0.3280506595012964</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>1.988852292756681</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0.0043796192014877</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0.0069184656956497</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>-0.0867486631134482</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>3.979307743674213</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>-0.0127376692527039</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI31" s="2" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="AJ31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM31" s="2" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="AN31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AO31" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="2" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="AR31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AS31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" s="2" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="AV31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW31" s="2" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="AX31" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY31" s="2" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="AZ31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BA31" s="2" t="n">
+        <v>0.00299</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>BSP</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:56:00-04:00</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>-1.136</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0.4094030573196039</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.3280506595012964</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1.946982379034813</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0.0023349322002463</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0.0116192017102654</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>-0.0887978251535894</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>3.977061413045741</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>-0.0128597379946647</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI32" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AN32" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AR32" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AS32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AV32" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AW32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY32" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AZ32" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BA32" s="2" t="n">
+        <v>0.00281</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CANG</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:41:00-04:00</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0.0954571451459611</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0.0171428407941545</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>3.058768267329295</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0.0249810786014439</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0.0219347455296283</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>-0.006709815489339</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>1.343934728793134</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>-0.0117864587795196</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="2" t="n"/>
+      <c r="AB33" s="2" t="n"/>
+      <c r="AC33" s="2" t="n"/>
+      <c r="AD33" s="2" t="n"/>
+      <c r="AE33" s="2" t="n"/>
+      <c r="AF33" s="2" t="n"/>
+      <c r="AG33" s="2" t="n"/>
+      <c r="AH33" s="2" t="n"/>
+      <c r="AI33" s="2" t="n"/>
+      <c r="AJ33" s="2" t="n"/>
+      <c r="AK33" s="2" t="n"/>
+      <c r="AL33" s="2" t="n"/>
+      <c r="AM33" s="2" t="n"/>
+      <c r="AN33" s="2" t="n"/>
+      <c r="AO33" s="2" t="n"/>
+      <c r="AP33" s="2" t="n"/>
+      <c r="AQ33" s="2" t="n"/>
+      <c r="AR33" s="2" t="n"/>
+      <c r="AS33" s="2" t="n"/>
+      <c r="AT33" s="2" t="n"/>
+      <c r="AU33" s="2" t="n"/>
+      <c r="AV33" s="2" t="n"/>
+      <c r="AW33" s="2" t="n"/>
+      <c r="AX33" s="2" t="n"/>
+      <c r="AY33" s="2" t="n"/>
+      <c r="AZ33" s="2" t="n"/>
+      <c r="BA33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:44:00-04:00</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0.0558864576207154</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>0.0246252182525501</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1.275905382580093</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0.0110446447468701</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0.0164246612370103</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>-0.009841382893656299</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>3.898124839322632</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>-0.0116450912518761</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="2" t="n"/>
+      <c r="AB34" s="2" t="n"/>
+      <c r="AC34" s="2" t="n"/>
+      <c r="AD34" s="2" t="n"/>
+      <c r="AE34" s="2" t="n"/>
+      <c r="AF34" s="2" t="n"/>
+      <c r="AG34" s="2" t="n"/>
+      <c r="AH34" s="2" t="n"/>
+      <c r="AI34" s="2" t="n"/>
+      <c r="AJ34" s="2" t="n"/>
+      <c r="AK34" s="2" t="n"/>
+      <c r="AL34" s="2" t="n"/>
+      <c r="AM34" s="2" t="n"/>
+      <c r="AN34" s="2" t="n"/>
+      <c r="AO34" s="2" t="n"/>
+      <c r="AP34" s="2" t="n"/>
+      <c r="AQ34" s="2" t="n"/>
+      <c r="AR34" s="2" t="n"/>
+      <c r="AS34" s="2" t="n"/>
+      <c r="AT34" s="2" t="n"/>
+      <c r="AU34" s="2" t="n"/>
+      <c r="AV34" s="2" t="n"/>
+      <c r="AW34" s="2" t="n"/>
+      <c r="AX34" s="2" t="n"/>
+      <c r="AY34" s="2" t="n"/>
+      <c r="AZ34" s="2" t="n"/>
+      <c r="BA34" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5153,7 +7277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5403,6 +7527,204 @@
         <v>-3.24</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>GFR</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>GFR</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>-6.63</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>closed</t>
         </is>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,6 +1561,311 @@
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>VWAP pullback: +31.7%, dipped to VWAP 1.26, reclaimed with green bar | news: [Benzinga] MaxCyte Reports Preliminary Q3 Core Revenue Of ~$</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 10.68, closed back over 9 EMA | news: [Newswire] Fengate Private Equity Acquires Majority Stake in</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 10.68, closed back over 9 EMA | news: [Newswire] Fengate Private Equity Acquires Majority Stake in</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 4.5% pole, 1.3% flag on light vol, broke 10.53 | news: [Newswire] Fengate Private Equity Acquires Majority Stake in</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 4.5% pole, 1.3% flag on light vol, broke 10.53 | news: [Newswire] Fengate Private Equity Acquires Majority Stake in</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +24.3%, dipped to VWAP 10.06, reclaimed with green bar | news: [Newswire] Fengate Private Equity Acquires Majority Stake in</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA34"/>
+  <dimension ref="A1:BA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7070,8 +7375,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="H33" s="2" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -7125,33 +7436,87 @@
       <c r="Z33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA33" s="2" t="n"/>
-      <c r="AB33" s="2" t="n"/>
-      <c r="AC33" s="2" t="n"/>
-      <c r="AD33" s="2" t="n"/>
-      <c r="AE33" s="2" t="n"/>
-      <c r="AF33" s="2" t="n"/>
-      <c r="AG33" s="2" t="n"/>
-      <c r="AH33" s="2" t="n"/>
-      <c r="AI33" s="2" t="n"/>
-      <c r="AJ33" s="2" t="n"/>
-      <c r="AK33" s="2" t="n"/>
-      <c r="AL33" s="2" t="n"/>
-      <c r="AM33" s="2" t="n"/>
-      <c r="AN33" s="2" t="n"/>
-      <c r="AO33" s="2" t="n"/>
-      <c r="AP33" s="2" t="n"/>
-      <c r="AQ33" s="2" t="n"/>
-      <c r="AR33" s="2" t="n"/>
-      <c r="AS33" s="2" t="n"/>
-      <c r="AT33" s="2" t="n"/>
-      <c r="AU33" s="2" t="n"/>
-      <c r="AV33" s="2" t="n"/>
-      <c r="AW33" s="2" t="n"/>
-      <c r="AX33" s="2" t="n"/>
-      <c r="AY33" s="2" t="n"/>
-      <c r="AZ33" s="2" t="n"/>
-      <c r="BA33" s="2" t="n"/>
+      <c r="AA33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI33" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM33" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AN33" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AR33" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AV33" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY33" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AZ33" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA33" s="2" t="n">
+        <v>0.0105</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -7183,8 +7548,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="H34" s="2" t="n">
+        <v>-3.076</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -7238,33 +7609,1796 @@
       <c r="Z34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA34" s="2" t="n"/>
-      <c r="AB34" s="2" t="n"/>
-      <c r="AC34" s="2" t="n"/>
-      <c r="AD34" s="2" t="n"/>
-      <c r="AE34" s="2" t="n"/>
-      <c r="AF34" s="2" t="n"/>
-      <c r="AG34" s="2" t="n"/>
-      <c r="AH34" s="2" t="n"/>
-      <c r="AI34" s="2" t="n"/>
-      <c r="AJ34" s="2" t="n"/>
-      <c r="AK34" s="2" t="n"/>
-      <c r="AL34" s="2" t="n"/>
-      <c r="AM34" s="2" t="n"/>
-      <c r="AN34" s="2" t="n"/>
-      <c r="AO34" s="2" t="n"/>
-      <c r="AP34" s="2" t="n"/>
-      <c r="AQ34" s="2" t="n"/>
-      <c r="AR34" s="2" t="n"/>
-      <c r="AS34" s="2" t="n"/>
-      <c r="AT34" s="2" t="n"/>
-      <c r="AU34" s="2" t="n"/>
-      <c r="AV34" s="2" t="n"/>
-      <c r="AW34" s="2" t="n"/>
-      <c r="AX34" s="2" t="n"/>
-      <c r="AY34" s="2" t="n"/>
-      <c r="AZ34" s="2" t="n"/>
-      <c r="BA34" s="2" t="n"/>
+      <c r="AA34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="2" t="n">
+        <v>-3.1683</v>
+      </c>
+      <c r="AD34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AG34" s="2" t="n">
+        <v>-3.1683</v>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI34" s="2" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AK34" s="2" t="n">
+        <v>-3.1683</v>
+      </c>
+      <c r="AL34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" s="2" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="AN34" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>-3.1953</v>
+      </c>
+      <c r="AP34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" s="2" t="n">
+        <v>49.3099</v>
+      </c>
+      <c r="AR34" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AS34" s="2" t="n">
+        <v>-3.1953</v>
+      </c>
+      <c r="AT34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" s="2" t="n">
+        <v>49.3099</v>
+      </c>
+      <c r="AV34" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AW34" s="2" t="n">
+        <v>-3.1953</v>
+      </c>
+      <c r="AX34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY34" s="2" t="n">
+        <v>49.3099</v>
+      </c>
+      <c r="AZ34" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="BA34" s="2" t="n">
+        <v>0.00061</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>PATK</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>66.91</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:15:00-04:00</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0.0639709232223955</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>0.0153213929073625</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>1.059106073477457</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0.004841410123316</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0.0066805315658267</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>-0.0083909861955467</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>4.21005137899511</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0.0012344233850942</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AG35" s="2" t="n">
+        <v>1.9247</v>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI35" s="2" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AK35" s="2" t="n">
+        <v>1.4624</v>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM35" s="2" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AN35" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="2" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="AR35" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AS35" s="2" t="n">
+        <v>2.0222</v>
+      </c>
+      <c r="AT35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" s="2" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="AV35" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AW35" s="2" t="n">
+        <v>1.5111</v>
+      </c>
+      <c r="AX35" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY35" s="2" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="AZ35" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BA35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:20:00-04:00</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>-1.074</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0.3390875605938934</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-0.0160295490884178</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>2.323216193178613</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0.08541890490022939</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0.0230202269411247</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>-0.0233725212391703</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>2.385086282892276</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0.0010524916635776</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AF36" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI36" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AN36" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AR36" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AS36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AV36" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY36" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AZ36" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:26:00-04:00</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>-0.459</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0.0797101290696873</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-0.00483091342307</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1.159949356078415</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0.0299164875593827</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0.011185635914651</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>-0.019736875815185</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0.80424118112854</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0.0010135516133313</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="2" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="AD37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>2.2362</v>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="AG37" s="2" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI37" s="2" t="n">
+        <v>2.2362</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="AK37" s="2" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" s="2" t="n">
+        <v>2.2362</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP37" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ37" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="AR37" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS37" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="AV37" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW37" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AX37" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY37" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="AZ37" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:31:00-04:00</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0.2428853364747751</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-0.0160295490884178</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>2.424290474393779</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0.0022685678470941</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0.0118851223471147</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>-0.093535024691125</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>2.310533386661928</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0.0010135516133313</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK38" s="2" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="2" t="n">
+        <v>10.0798</v>
+      </c>
+      <c r="AR38" s="2" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="AS38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" s="2" t="n">
+        <v>10.0798</v>
+      </c>
+      <c r="AV38" s="2" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="AW38" s="2" t="n">
+        <v>1.0851</v>
+      </c>
+      <c r="AX38" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY38" s="2" t="n">
+        <v>10.0798</v>
+      </c>
+      <c r="AZ38" s="2" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="BA38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>DNN</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:38:00-04:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0.0717592431623264</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-0.0138888750915179</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1.351792630266435</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0.0062284305762303</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0.0107991605194496</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>-0.0190677287608689</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0.839409712255458</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0.0019623881940746</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AF39" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AG39" s="2" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="AH39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI39" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AJ39" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AK39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM39" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AN39" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AO39" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AR39" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS39" s="2" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="AT39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AV39" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY39" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="AZ39" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:41:00-04:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.0981211421235559</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0.1115657600256756</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>1.814459349094037</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0.0090128034427037</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>0.008555176221237901</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>-0.013133151186904</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>2.35327825082322</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0.002637613423801</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="2" t="n">
+        <v>1.3778</v>
+      </c>
+      <c r="AD40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE40" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AF40" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG40" s="2" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="AH40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI40" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AJ40" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK40" s="2" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="AL40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM40" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AN40" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO40" s="2" t="n">
+        <v>1.3778</v>
+      </c>
+      <c r="AP40" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ40" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AR40" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AS40" s="2" t="n">
+        <v>1.7555</v>
+      </c>
+      <c r="AT40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AV40" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW40" s="2" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="AX40" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY40" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AZ40" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:56:00-04:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>-1.106</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0.3002466735756122</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-0.0160295490884178</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>2.456114605523753</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0.0441213982963213</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>0.0146989165644861</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>-0.051700077015041</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>2.355651821165821</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0.0023648744568021</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>10.559</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AG41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI41" s="2" t="n">
+        <v>10.559</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AK41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM41" s="2" t="n">
+        <v>10.559</v>
+      </c>
+      <c r="AN41" s="2" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ41" s="2" t="n">
+        <v>10.545</v>
+      </c>
+      <c r="AR41" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AS41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" s="2" t="n">
+        <v>10.545</v>
+      </c>
+      <c r="AV41" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AW41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY41" s="2" t="n">
+        <v>10.545</v>
+      </c>
+      <c r="AZ41" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="BA41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>DNN</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:46:00-04:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0.0717592431623264</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-0.0138888750915179</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1.558963719731424</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0.0040181443508628</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0.0107991605194496</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>-0.0190677287608689</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0.839409712255458</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0.0005912384411099</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="2" t="n">
+        <v>1.3317</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>1.6633</v>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK42" s="2" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AN42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>1.3317</v>
+      </c>
+      <c r="AP42" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AR42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AS42" s="2" t="n">
+        <v>1.6633</v>
+      </c>
+      <c r="AT42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW42" s="2" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="AX42" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY42" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AZ42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA42" s="2" t="n">
+        <v>0.00432</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0.1059499322970869</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>0.1115657600256756</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1.682021798397494</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0.0139724806565413</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>0.0051911529629657</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>-0.0060975216992221</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>2.360382216923548</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0.0032225072538731</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="2" t="n"/>
+      <c r="AB43" s="2" t="n"/>
+      <c r="AC43" s="2" t="n"/>
+      <c r="AD43" s="2" t="n"/>
+      <c r="AE43" s="2" t="n"/>
+      <c r="AF43" s="2" t="n"/>
+      <c r="AG43" s="2" t="n"/>
+      <c r="AH43" s="2" t="n"/>
+      <c r="AI43" s="2" t="n"/>
+      <c r="AJ43" s="2" t="n"/>
+      <c r="AK43" s="2" t="n"/>
+      <c r="AL43" s="2" t="n"/>
+      <c r="AM43" s="2" t="n"/>
+      <c r="AN43" s="2" t="n"/>
+      <c r="AO43" s="2" t="n"/>
+      <c r="AP43" s="2" t="n"/>
+      <c r="AQ43" s="2" t="n"/>
+      <c r="AR43" s="2" t="n"/>
+      <c r="AS43" s="2" t="n"/>
+      <c r="AT43" s="2" t="n"/>
+      <c r="AU43" s="2" t="n"/>
+      <c r="AV43" s="2" t="n"/>
+      <c r="AW43" s="2" t="n"/>
+      <c r="AX43" s="2" t="n"/>
+      <c r="AY43" s="2" t="n"/>
+      <c r="AZ43" s="2" t="n"/>
+      <c r="BA43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>DNN</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0.0851851888644841</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-0.0138888750915179</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>1.479226032483189</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.0162908093659825</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0.0187713733753794</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>-0.0067795740328615</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0.8518589148416754</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0.0032225072538731</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2" t="n"/>
+      <c r="AB44" s="2" t="n"/>
+      <c r="AC44" s="2" t="n"/>
+      <c r="AD44" s="2" t="n"/>
+      <c r="AE44" s="2" t="n"/>
+      <c r="AF44" s="2" t="n"/>
+      <c r="AG44" s="2" t="n"/>
+      <c r="AH44" s="2" t="n"/>
+      <c r="AI44" s="2" t="n"/>
+      <c r="AJ44" s="2" t="n"/>
+      <c r="AK44" s="2" t="n"/>
+      <c r="AL44" s="2" t="n"/>
+      <c r="AM44" s="2" t="n"/>
+      <c r="AN44" s="2" t="n"/>
+      <c r="AO44" s="2" t="n"/>
+      <c r="AP44" s="2" t="n"/>
+      <c r="AQ44" s="2" t="n"/>
+      <c r="AR44" s="2" t="n"/>
+      <c r="AS44" s="2" t="n"/>
+      <c r="AT44" s="2" t="n"/>
+      <c r="AU44" s="2" t="n"/>
+      <c r="AV44" s="2" t="n"/>
+      <c r="AW44" s="2" t="n"/>
+      <c r="AX44" s="2" t="n"/>
+      <c r="AY44" s="2" t="n"/>
+      <c r="AZ44" s="2" t="n"/>
+      <c r="BA44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:42:00-04:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0.091787470216393</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-0.00483091342307</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>1.000391329512645</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0.0352824473891444</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>0.0132743321194029</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>-0.0087719215690703</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0.8153648090643967</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0.0034823983835199</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="2" t="n"/>
+      <c r="AB45" s="2" t="n"/>
+      <c r="AC45" s="2" t="n"/>
+      <c r="AD45" s="2" t="n"/>
+      <c r="AE45" s="2" t="n"/>
+      <c r="AF45" s="2" t="n"/>
+      <c r="AG45" s="2" t="n"/>
+      <c r="AH45" s="2" t="n"/>
+      <c r="AI45" s="2" t="n"/>
+      <c r="AJ45" s="2" t="n"/>
+      <c r="AK45" s="2" t="n"/>
+      <c r="AL45" s="2" t="n"/>
+      <c r="AM45" s="2" t="n"/>
+      <c r="AN45" s="2" t="n"/>
+      <c r="AO45" s="2" t="n"/>
+      <c r="AP45" s="2" t="n"/>
+      <c r="AQ45" s="2" t="n"/>
+      <c r="AR45" s="2" t="n"/>
+      <c r="AS45" s="2" t="n"/>
+      <c r="AT45" s="2" t="n"/>
+      <c r="AU45" s="2" t="n"/>
+      <c r="AV45" s="2" t="n"/>
+      <c r="AW45" s="2" t="n"/>
+      <c r="AX45" s="2" t="n"/>
+      <c r="AY45" s="2" t="n"/>
+      <c r="AZ45" s="2" t="n"/>
+      <c r="BA45" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7277,7 +9411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7727,6 +9861,186 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
         </is>
       </c>
     </row>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -1880,7 +1880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA45"/>
+  <dimension ref="A1:BA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9091,8 +9091,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="H43" s="2" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -9146,33 +9152,87 @@
       <c r="Z43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA43" s="2" t="n"/>
-      <c r="AB43" s="2" t="n"/>
-      <c r="AC43" s="2" t="n"/>
-      <c r="AD43" s="2" t="n"/>
-      <c r="AE43" s="2" t="n"/>
-      <c r="AF43" s="2" t="n"/>
-      <c r="AG43" s="2" t="n"/>
-      <c r="AH43" s="2" t="n"/>
-      <c r="AI43" s="2" t="n"/>
-      <c r="AJ43" s="2" t="n"/>
-      <c r="AK43" s="2" t="n"/>
-      <c r="AL43" s="2" t="n"/>
-      <c r="AM43" s="2" t="n"/>
-      <c r="AN43" s="2" t="n"/>
-      <c r="AO43" s="2" t="n"/>
-      <c r="AP43" s="2" t="n"/>
-      <c r="AQ43" s="2" t="n"/>
-      <c r="AR43" s="2" t="n"/>
-      <c r="AS43" s="2" t="n"/>
-      <c r="AT43" s="2" t="n"/>
-      <c r="AU43" s="2" t="n"/>
-      <c r="AV43" s="2" t="n"/>
-      <c r="AW43" s="2" t="n"/>
-      <c r="AX43" s="2" t="n"/>
-      <c r="AY43" s="2" t="n"/>
-      <c r="AZ43" s="2" t="n"/>
-      <c r="BA43" s="2" t="n"/>
+      <c r="AA43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>10.5988</v>
+      </c>
+      <c r="AF43" s="2" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AG43" s="2" t="n">
+        <v>-0.4898</v>
+      </c>
+      <c r="AH43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI43" s="2" t="n">
+        <v>10.5988</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AK43" s="2" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="AL43" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM43" s="2" t="n">
+        <v>10.5988</v>
+      </c>
+      <c r="AN43" s="2" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="2" t="n">
+        <v>10.595</v>
+      </c>
+      <c r="AR43" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AS43" s="2" t="n">
+        <v>-0.4546</v>
+      </c>
+      <c r="AT43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" s="2" t="n">
+        <v>10.595</v>
+      </c>
+      <c r="AV43" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AW43" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AX43" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY43" s="2" t="n">
+        <v>10.595</v>
+      </c>
+      <c r="AZ43" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BA43" s="2" t="n">
+        <v>0.00094</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -9204,8 +9264,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+      <c r="H44" s="2" t="n">
+        <v>-0.538</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -9259,33 +9325,87 @@
       <c r="Z44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA44" s="2" t="n"/>
-      <c r="AB44" s="2" t="n"/>
-      <c r="AC44" s="2" t="n"/>
-      <c r="AD44" s="2" t="n"/>
-      <c r="AE44" s="2" t="n"/>
-      <c r="AF44" s="2" t="n"/>
-      <c r="AG44" s="2" t="n"/>
-      <c r="AH44" s="2" t="n"/>
-      <c r="AI44" s="2" t="n"/>
-      <c r="AJ44" s="2" t="n"/>
-      <c r="AK44" s="2" t="n"/>
-      <c r="AL44" s="2" t="n"/>
-      <c r="AM44" s="2" t="n"/>
-      <c r="AN44" s="2" t="n"/>
-      <c r="AO44" s="2" t="n"/>
-      <c r="AP44" s="2" t="n"/>
-      <c r="AQ44" s="2" t="n"/>
-      <c r="AR44" s="2" t="n"/>
-      <c r="AS44" s="2" t="n"/>
-      <c r="AT44" s="2" t="n"/>
-      <c r="AU44" s="2" t="n"/>
-      <c r="AV44" s="2" t="n"/>
-      <c r="AW44" s="2" t="n"/>
-      <c r="AX44" s="2" t="n"/>
-      <c r="AY44" s="2" t="n"/>
-      <c r="AZ44" s="2" t="n"/>
-      <c r="BA44" s="2" t="n"/>
+      <c r="AA44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="2" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AD44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE44" s="2" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AJ44" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AK44" s="2" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM44" s="2" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="AN44" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AO44" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ44" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AR44" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS44" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AT44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV44" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW44" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY44" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AZ44" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA44" s="2" t="n">
+        <v>0.00426</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -9317,8 +9437,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
+      <c r="H45" s="2" t="n">
+        <v>-1.667</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -9372,33 +9498,260 @@
       <c r="Z45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA45" s="2" t="n"/>
-      <c r="AB45" s="2" t="n"/>
-      <c r="AC45" s="2" t="n"/>
-      <c r="AD45" s="2" t="n"/>
-      <c r="AE45" s="2" t="n"/>
-      <c r="AF45" s="2" t="n"/>
-      <c r="AG45" s="2" t="n"/>
-      <c r="AH45" s="2" t="n"/>
-      <c r="AI45" s="2" t="n"/>
-      <c r="AJ45" s="2" t="n"/>
-      <c r="AK45" s="2" t="n"/>
-      <c r="AL45" s="2" t="n"/>
-      <c r="AM45" s="2" t="n"/>
-      <c r="AN45" s="2" t="n"/>
-      <c r="AO45" s="2" t="n"/>
-      <c r="AP45" s="2" t="n"/>
-      <c r="AQ45" s="2" t="n"/>
-      <c r="AR45" s="2" t="n"/>
-      <c r="AS45" s="2" t="n"/>
-      <c r="AT45" s="2" t="n"/>
-      <c r="AU45" s="2" t="n"/>
-      <c r="AV45" s="2" t="n"/>
-      <c r="AW45" s="2" t="n"/>
-      <c r="AX45" s="2" t="n"/>
-      <c r="AY45" s="2" t="n"/>
-      <c r="AZ45" s="2" t="n"/>
-      <c r="BA45" s="2" t="n"/>
+      <c r="AA45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AD45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE45" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AF45" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AG45" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AH45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI45" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AJ45" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AK45" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AL45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AN45" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AO45" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AP45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AR45" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS45" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AT45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AV45" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW45" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AX45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY45" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AZ45" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA45" s="2" t="n">
+        <v>0.00443</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 14:54:00-04:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>-1.235</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0.0302313067527439</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>-0.029359424415115</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>1.999813653745339</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0.0047240496639835</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0.0120727176893999</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>-0.0366223618052974</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>1.756114990234857</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>-0.0133585533009195</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE46" s="2" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="AF46" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AG46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI46" s="2" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="AJ46" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AK46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" s="2" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="AN46" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AO46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ46" s="2" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="AR46" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AS46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" s="2" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="AV46" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AW46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY46" s="2" t="n">
+        <v>5.785</v>
+      </c>
+      <c r="AZ46" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="BA46" s="2" t="n">
+        <v>0.00173</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,6 +1866,189 @@
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>VWAP pullback: +24.3%, dipped to VWAP 10.06, reclaimed with green bar | news: [Newswire] Fengate Private Equity Acquires Majority Stake in</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PBLS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +11.5%, dipped to VWAP 25.32, reclaimed with green bar | news: [Benzinga] Parabilis Medicines To Present Updated Clinical D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>EOD squeeze: +19.1%, within 1% of HOD 14.58, hold to next open | news: [Benzinga] Stock Market Today: Nasdaq 100 Rises as AI Chip R</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>EOD squeeze: +19.1%, within 1% of HOD 14.58, hold to next open | news: [Benzinga] Stock Market Today: Nasdaq 100 Rises as AI Chip R</t>
         </is>
       </c>
     </row>
@@ -1880,7 +2063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA46"/>
+  <dimension ref="A1:BA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9753,6 +9936,242 @@
         <v>0.00173</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>PBLS</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>-1.571</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0.114945044884315</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>0.0101098699884101</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0.9477842202978118</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0.0018451131897441</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>0.0013798451186275</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>-0.033346036876231</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>3.233370261995123</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0.0057743696005978</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="2" t="n"/>
+      <c r="AD47" s="2" t="n"/>
+      <c r="AE47" s="2" t="n"/>
+      <c r="AF47" s="2" t="n"/>
+      <c r="AG47" s="2" t="n"/>
+      <c r="AH47" s="2" t="n"/>
+      <c r="AI47" s="2" t="n"/>
+      <c r="AJ47" s="2" t="n"/>
+      <c r="AK47" s="2" t="n"/>
+      <c r="AL47" s="2" t="n"/>
+      <c r="AM47" s="2" t="n"/>
+      <c r="AN47" s="2" t="n"/>
+      <c r="AO47" s="2" t="n"/>
+      <c r="AP47" s="2" t="n"/>
+      <c r="AQ47" s="2" t="n"/>
+      <c r="AR47" s="2" t="n"/>
+      <c r="AS47" s="2" t="n"/>
+      <c r="AT47" s="2" t="n"/>
+      <c r="AU47" s="2" t="n"/>
+      <c r="AV47" s="2" t="n"/>
+      <c r="AW47" s="2" t="n"/>
+      <c r="AX47" s="2" t="n"/>
+      <c r="AY47" s="2" t="n"/>
+      <c r="AZ47" s="2" t="n"/>
+      <c r="BA47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:40:00-04:00</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0.1910066465277717</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0.1716171570417557</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>1.662554928578008</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0.0373658757717905</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0.0169726645302865</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>-0.0099450963544653</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>2.669655842184292</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0.0064723255046266</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="2" t="n"/>
+      <c r="AB48" s="2" t="n"/>
+      <c r="AC48" s="2" t="n"/>
+      <c r="AD48" s="2" t="n"/>
+      <c r="AE48" s="2" t="n"/>
+      <c r="AF48" s="2" t="n"/>
+      <c r="AG48" s="2" t="n"/>
+      <c r="AH48" s="2" t="n"/>
+      <c r="AI48" s="2" t="n"/>
+      <c r="AJ48" s="2" t="n"/>
+      <c r="AK48" s="2" t="n"/>
+      <c r="AL48" s="2" t="n"/>
+      <c r="AM48" s="2" t="n"/>
+      <c r="AN48" s="2" t="n"/>
+      <c r="AO48" s="2" t="n"/>
+      <c r="AP48" s="2" t="n"/>
+      <c r="AQ48" s="2" t="n"/>
+      <c r="AR48" s="2" t="n"/>
+      <c r="AS48" s="2" t="n"/>
+      <c r="AT48" s="2" t="n"/>
+      <c r="AU48" s="2" t="n"/>
+      <c r="AV48" s="2" t="n"/>
+      <c r="AW48" s="2" t="n"/>
+      <c r="AX48" s="2" t="n"/>
+      <c r="AY48" s="2" t="n"/>
+      <c r="AZ48" s="2" t="n"/>
+      <c r="BA48" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9764,7 +10183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10394,6 +10813,122 @@
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PBLS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CLF</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
         </is>
       </c>
     </row>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,6 +2049,189 @@
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>EOD squeeze: +19.1%, within 1% of HOD 14.58, hold to next open | news: [Benzinga] Stock Market Today: Nasdaq 100 Rises as AI Chip R</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CANG</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VWAP pullback: +8.1%, dipped to VWAP 2.32, reclaimed with green bar | news: [Newswire] TheEnergyMag | Energy, Compute, Markets, Stocks, </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 14.04, closed back over 9 EMA | news: [Newswire] Hesai Group to Report Third Quarter 2026 Financia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 14.04, closed back over 9 EMA | news: [Newswire] Hesai Group to Report Third Quarter 2026 Financia</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA48"/>
+  <dimension ref="A1:BA58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10089,8 +10272,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
+      <c r="H48" s="2" t="n">
+        <v>-1.075</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -10144,33 +10333,1583 @@
       <c r="Z48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA48" s="2" t="n"/>
-      <c r="AB48" s="2" t="n"/>
-      <c r="AC48" s="2" t="n"/>
-      <c r="AD48" s="2" t="n"/>
-      <c r="AE48" s="2" t="n"/>
-      <c r="AF48" s="2" t="n"/>
-      <c r="AG48" s="2" t="n"/>
-      <c r="AH48" s="2" t="n"/>
-      <c r="AI48" s="2" t="n"/>
-      <c r="AJ48" s="2" t="n"/>
-      <c r="AK48" s="2" t="n"/>
-      <c r="AL48" s="2" t="n"/>
-      <c r="AM48" s="2" t="n"/>
-      <c r="AN48" s="2" t="n"/>
-      <c r="AO48" s="2" t="n"/>
-      <c r="AP48" s="2" t="n"/>
-      <c r="AQ48" s="2" t="n"/>
-      <c r="AR48" s="2" t="n"/>
-      <c r="AS48" s="2" t="n"/>
-      <c r="AT48" s="2" t="n"/>
-      <c r="AU48" s="2" t="n"/>
-      <c r="AV48" s="2" t="n"/>
-      <c r="AW48" s="2" t="n"/>
-      <c r="AX48" s="2" t="n"/>
-      <c r="AY48" s="2" t="n"/>
-      <c r="AZ48" s="2" t="n"/>
-      <c r="BA48" s="2" t="n"/>
+      <c r="AA48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE48" s="2" t="n">
+        <v>14.4377</v>
+      </c>
+      <c r="AF48" s="2" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AG48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI48" s="2" t="n">
+        <v>14.4377</v>
+      </c>
+      <c r="AJ48" s="2" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AK48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" s="2" t="n">
+        <v>14.4377</v>
+      </c>
+      <c r="AN48" s="2" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AO48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" s="2" t="n">
+        <v>14.435</v>
+      </c>
+      <c r="AR48" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AS48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" s="2" t="n">
+        <v>14.435</v>
+      </c>
+      <c r="AV48" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AW48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY48" s="2" t="n">
+        <v>14.435</v>
+      </c>
+      <c r="AZ48" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="BA48" s="2" t="n">
+        <v>0.00069</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:27:00-04:00</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>-1.143</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0.0905572809121495</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>0.0804953526092662</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>1.283513426620093</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0.0121395430531656</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>0.0092264124329347</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>-0.0126138962439802</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>2.645465336740105</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0.0037966212475737</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE49" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AF49" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI49" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AJ49" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AN49" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AO49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ49" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AR49" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AS49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU49" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AV49" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY49" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AZ49" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA49" s="2" t="n">
+        <v>0.00071</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>-0.587</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0.5148135712803592</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>0.5156457187643733</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>3.84389096961956</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0.003203872757401</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0.0053840470797594</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>-0.00186442386901</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>3.817822233501799</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0.0042924005144764</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="2" t="n">
+        <v>-0.1837</v>
+      </c>
+      <c r="AD50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>45.505</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AG50" s="2" t="n">
+        <v>-0.1837</v>
+      </c>
+      <c r="AH50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI50" s="2" t="n">
+        <v>45.505</v>
+      </c>
+      <c r="AJ50" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AK50" s="2" t="n">
+        <v>-0.1837</v>
+      </c>
+      <c r="AL50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM50" s="2" t="n">
+        <v>45.505</v>
+      </c>
+      <c r="AN50" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AO50" s="2" t="n">
+        <v>-0.1837</v>
+      </c>
+      <c r="AP50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ50" s="2" t="n">
+        <v>45.505</v>
+      </c>
+      <c r="AR50" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AS50" s="2" t="n">
+        <v>-0.1837</v>
+      </c>
+      <c r="AT50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" s="2" t="n">
+        <v>45.505</v>
+      </c>
+      <c r="AV50" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AW50" s="2" t="n">
+        <v>-0.1837</v>
+      </c>
+      <c r="AX50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY50" s="2" t="n">
+        <v>45.505</v>
+      </c>
+      <c r="AZ50" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="BA50" s="2" t="n">
+        <v>0.00022</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:36:00-04:00</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0.5144806106969493</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>0.5156457187643733</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>3.823536846097816</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0.002971792948248</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>0.0005494874705282</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>-0.0020838170735941</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>3.817602406331014</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0.0039771435087476</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="2" t="n"/>
+      <c r="AD51" s="2" t="n"/>
+      <c r="AE51" s="2" t="n"/>
+      <c r="AF51" s="2" t="n"/>
+      <c r="AG51" s="2" t="n"/>
+      <c r="AH51" s="2" t="n"/>
+      <c r="AI51" s="2" t="n"/>
+      <c r="AJ51" s="2" t="n"/>
+      <c r="AK51" s="2" t="n"/>
+      <c r="AL51" s="2" t="n"/>
+      <c r="AM51" s="2" t="n"/>
+      <c r="AN51" s="2" t="n"/>
+      <c r="AO51" s="2" t="n"/>
+      <c r="AP51" s="2" t="n"/>
+      <c r="AQ51" s="2" t="n"/>
+      <c r="AR51" s="2" t="n"/>
+      <c r="AS51" s="2" t="n"/>
+      <c r="AT51" s="2" t="n"/>
+      <c r="AU51" s="2" t="n"/>
+      <c r="AV51" s="2" t="n"/>
+      <c r="AW51" s="2" t="n"/>
+      <c r="AX51" s="2" t="n"/>
+      <c r="AY51" s="2" t="n"/>
+      <c r="AZ51" s="2" t="n"/>
+      <c r="BA51" s="2" t="n">
+        <v>0.00022</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>RCUS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03:00-04:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0.09372180759452139</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-0.0397470273272927</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>2.452828025918519</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0.0176266067619339</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>0.0055750630492341</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>-0.0196356516344432</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>3.186972282156572</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0.0036791663136381</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI52" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AJ52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK52" s="2" t="n">
+        <v>1.8636</v>
+      </c>
+      <c r="AL52" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM52" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AN52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AO52" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AR52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AS52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AV52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW52" s="2" t="n">
+        <v>1.8636</v>
+      </c>
+      <c r="AX52" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY52" s="2" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AZ52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA52" s="2" t="n">
+        <v>0.00165</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>CANG</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:08:00-04:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0.0813953230482888</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>-0.0418605342305855</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1.293064629741095</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0.0038466742674956</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>0.0150537836412453</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>-0.0699999809265137</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0.8437200595484445</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0.0040836094386944</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE53" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI53" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AN53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AO53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ53" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AR53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AS53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY53" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AZ53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA53" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>XPEV</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:47:00-04:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>-0.139</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0.0743757238631368</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>0.0369164116373117</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1.599715087213526</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0.0043044078162073</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0.0075796315607874</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>-0.009509440994097101</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>2.292029625316647</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0.0031051103009329</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="2" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AD54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE54" s="2" t="n">
+        <v>9.8901</v>
+      </c>
+      <c r="AF54" s="2" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AG54" s="2" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AH54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI54" s="2" t="n">
+        <v>9.8901</v>
+      </c>
+      <c r="AJ54" s="2" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AK54" s="2" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AL54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" s="2" t="n">
+        <v>9.8901</v>
+      </c>
+      <c r="AN54" s="2" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AO54" s="2" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AP54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ54" s="2" t="n">
+        <v>9.8901</v>
+      </c>
+      <c r="AR54" s="2" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AS54" s="2" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AT54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" s="2" t="n">
+        <v>9.8901</v>
+      </c>
+      <c r="AV54" s="2" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AW54" s="2" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AX54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY54" s="2" t="n">
+        <v>9.8901</v>
+      </c>
+      <c r="AZ54" s="2" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="BA54" s="2" t="n">
+        <v>0.00101</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>XPEV</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:25:00-04:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0.0711183203320566</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>0.0369164116373117</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1.540082950768645</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0.0011559914637337</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0.0025341887175057</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>-0.0125125127991878</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>2.288993116273176</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0.0022831646547765</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="2" t="n">
+        <v>9.866300000000001</v>
+      </c>
+      <c r="AF55" s="2" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="AG55" s="2" t="n">
+        <v>1.9506</v>
+      </c>
+      <c r="AH55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI55" s="2" t="n">
+        <v>9.866300000000001</v>
+      </c>
+      <c r="AJ55" s="2" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="AK55" s="2" t="n">
+        <v>1.0457</v>
+      </c>
+      <c r="AL55" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM55" s="2" t="n">
+        <v>9.866300000000001</v>
+      </c>
+      <c r="AN55" s="2" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="AO55" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="2" t="n">
+        <v>9.865</v>
+      </c>
+      <c r="AR55" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS55" s="2" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="AT55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU55" s="2" t="n">
+        <v>9.865</v>
+      </c>
+      <c r="AV55" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW55" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX55" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY55" s="2" t="n">
+        <v>9.865</v>
+      </c>
+      <c r="AZ55" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA55" s="2" t="n">
+        <v>0.00101</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>TLK</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0.1138660688969017</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>0.077512003291956</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>2.401478861785644</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0.0108972857059026</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>0.0042869961623292</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>-0.0017238113341003</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>2.454438869029388</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0.0021527299552603</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="2" t="n"/>
+      <c r="AB56" s="2" t="n"/>
+      <c r="AC56" s="2" t="n"/>
+      <c r="AD56" s="2" t="n"/>
+      <c r="AE56" s="2" t="n"/>
+      <c r="AF56" s="2" t="n"/>
+      <c r="AG56" s="2" t="n"/>
+      <c r="AH56" s="2" t="n"/>
+      <c r="AI56" s="2" t="n"/>
+      <c r="AJ56" s="2" t="n"/>
+      <c r="AK56" s="2" t="n"/>
+      <c r="AL56" s="2" t="n"/>
+      <c r="AM56" s="2" t="n"/>
+      <c r="AN56" s="2" t="n"/>
+      <c r="AO56" s="2" t="n"/>
+      <c r="AP56" s="2" t="n"/>
+      <c r="AQ56" s="2" t="n"/>
+      <c r="AR56" s="2" t="n"/>
+      <c r="AS56" s="2" t="n"/>
+      <c r="AT56" s="2" t="n"/>
+      <c r="AU56" s="2" t="n"/>
+      <c r="AV56" s="2" t="n"/>
+      <c r="AW56" s="2" t="n"/>
+      <c r="AX56" s="2" t="n"/>
+      <c r="AY56" s="2" t="n"/>
+      <c r="AZ56" s="2" t="n"/>
+      <c r="BA56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0.5128161887416656</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>0.5156457187643733</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>3.527450597250498</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0.00164365963832</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>0.0014302936574036</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>-0.0036176477377616</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>3.816502796855456</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0.0021527299552603</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="2" t="n"/>
+      <c r="AB57" s="2" t="n"/>
+      <c r="AC57" s="2" t="n"/>
+      <c r="AD57" s="2" t="n"/>
+      <c r="AE57" s="2" t="n"/>
+      <c r="AF57" s="2" t="n"/>
+      <c r="AG57" s="2" t="n"/>
+      <c r="AH57" s="2" t="n"/>
+      <c r="AI57" s="2" t="n"/>
+      <c r="AJ57" s="2" t="n"/>
+      <c r="AK57" s="2" t="n"/>
+      <c r="AL57" s="2" t="n"/>
+      <c r="AM57" s="2" t="n"/>
+      <c r="AN57" s="2" t="n"/>
+      <c r="AO57" s="2" t="n"/>
+      <c r="AP57" s="2" t="n"/>
+      <c r="AQ57" s="2" t="n"/>
+      <c r="AR57" s="2" t="n"/>
+      <c r="AS57" s="2" t="n"/>
+      <c r="AT57" s="2" t="n"/>
+      <c r="AU57" s="2" t="n"/>
+      <c r="AV57" s="2" t="n"/>
+      <c r="AW57" s="2" t="n"/>
+      <c r="AX57" s="2" t="n"/>
+      <c r="AY57" s="2" t="n"/>
+      <c r="AZ57" s="2" t="n"/>
+      <c r="BA57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>XPEV</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:34:00-04:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0.075461421492464</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>0.0369164116373117</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>1.537655622122121</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0.0051440260165827</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0.0065623154693103</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>-0.0085085125219636</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>2.293039653191522</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0.0026485092221633</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="2" t="n"/>
+      <c r="AB58" s="2" t="n"/>
+      <c r="AC58" s="2" t="n"/>
+      <c r="AD58" s="2" t="n"/>
+      <c r="AE58" s="2" t="n"/>
+      <c r="AF58" s="2" t="n"/>
+      <c r="AG58" s="2" t="n"/>
+      <c r="AH58" s="2" t="n"/>
+      <c r="AI58" s="2" t="n"/>
+      <c r="AJ58" s="2" t="n"/>
+      <c r="AK58" s="2" t="n"/>
+      <c r="AL58" s="2" t="n"/>
+      <c r="AM58" s="2" t="n"/>
+      <c r="AN58" s="2" t="n"/>
+      <c r="AO58" s="2" t="n"/>
+      <c r="AP58" s="2" t="n"/>
+      <c r="AQ58" s="2" t="n"/>
+      <c r="AR58" s="2" t="n"/>
+      <c r="AS58" s="2" t="n"/>
+      <c r="AT58" s="2" t="n"/>
+      <c r="AU58" s="2" t="n"/>
+      <c r="AV58" s="2" t="n"/>
+      <c r="AW58" s="2" t="n"/>
+      <c r="AX58" s="2" t="n"/>
+      <c r="AY58" s="2" t="n"/>
+      <c r="AZ58" s="2" t="n"/>
+      <c r="BA58" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10183,7 +11922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10927,6 +12666,126 @@
         <v>-3.12</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CANG</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>closed</t>
         </is>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,6 +2232,311 @@
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>9/21 EMA bounce: tagged 21 EMA 14.04, closed back over 9 EMA | news: [Newswire] Hesai Group to Report Third Quarter 2026 Financia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>TLK</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>EOD squeeze: +11.4%, within 1% of HOD 11.66, hold to next open | news: [Newswire] ORCL Stock Price | Oracle Corp. Stock Quote (U.S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +5.5%, dipped to VWAP 12.63, reclaimed with green bar | news: [Benzinga] 10 Information Technology Stocks With Whale Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 2.49, closed back over 9 EMA | news: [Benzinga] Ashford Hospitality Trust Announces $17 Million A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 2.49, closed back over 9 EMA | news: [Benzinga] Ashford Hospitality Trust Announces $17 Million A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Afternoon HOD: +8.5%, new high 20.94 after 1pm on 1.5x vol | news: [Benzinga] Soluna Holdings and Applied Digital Form Strategi</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA58"/>
+  <dimension ref="A1:BA82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11602,8 +11907,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
+      <c r="H56" s="2" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -11657,33 +11968,87 @@
       <c r="Z56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA56" s="2" t="n"/>
-      <c r="AB56" s="2" t="n"/>
-      <c r="AC56" s="2" t="n"/>
-      <c r="AD56" s="2" t="n"/>
-      <c r="AE56" s="2" t="n"/>
-      <c r="AF56" s="2" t="n"/>
-      <c r="AG56" s="2" t="n"/>
-      <c r="AH56" s="2" t="n"/>
-      <c r="AI56" s="2" t="n"/>
-      <c r="AJ56" s="2" t="n"/>
-      <c r="AK56" s="2" t="n"/>
-      <c r="AL56" s="2" t="n"/>
-      <c r="AM56" s="2" t="n"/>
-      <c r="AN56" s="2" t="n"/>
-      <c r="AO56" s="2" t="n"/>
-      <c r="AP56" s="2" t="n"/>
-      <c r="AQ56" s="2" t="n"/>
-      <c r="AR56" s="2" t="n"/>
-      <c r="AS56" s="2" t="n"/>
-      <c r="AT56" s="2" t="n"/>
-      <c r="AU56" s="2" t="n"/>
-      <c r="AV56" s="2" t="n"/>
-      <c r="AW56" s="2" t="n"/>
-      <c r="AX56" s="2" t="n"/>
-      <c r="AY56" s="2" t="n"/>
-      <c r="AZ56" s="2" t="n"/>
-      <c r="BA56" s="2" t="n"/>
+      <c r="AA56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD56" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE56" s="2" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AF56" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG56" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI56" s="2" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AJ56" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK56" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL56" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM56" s="2" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AN56" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO56" s="2" t="n">
+        <v>1.9038</v>
+      </c>
+      <c r="AP56" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ56" s="2" t="n">
+        <v>11.6399</v>
+      </c>
+      <c r="AR56" s="2" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="AS56" s="2" t="n">
+        <v>2.8076</v>
+      </c>
+      <c r="AT56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" s="2" t="n">
+        <v>11.6399</v>
+      </c>
+      <c r="AV56" s="2" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="AW56" s="2" t="n">
+        <v>0.7014</v>
+      </c>
+      <c r="AX56" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY56" s="2" t="n">
+        <v>11.6399</v>
+      </c>
+      <c r="AZ56" s="2" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="BA56" s="2" t="n">
+        <v>0.00086</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -11715,8 +12080,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
+      <c r="H57" s="2" t="n">
+        <v>-0.654</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -11770,8 +12141,12 @@
       <c r="Z57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA57" s="2" t="n"/>
-      <c r="AB57" s="2" t="n"/>
+      <c r="AA57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC57" s="2" t="n"/>
       <c r="AD57" s="2" t="n"/>
       <c r="AE57" s="2" t="n"/>
@@ -11796,7 +12171,9 @@
       <c r="AX57" s="2" t="n"/>
       <c r="AY57" s="2" t="n"/>
       <c r="AZ57" s="2" t="n"/>
-      <c r="BA57" s="2" t="n"/>
+      <c r="BA57" s="2" t="n">
+        <v>0.00022</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11828,8 +12205,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
+      <c r="H58" s="2" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -11883,33 +12266,3987 @@
       <c r="Z58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA58" s="2" t="n"/>
-      <c r="AB58" s="2" t="n"/>
-      <c r="AC58" s="2" t="n"/>
-      <c r="AD58" s="2" t="n"/>
-      <c r="AE58" s="2" t="n"/>
-      <c r="AF58" s="2" t="n"/>
-      <c r="AG58" s="2" t="n"/>
-      <c r="AH58" s="2" t="n"/>
-      <c r="AI58" s="2" t="n"/>
-      <c r="AJ58" s="2" t="n"/>
-      <c r="AK58" s="2" t="n"/>
-      <c r="AL58" s="2" t="n"/>
-      <c r="AM58" s="2" t="n"/>
-      <c r="AN58" s="2" t="n"/>
-      <c r="AO58" s="2" t="n"/>
-      <c r="AP58" s="2" t="n"/>
-      <c r="AQ58" s="2" t="n"/>
-      <c r="AR58" s="2" t="n"/>
-      <c r="AS58" s="2" t="n"/>
-      <c r="AT58" s="2" t="n"/>
-      <c r="AU58" s="2" t="n"/>
-      <c r="AV58" s="2" t="n"/>
-      <c r="AW58" s="2" t="n"/>
-      <c r="AX58" s="2" t="n"/>
-      <c r="AY58" s="2" t="n"/>
-      <c r="AZ58" s="2" t="n"/>
-      <c r="BA58" s="2" t="n"/>
+      <c r="AA58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="2" t="n">
+        <v>-6.3334</v>
+      </c>
+      <c r="AD58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE58" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AF58" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG58" s="2" t="n">
+        <v>-6.3334</v>
+      </c>
+      <c r="AH58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI58" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AJ58" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AK58" s="2" t="n">
+        <v>-6.3334</v>
+      </c>
+      <c r="AL58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AN58" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AO58" s="2" t="n">
+        <v>-6.3334</v>
+      </c>
+      <c r="AP58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ58" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AR58" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS58" s="2" t="n">
+        <v>-6.3334</v>
+      </c>
+      <c r="AT58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU58" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AV58" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AW58" s="2" t="n">
+        <v>-6.3334</v>
+      </c>
+      <c r="AX58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY58" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AZ58" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BA58" s="2" t="n">
+        <v>0.00101</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>WFRD</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:57:00-04:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>-1.406</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0.0587346089891849</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>0.0470129005432313</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>1.240442109503898</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0.0002604287086194</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>0.0032142857142856</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>-0.0172564902071062</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>4.430816798843313</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0.0025746590408104</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="2" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="AD59" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE59" s="2" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AG59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI59" s="2" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="AJ59" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AK59" s="2" t="n">
+        <v>0.8552999999999999</v>
+      </c>
+      <c r="AL59" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM59" s="2" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="AN59" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AO59" s="2" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="AP59" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ59" s="2" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="AR59" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AS59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU59" s="2" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="AV59" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AW59" s="2" t="n">
+        <v>0.8552999999999999</v>
+      </c>
+      <c r="AX59" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY59" s="2" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="AZ59" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BA59" s="2" t="n">
+        <v>0.00524</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:57:00-04:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>-1.261</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0.06257163481853099</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>0.09851095709579601</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>1.776154488737042</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0.0039891301899144</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0.0044468277663906</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>-0.0329684499573245</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>3.613751719085116</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0.0025746590408104</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD60" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE60" s="2" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="AF60" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AG60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI60" s="2" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="AJ60" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK60" s="2" t="n">
+        <v>0.8088</v>
+      </c>
+      <c r="AL60" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM60" s="2" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="AN60" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO60" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP60" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ60" s="2" t="n">
+        <v>37.105</v>
+      </c>
+      <c r="AR60" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AS60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU60" s="2" t="n">
+        <v>37.105</v>
+      </c>
+      <c r="AV60" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AW60" s="2" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="AX60" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY60" s="2" t="n">
+        <v>37.105</v>
+      </c>
+      <c r="AZ60" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="BA60" s="2" t="n">
+        <v>0.00054</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:57:00-04:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0.4022346614269632</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>0.3351956177865058</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>8.195914992210318</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0.0400584169240663</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>0.0239043787614448</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>-0.0271317578731731</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0.9202827493441932</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0.0025746590408104</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE61" s="2" t="n">
+        <v>2.5112</v>
+      </c>
+      <c r="AF61" s="2" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="AG61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI61" s="2" t="n">
+        <v>2.5112</v>
+      </c>
+      <c r="AJ61" s="2" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="AK61" s="2" t="n">
+        <v>0.8178</v>
+      </c>
+      <c r="AL61" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM61" s="2" t="n">
+        <v>2.5112</v>
+      </c>
+      <c r="AN61" s="2" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="AO61" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="2" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AR61" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AS61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" s="2" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AV61" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AW61" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AX61" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY61" s="2" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="AZ61" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BA61" s="2" t="n">
+        <v>0.00398</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:57:00-04:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0.0724621157594378</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>0.0491955090870073</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1.139281437820044</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0.0070404993171284</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0.0080949974476731</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>-0.0060079129288076</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>4.52882896920065</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0.0025746590408104</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD62" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE62" s="2" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="AF62" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AG62" s="2" t="n">
+        <v>0.2237</v>
+      </c>
+      <c r="AH62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI62" s="2" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="AJ62" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AK62" s="2" t="n">
+        <v>1.2138</v>
+      </c>
+      <c r="AL62" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM62" s="2" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="AN62" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AO62" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP62" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ62" s="2" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AR62" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AS62" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AT62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU62" s="2" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AV62" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW62" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AX62" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY62" s="2" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AZ62" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BA62" s="2" t="n">
+        <v>0.00119</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:01:00-04:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0.0582847457056467</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>0.0574520871967993</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>1.07277050811925</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0.0066292207888425</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>0.0070810415324038</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>-0.0147286500776616</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>2.542389088202698</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0.0024995009966179</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE63" s="2" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="AF63" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AG63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI63" s="2" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="AJ63" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AK63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" s="2" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="AN63" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AO63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ63" s="2" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="AR63" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AS63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU63" s="2" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="AV63" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AW63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY63" s="2" t="n">
+        <v>12.705</v>
+      </c>
+      <c r="AZ63" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="BA63" s="2" t="n">
+        <v>0.00079</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:04:00-04:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0.0661512455446038</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>0.09851095709579601</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1.739997591639858</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0.0071875149227798</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0.008058005531157399</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>-0.0297106964134189</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>3.617114875589066</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0.0025095802697039</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE64" s="2" t="n">
+        <v>37.245</v>
+      </c>
+      <c r="AF64" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AG64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI64" s="2" t="n">
+        <v>37.245</v>
+      </c>
+      <c r="AJ64" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AK64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" s="2" t="n">
+        <v>37.245</v>
+      </c>
+      <c r="AN64" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AO64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ64" s="2" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="AR64" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AS64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU64" s="2" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="AV64" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY64" s="2" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="AZ64" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA64" s="2" t="n">
+        <v>0.00107</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GLXY</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:06:00-04:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>-1.187</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0.084390856877571</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>0.0431472268591475</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>1.108535437773315</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0.0265209055041564</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>0.0076067964556573</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>-0.0121386759383659</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>2.838493506055989</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0.0026006111848979</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD65" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE65" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AF65" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI65" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AJ65" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AK65" s="2" t="n">
+        <v>0.6731</v>
+      </c>
+      <c r="AL65" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM65" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AN65" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AO65" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP65" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ65" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AR65" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU65" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AV65" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW65" s="2" t="n">
+        <v>0.6731</v>
+      </c>
+      <c r="AX65" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY65" s="2" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="AZ65" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BA65" s="2" t="n">
+        <v>0.00117</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:07:00-04:00</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>-1.133</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0.072684981489443</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>0.0437143981732868</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.938732228796364</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0.0186441061903501</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0.009404417873718899</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>-0.0031249340910153</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>3.031823123134156</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0.0026916421000919</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE66" s="2" t="n">
+        <v>20.735</v>
+      </c>
+      <c r="AF66" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AG66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI66" s="2" t="n">
+        <v>20.735</v>
+      </c>
+      <c r="AJ66" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AK66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" s="2" t="n">
+        <v>20.735</v>
+      </c>
+      <c r="AN66" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AO66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ66" s="2" t="n">
+        <v>20.735</v>
+      </c>
+      <c r="AR66" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AS66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" s="2" t="n">
+        <v>20.735</v>
+      </c>
+      <c r="AV66" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AW66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY66" s="2" t="n">
+        <v>20.735</v>
+      </c>
+      <c r="AZ66" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="BA66" s="2" t="n">
+        <v>0.00048</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:07:00-04:00</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0.0553705203313672</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>0.0574520871967993</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1.045453496421826</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0.0037727243227259</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>0.0027613562294418</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>-0.0174418166239485</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>2.539631564525362</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0.0026916421000919</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE67" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AF67" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI67" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AJ67" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AN67" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ67" s="2" t="n">
+        <v>12.675</v>
+      </c>
+      <c r="AR67" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU67" s="2" t="n">
+        <v>12.675</v>
+      </c>
+      <c r="AV67" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY67" s="2" t="n">
+        <v>12.675</v>
+      </c>
+      <c r="AZ67" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA67" s="2" t="n">
+        <v>0.00079</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0.08043140790959639</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-0.0024712828533421</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1.228273048924955</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0.0223354420107861</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>0.0056144760185316</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>-0.0074283211416306</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>3.873074258462536</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0.0029777505998953</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD68" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE68" s="2" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="AF68" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AG68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" s="2" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="AJ68" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AK68" s="2" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="AL68" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM68" s="2" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="AN68" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AO68" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP68" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ68" s="2" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="AR68" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AS68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="2" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="AV68" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AW68" s="2" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="AX68" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY68" s="2" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="AZ68" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="BA68" s="2" t="n">
+        <v>0.00312</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>WFRD</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>83.61</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:49:00-04:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0.0618856048492717</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>0.0470129005432313</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>1.108754458497237</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>0.0033566988206361</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>0.0075964391691394</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>-0.0143316583327226</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>4.433788569232471</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>0.0049151932343474</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC69" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" s="2" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="AF69" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" s="2" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="AJ69" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AK69" s="2" t="n">
+        <v>1.2357</v>
+      </c>
+      <c r="AL69" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM69" s="2" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="AN69" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AO69" s="2" t="n"/>
+      <c r="AP69" s="2" t="n"/>
+      <c r="AQ69" s="2" t="n"/>
+      <c r="AR69" s="2" t="n"/>
+      <c r="AS69" s="2" t="n"/>
+      <c r="AT69" s="2" t="n"/>
+      <c r="AU69" s="2" t="n"/>
+      <c r="AV69" s="2" t="n"/>
+      <c r="AW69" s="2" t="n"/>
+      <c r="AX69" s="2" t="n"/>
+      <c r="AY69" s="2" t="n"/>
+      <c r="AZ69" s="2" t="n"/>
+      <c r="BA69" s="2" t="n">
+        <v>0.00474</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:14:00-04:00</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0.3959777053316788</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>0.3351956177865058</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>7.863419779725414</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>0.0139315907860309</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>0.01552746865747</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>-0.1107472988701674</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0.9158106323613781</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>0.0046031325904565</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE70" s="2" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AF70" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI70" s="2" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AJ70" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" s="2" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AN70" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ70" s="2" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AR70" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" s="2" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AV70" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY70" s="2" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="AZ70" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA70" s="2" t="n">
+        <v>0.00401</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>WGO</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0.0854553101301944</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>0.06905482849379641</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>1.455040430641148</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>0.0144071910290453</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>0.0107355714761658</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>-0.0007946149266209</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>3.224857881377966</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>0.0041870252771503</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="2" t="n">
+        <v>1.1328</v>
+      </c>
+      <c r="AD71" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE71" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AF71" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AG71" s="2" t="n">
+        <v>1.2656</v>
+      </c>
+      <c r="AH71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI71" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AJ71" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AK71" s="2" t="n">
+        <v>1.1328</v>
+      </c>
+      <c r="AL71" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM71" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AN71" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AO71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ71" s="2" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AR71" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AS71" s="2" t="n">
+        <v>1.7885</v>
+      </c>
+      <c r="AT71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" s="2" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AV71" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW71" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY71" s="2" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AZ71" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BA71" s="2" t="n">
+        <v>0.00317</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:35:00-04:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0.0623383304946763</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>0.0437143981732868</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0.7666863290969826</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0.0034848122242043</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>0.0017043996918519</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>-0.0169937555102198</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>3.022130739977896</v>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>0.0041349622602651</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="2" t="n"/>
+      <c r="AD72" s="2" t="n"/>
+      <c r="AE72" s="2" t="n"/>
+      <c r="AF72" s="2" t="n"/>
+      <c r="AG72" s="2" t="n"/>
+      <c r="AH72" s="2" t="n"/>
+      <c r="AI72" s="2" t="n"/>
+      <c r="AJ72" s="2" t="n"/>
+      <c r="AK72" s="2" t="n"/>
+      <c r="AL72" s="2" t="n"/>
+      <c r="AM72" s="2" t="n"/>
+      <c r="AN72" s="2" t="n"/>
+      <c r="AO72" s="2" t="n"/>
+      <c r="AP72" s="2" t="n"/>
+      <c r="AQ72" s="2" t="n"/>
+      <c r="AR72" s="2" t="n"/>
+      <c r="AS72" s="2" t="n"/>
+      <c r="AT72" s="2" t="n"/>
+      <c r="AU72" s="2" t="n"/>
+      <c r="AV72" s="2" t="n"/>
+      <c r="AW72" s="2" t="n"/>
+      <c r="AX72" s="2" t="n"/>
+      <c r="AY72" s="2" t="n"/>
+      <c r="AZ72" s="2" t="n"/>
+      <c r="BA72" s="2" t="n">
+        <v>0.00049</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:59:00-04:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0.0845835610623408</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>0.0437143981732868</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>0.7475614000747192</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>0.0230579191886173</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>0.0112091653173149</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>-0.0004767689487467</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>3.042854387900946</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>0.0056953448440748</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="2" t="n">
+        <v>20.965</v>
+      </c>
+      <c r="AF73" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AG73" s="2" t="n">
+        <v>-0.2128</v>
+      </c>
+      <c r="AH73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI73" s="2" t="n">
+        <v>20.965</v>
+      </c>
+      <c r="AJ73" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AK73" s="2" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="AL73" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM73" s="2" t="n">
+        <v>20.965</v>
+      </c>
+      <c r="AN73" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AO73" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="2" t="n">
+        <v>20.965</v>
+      </c>
+      <c r="AR73" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AS73" s="2" t="n">
+        <v>-0.2128</v>
+      </c>
+      <c r="AT73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" s="2" t="n">
+        <v>20.965</v>
+      </c>
+      <c r="AV73" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AW73" s="2" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="AX73" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY73" s="2" t="n">
+        <v>20.965</v>
+      </c>
+      <c r="AZ73" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="BA73" s="2" t="n">
+        <v>0.00048</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>ECHO</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:03:00-04:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0.0779025744239096</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>0.0491955090870073</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0.9461370068748308</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>0.005763189504971</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>0.0045103386403996</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>-0.0091508893342481</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="2" t="n">
+        <v>4.533889013478209</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>0.0057213763525174</v>
+      </c>
+      <c r="U74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE74" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AF74" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AG74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI74" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AJ74" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AK74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AN74" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AO74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ74" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AR74" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AS74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AV74" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY74" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AZ74" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BA74" s="2" t="n">
+        <v>0.00086</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>GLXY</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:14:00-04:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>-1.167</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0.1027918089059383</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>0.0431472268591475</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.9883670990163382</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>0.0324595567687253</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>0.008055188004993399</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>-0.0008623912964816</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="n">
+        <v>2.855320071549938</v>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>0.0062414509708839</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE75" s="2" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AF75" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI75" s="2" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AJ75" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" s="2" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AN75" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ75" s="2" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="AR75" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" s="2" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="AV75" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY75" s="2" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="AZ75" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BA75" s="2" t="n">
+        <v>0.00173</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:55:00-04:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0.0811822988521446</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>0.0574520871967993</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.777384282148076</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>0.0238100863698085</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>0.008086227143121299</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>-0.0003849202870684</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="2" t="n">
+        <v>2.563794818674761</v>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>0.0064755758181571</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE76" s="2" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="AF76" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AG76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI76" s="2" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="AJ76" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AK76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="2" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="AN76" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AO76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ76" s="2" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="AR76" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AS76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU76" s="2" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="AV76" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AW76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY76" s="2" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="AZ76" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="BA76" s="2" t="n">
+        <v>0.00077</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:27:00-04:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0.1006516181953267</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-0.0024712828533421</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0.9943872786280572</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>0.0264639110825528</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>0.0087773354507925</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>-0.0042682740084597</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="n">
+        <v>3.891616229911899</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>0.0069045401569747</v>
+      </c>
+      <c r="U77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="2" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AD77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE77" s="2" t="n">
+        <v>48.955</v>
+      </c>
+      <c r="AF77" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AG77" s="2" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AH77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI77" s="2" t="n">
+        <v>48.955</v>
+      </c>
+      <c r="AJ77" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AK77" s="2" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AL77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM77" s="2" t="n">
+        <v>48.955</v>
+      </c>
+      <c r="AN77" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AO77" s="2" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AP77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ77" s="2" t="n">
+        <v>48.955</v>
+      </c>
+      <c r="AR77" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AS77" s="2" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AT77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" s="2" t="n">
+        <v>48.955</v>
+      </c>
+      <c r="AV77" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AW77" s="2" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="AX77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY77" s="2" t="n">
+        <v>48.955</v>
+      </c>
+      <c r="AZ77" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="BA77" s="2" t="n">
+        <v>0.00184</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>WGO</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:08:00-04:00</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0.0811393679143788</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>0.06905482849379641</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>1.254994889364698</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>0.0050503391567211</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>0.00638719528677</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>-0.0172616923502748</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2" t="n">
+        <v>3.220873797074209</v>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>0.0030297342524254</v>
+      </c>
+      <c r="U78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE78" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AF78" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI78" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AJ78" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK78" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL78" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM78" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AN78" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AO78" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AR78" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AV78" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW78" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX78" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY78" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AZ78" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA78" s="2" t="n">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>GLXY</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:11:00-04:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0.0818527277566059</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>0.0431472268591475</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0.9393046002706378</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>0.0055503568021033</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>0.0035190169938618</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>-0.0226426176367813</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="n">
+        <v>2.836150158982343</v>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>0.0027702921759047</v>
+      </c>
+      <c r="U79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD79" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE79" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AF79" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI79" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AJ79" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AK79" s="2" t="n">
+        <v>0.7917</v>
+      </c>
+      <c r="AL79" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM79" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AN79" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AO79" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP79" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ79" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AR79" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AV79" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AW79" s="2" t="n">
+        <v>0.7917</v>
+      </c>
+      <c r="AX79" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY79" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AZ79" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BA79" s="2" t="n">
+        <v>0.00117</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0.099977554049617</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-0.0024712828533421</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.9707696671333648</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>0.0220802581012165</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>0.0073529226144701</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>-0.0058883434624841</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>3.891003619504574</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>0.0054417757298246</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="2" t="n"/>
+      <c r="AB80" s="2" t="n"/>
+      <c r="AC80" s="2" t="n"/>
+      <c r="AD80" s="2" t="n"/>
+      <c r="AE80" s="2" t="n"/>
+      <c r="AF80" s="2" t="n"/>
+      <c r="AG80" s="2" t="n"/>
+      <c r="AH80" s="2" t="n"/>
+      <c r="AI80" s="2" t="n"/>
+      <c r="AJ80" s="2" t="n"/>
+      <c r="AK80" s="2" t="n"/>
+      <c r="AL80" s="2" t="n"/>
+      <c r="AM80" s="2" t="n"/>
+      <c r="AN80" s="2" t="n"/>
+      <c r="AO80" s="2" t="n"/>
+      <c r="AP80" s="2" t="n"/>
+      <c r="AQ80" s="2" t="n"/>
+      <c r="AR80" s="2" t="n"/>
+      <c r="AS80" s="2" t="n"/>
+      <c r="AT80" s="2" t="n"/>
+      <c r="AU80" s="2" t="n"/>
+      <c r="AV80" s="2" t="n"/>
+      <c r="AW80" s="2" t="n"/>
+      <c r="AX80" s="2" t="n"/>
+      <c r="AY80" s="2" t="n"/>
+      <c r="AZ80" s="2" t="n"/>
+      <c r="BA80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>WGO</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0.0927923872011555</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>0.06905482849379641</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>1.256409448164708</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>0.0154591800975607</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>0.0173775552972918</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>-0.0066692851243791</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>3.23159458522322</v>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>0.0054417757298246</v>
+      </c>
+      <c r="U81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="2" t="n"/>
+      <c r="AB81" s="2" t="n"/>
+      <c r="AC81" s="2" t="n"/>
+      <c r="AD81" s="2" t="n"/>
+      <c r="AE81" s="2" t="n"/>
+      <c r="AF81" s="2" t="n"/>
+      <c r="AG81" s="2" t="n"/>
+      <c r="AH81" s="2" t="n"/>
+      <c r="AI81" s="2" t="n"/>
+      <c r="AJ81" s="2" t="n"/>
+      <c r="AK81" s="2" t="n"/>
+      <c r="AL81" s="2" t="n"/>
+      <c r="AM81" s="2" t="n"/>
+      <c r="AN81" s="2" t="n"/>
+      <c r="AO81" s="2" t="n"/>
+      <c r="AP81" s="2" t="n"/>
+      <c r="AQ81" s="2" t="n"/>
+      <c r="AR81" s="2" t="n"/>
+      <c r="AS81" s="2" t="n"/>
+      <c r="AT81" s="2" t="n"/>
+      <c r="AU81" s="2" t="n"/>
+      <c r="AV81" s="2" t="n"/>
+      <c r="AW81" s="2" t="n"/>
+      <c r="AX81" s="2" t="n"/>
+      <c r="AY81" s="2" t="n"/>
+      <c r="AZ81" s="2" t="n"/>
+      <c r="BA81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0.0761865066124329</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>0.0574520871967993</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.7602620672487318</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>0.0144347739743151</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>0.013539666394768</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>-0.0099578790809662</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>2.559163435151542</v>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>0.0054417757298246</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="2" t="n"/>
+      <c r="AB82" s="2" t="n"/>
+      <c r="AC82" s="2" t="n"/>
+      <c r="AD82" s="2" t="n"/>
+      <c r="AE82" s="2" t="n"/>
+      <c r="AF82" s="2" t="n"/>
+      <c r="AG82" s="2" t="n"/>
+      <c r="AH82" s="2" t="n"/>
+      <c r="AI82" s="2" t="n"/>
+      <c r="AJ82" s="2" t="n"/>
+      <c r="AK82" s="2" t="n"/>
+      <c r="AL82" s="2" t="n"/>
+      <c r="AM82" s="2" t="n"/>
+      <c r="AN82" s="2" t="n"/>
+      <c r="AO82" s="2" t="n"/>
+      <c r="AP82" s="2" t="n"/>
+      <c r="AQ82" s="2" t="n"/>
+      <c r="AR82" s="2" t="n"/>
+      <c r="AS82" s="2" t="n"/>
+      <c r="AT82" s="2" t="n"/>
+      <c r="AU82" s="2" t="n"/>
+      <c r="AV82" s="2" t="n"/>
+      <c r="AW82" s="2" t="n"/>
+      <c r="AX82" s="2" t="n"/>
+      <c r="AY82" s="2" t="n"/>
+      <c r="AZ82" s="2" t="n"/>
+      <c r="BA82" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11922,7 +16259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12786,6 +17123,206 @@
         <v>-3.12</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>TLK</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>20.945</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>closed</t>
         </is>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2537,6 +2537,372 @@
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>Afternoon HOD: +8.5%, new high 20.94 after 1pm on 1.5x vol | news: [Benzinga] Soluna Holdings and Applied Digital Form Strategi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 3.3% pole, 0.6% flag on light vol, broke 13.77 | news: [Benzinga] Ermenegildo Zegna Reports Q3 2026 Financial Resul</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 3.3% pole, 0.6% flag on light vol, broke 13.77 | news: [Benzinga] Ermenegildo Zegna Reports Q3 2026 Financial Resul</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>VLY</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +4.3%, dipped to VWAP 13.57, reclaimed with green bar | news: [Benzinga] Valley Ntl Q3 2026 Earnings Call Transcript +8-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>15-min ORB: closed above 15-min high 13.56, above VWAP | news: [Benzinga] Ermenegildo Zegna Reports Q3 2026 Financial Resul</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>5-min ORB: green first 5 min, closed above range high 13.52 | news: [Benzinga] Ermenegildo Zegna Reports Q3 2026 Financial Resul</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>5-min ORB: green first 5 min, closed above range high 13.52 | news: [Benzinga] Ermenegildo Zegna Reports Q3 2026 Financial Resul</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA82"/>
+  <dimension ref="A1:BA124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15939,8 +16305,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
+      <c r="H80" s="2" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -15994,33 +16366,87 @@
       <c r="Z80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA80" s="2" t="n"/>
-      <c r="AB80" s="2" t="n"/>
-      <c r="AC80" s="2" t="n"/>
-      <c r="AD80" s="2" t="n"/>
-      <c r="AE80" s="2" t="n"/>
-      <c r="AF80" s="2" t="n"/>
-      <c r="AG80" s="2" t="n"/>
-      <c r="AH80" s="2" t="n"/>
-      <c r="AI80" s="2" t="n"/>
-      <c r="AJ80" s="2" t="n"/>
-      <c r="AK80" s="2" t="n"/>
-      <c r="AL80" s="2" t="n"/>
-      <c r="AM80" s="2" t="n"/>
-      <c r="AN80" s="2" t="n"/>
-      <c r="AO80" s="2" t="n"/>
-      <c r="AP80" s="2" t="n"/>
-      <c r="AQ80" s="2" t="n"/>
-      <c r="AR80" s="2" t="n"/>
-      <c r="AS80" s="2" t="n"/>
-      <c r="AT80" s="2" t="n"/>
-      <c r="AU80" s="2" t="n"/>
-      <c r="AV80" s="2" t="n"/>
-      <c r="AW80" s="2" t="n"/>
-      <c r="AX80" s="2" t="n"/>
-      <c r="AY80" s="2" t="n"/>
-      <c r="AZ80" s="2" t="n"/>
-      <c r="BA80" s="2" t="n"/>
+      <c r="AA80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD80" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE80" s="2" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AF80" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG80" s="2" t="n">
+        <v>-0.6061</v>
+      </c>
+      <c r="AH80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI80" s="2" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AJ80" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL80" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM80" s="2" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AN80" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ80" s="2" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AR80" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AS80" s="2" t="n">
+        <v>-0.6061</v>
+      </c>
+      <c r="AT80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" s="2" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AV80" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY80" s="2" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AZ80" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA80" s="2" t="n">
+        <v>0.00306</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -16052,8 +16478,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="n"/>
+      <c r="H81" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -16107,33 +16539,87 @@
       <c r="Z81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA81" s="2" t="n"/>
-      <c r="AB81" s="2" t="n"/>
-      <c r="AC81" s="2" t="n"/>
-      <c r="AD81" s="2" t="n"/>
-      <c r="AE81" s="2" t="n"/>
-      <c r="AF81" s="2" t="n"/>
-      <c r="AG81" s="2" t="n"/>
-      <c r="AH81" s="2" t="n"/>
-      <c r="AI81" s="2" t="n"/>
-      <c r="AJ81" s="2" t="n"/>
-      <c r="AK81" s="2" t="n"/>
-      <c r="AL81" s="2" t="n"/>
-      <c r="AM81" s="2" t="n"/>
-      <c r="AN81" s="2" t="n"/>
-      <c r="AO81" s="2" t="n"/>
-      <c r="AP81" s="2" t="n"/>
-      <c r="AQ81" s="2" t="n"/>
-      <c r="AR81" s="2" t="n"/>
-      <c r="AS81" s="2" t="n"/>
-      <c r="AT81" s="2" t="n"/>
-      <c r="AU81" s="2" t="n"/>
-      <c r="AV81" s="2" t="n"/>
-      <c r="AW81" s="2" t="n"/>
-      <c r="AX81" s="2" t="n"/>
-      <c r="AY81" s="2" t="n"/>
-      <c r="AZ81" s="2" t="n"/>
-      <c r="BA81" s="2" t="n"/>
+      <c r="AA81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="2" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="AD81" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE81" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AF81" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AG81" s="2" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="AH81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI81" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ81" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AK81" s="2" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="AL81" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM81" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AN81" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AO81" s="2" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="AP81" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ81" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AR81" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AS81" s="2" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="AT81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AV81" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW81" s="2" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="AX81" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY81" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AZ81" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BA81" s="2" t="n">
+        <v>0.00158</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -16165,8 +16651,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
+      <c r="H82" s="2" t="n">
+        <v>-1.103</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -16220,33 +16712,6787 @@
       <c r="Z82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA82" s="2" t="n"/>
-      <c r="AB82" s="2" t="n"/>
-      <c r="AC82" s="2" t="n"/>
-      <c r="AD82" s="2" t="n"/>
-      <c r="AE82" s="2" t="n"/>
-      <c r="AF82" s="2" t="n"/>
-      <c r="AG82" s="2" t="n"/>
-      <c r="AH82" s="2" t="n"/>
-      <c r="AI82" s="2" t="n"/>
-      <c r="AJ82" s="2" t="n"/>
-      <c r="AK82" s="2" t="n"/>
-      <c r="AL82" s="2" t="n"/>
-      <c r="AM82" s="2" t="n"/>
-      <c r="AN82" s="2" t="n"/>
-      <c r="AO82" s="2" t="n"/>
-      <c r="AP82" s="2" t="n"/>
-      <c r="AQ82" s="2" t="n"/>
-      <c r="AR82" s="2" t="n"/>
-      <c r="AS82" s="2" t="n"/>
-      <c r="AT82" s="2" t="n"/>
-      <c r="AU82" s="2" t="n"/>
-      <c r="AV82" s="2" t="n"/>
-      <c r="AW82" s="2" t="n"/>
-      <c r="AX82" s="2" t="n"/>
-      <c r="AY82" s="2" t="n"/>
-      <c r="AZ82" s="2" t="n"/>
-      <c r="BA82" s="2" t="n"/>
+      <c r="AA82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE82" s="2" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="AF82" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AG82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI82" s="2" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="AJ82" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AK82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM82" s="2" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="AN82" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AO82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ82" s="2" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="AR82" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AS82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" s="2" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="AV82" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AW82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY82" s="2" t="n">
+        <v>12.925</v>
+      </c>
+      <c r="AZ82" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="BA82" s="2" t="n">
+        <v>0.00077</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:44:00-04:00</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0.04798760695804316</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>0.01934984508697557</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>1.086559116352204</v>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>0.009118137446201935</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>0.03028064719410204</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="2" t="n">
+        <v>2.605648264666775</v>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>-0.008369053426543371</v>
+      </c>
+      <c r="U83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE83" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AF83" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AG83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI83" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AJ83" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AK83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AN83" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AO83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ83" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AR83" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AS83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AV83" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AW83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY83" s="2" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AZ83" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BA83" s="2" t="n">
+        <v>0.00591</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:46:00-04:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0.05417955148077125</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>0.01934984508697557</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>1.72151043550806</v>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>0.01610975200863485</v>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>0.02569749548457617</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="2" t="n">
+        <v>2.61153929231895</v>
+      </c>
+      <c r="T84" s="2" t="n">
+        <v>-0.009041704105229753</v>
+      </c>
+      <c r="U84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="2" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AD84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE84" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AF84" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG84" s="2" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AH84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI84" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AJ84" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK84" s="2" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AL84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM84" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AN84" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AO84" s="2" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AP84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ84" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AR84" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS84" s="2" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AT84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AV84" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AW84" s="2" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AX84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY84" s="2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AZ84" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BA84" s="2" t="n">
+        <v>0.00513</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>RTO</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:54:00-04:00</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0.070817476534355</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>0.06368812675527735</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>1.638118250921359</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>0.006643237192822005</v>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>0.006213967260484445</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="2" t="n">
+        <v>3.114847784921095</v>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>-0.008899357958085163</v>
+      </c>
+      <c r="U85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE85" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="AF85" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG85" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI85" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="AJ85" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK85" s="2" t="n">
+        <v>1.2679</v>
+      </c>
+      <c r="AL85" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM85" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="AN85" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AO85" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="AR85" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS85" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="AV85" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW85" s="2" t="n">
+        <v>1.2679</v>
+      </c>
+      <c r="AX85" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY85" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="AZ85" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA85" s="2" t="n">
+        <v>0.0008899999999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:57:00-04:00</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0.0646693627012469</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>0.03491732589730101</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>1.789398887721221</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>0.01068661759301515</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>0.01979427136541444</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>-0.0003879817276368769</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="2" t="n">
+        <v>3.942164138650959</v>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>-0.007780484082692718</v>
+      </c>
+      <c r="U86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AD86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE86" s="2" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="AF86" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AG86" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AH86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI86" s="2" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="AJ86" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK86" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AL86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM86" s="2" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="AN86" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AO86" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AP86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ86" s="2" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="AR86" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AS86" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AT86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" s="2" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="AV86" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AW86" s="2" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AX86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY86" s="2" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="AZ86" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BA86" s="2" t="n">
+        <v>0.00019</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>TCBI</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:59:00-04:00</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>-1.178</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0.05059368344222226</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>0.01497488028525717</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>1.009031726528807</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>0.006974002473354446</v>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>0.006719621385669517</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>-0.003853927579093308</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="2" t="n">
+        <v>4.587209873039352</v>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>-0.00772229821999415</v>
+      </c>
+      <c r="U87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="2" t="n">
+        <v>-1.0349</v>
+      </c>
+      <c r="AD87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE87" s="2" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="AF87" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AG87" s="2" t="n">
+        <v>-1.0349</v>
+      </c>
+      <c r="AH87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI87" s="2" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="AJ87" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AK87" s="2" t="n">
+        <v>-1.0349</v>
+      </c>
+      <c r="AL87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM87" s="2" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="AN87" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AO87" s="2" t="n">
+        <v>-1.0455</v>
+      </c>
+      <c r="AP87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ87" s="2" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="AR87" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AS87" s="2" t="n">
+        <v>-1.0455</v>
+      </c>
+      <c r="AT87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" s="2" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="AV87" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AW87" s="2" t="n">
+        <v>-1.0455</v>
+      </c>
+      <c r="AX87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY87" s="2" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="AZ87" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BA87" s="2" t="n">
+        <v>0.01148</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>SEAT</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:00-04:00</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>-1.211</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0.1003584140566811</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>1.901241622054268</v>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>0.06998759800438514</v>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>0.02931593980451075</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="2" t="n">
+        <v>1.121677539854089</v>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>-0.007424816088856812</v>
+      </c>
+      <c r="U88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AD88" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE88" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AF88" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AG88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI88" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AJ88" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AK88" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AL88" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM88" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AN88" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AO88" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AP88" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ88" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AR88" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AS88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AV88" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AW88" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AX88" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY88" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="AZ88" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="BA88" s="2" t="n">
+        <v>0.02314</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:03:00-04:00</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>-1.182</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0.06617643476683188</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>0.01934984508697557</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>1.425105285408671</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>0.02166164450961605</v>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>0.006896524222220612</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>-0.001087769642077574</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="2" t="n">
+        <v>2.622855327346076</v>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>-0.007308365413849494</v>
+      </c>
+      <c r="U89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD89" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE89" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AF89" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI89" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AJ89" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK89" s="2" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="AL89" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM89" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AN89" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO89" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP89" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ89" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AR89" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AS89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AV89" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW89" s="2" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="AX89" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY89" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AZ89" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA89" s="2" t="n">
+        <v>0.00291</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>TCBI</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:04:00-04:00</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>-1.429</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0.04845436819773852</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>0.01497488028525717</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>1.107508218307591</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>0.003548484070436286</v>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>0.00234642573906545</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>-0.005882371602743186</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="2" t="n">
+        <v>4.585171505233966</v>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>-0.007347208622055401</v>
+      </c>
+      <c r="U90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE90" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AF90" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI90" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AJ90" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM90" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AN90" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AO90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ90" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AR90" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AV90" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY90" s="2" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AZ90" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA90" s="2" t="n">
+        <v>0.00357</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:09:00-04:00</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>-1.267</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0.06219004600493228</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>0.03491732589730101</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>1.833983493507063</v>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>0.004912350722699799</v>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>0.002528687955610881</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>-0.00657005125773702</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="2" t="n">
+        <v>3.939832703099355</v>
+      </c>
+      <c r="T91" s="2" t="n">
+        <v>-0.008967333572445391</v>
+      </c>
+      <c r="U91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE91" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AF91" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI91" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AJ91" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AK91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM91" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AN91" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AO91" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP91" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ91" s="2" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="AR91" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" s="2" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="AV91" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW91" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX91" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY91" s="2" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="AZ91" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BA91" s="2" t="n">
+        <v>0.00019</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>VLY</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:09:00-04:00</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0.04800307050890473</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>0.006144387165389897</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>1.359461971993409</v>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>0.008169722907710453</v>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>0.008428028868129503</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>-0.002193764720494595</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="2" t="n">
+        <v>2.61337318770839</v>
+      </c>
+      <c r="T92" s="2" t="n">
+        <v>-0.008967333572445391</v>
+      </c>
+      <c r="U92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="2" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="AD92" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE92" s="2" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="AF92" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AG92" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="AH92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI92" s="2" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="AJ92" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AK92" s="2" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="AL92" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM92" s="2" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="AN92" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AO92" s="2" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="AP92" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ92" s="2" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="AR92" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AS92" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="AT92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU92" s="2" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="AV92" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AW92" s="2" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="AX92" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY92" s="2" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="AZ92" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="BA92" s="2" t="n">
+        <v>0.00073</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>-1.162</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0.04157615830745187</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-0.003260840607950843</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>1.647549896273965</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>0.009322115943702469</v>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>0.008087707180945741</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>-0.003898069463774356</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="2" t="n">
+        <v>3.646232927163261</v>
+      </c>
+      <c r="T93" s="2" t="n">
+        <v>-0.008989913160955321</v>
+      </c>
+      <c r="U93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE93" s="2" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AF93" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AG93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI93" s="2" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AJ93" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AK93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM93" s="2" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AN93" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AO93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ93" s="2" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AR93" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AS93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU93" s="2" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AV93" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AW93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY93" s="2" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AZ93" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BA93" s="2" t="n">
+        <v>0.00078</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>HCSG</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:13:00-04:00</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0.0773837114704139</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>0.007369956771448249</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.9801330864458045</v>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>0.01260406218237309</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>0.00983323623985329</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>-0.004680877036236653</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="2" t="n">
+        <v>3.152308554501536</v>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>-0.008989913160955321</v>
+      </c>
+      <c r="U94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE94" s="2" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AF94" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI94" s="2" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AJ94" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AK94" s="2" t="n">
+        <v>1.0359</v>
+      </c>
+      <c r="AL94" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM94" s="2" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AN94" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AO94" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="2" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AR94" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AS94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" s="2" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AV94" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW94" s="2" t="n">
+        <v>1.0359</v>
+      </c>
+      <c r="AX94" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY94" s="2" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AZ94" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA94" s="2" t="n">
+        <v>0.00171</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:18:00-04:00</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>-1.134</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0.05994149682247985</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>0.002923981500329909</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.8239540341769523</v>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>0.003404026589288955</v>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>0.01164750957854414</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>-0.02100527372584249</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2" t="n">
+        <v>4.178226046202803</v>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>-0.009377950494962706</v>
+      </c>
+      <c r="U95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE95" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
+      <c r="AF95" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AG95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI95" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
+      <c r="AJ95" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AK95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM95" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
+      <c r="AN95" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AO95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ95" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
+      <c r="AR95" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AS95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU95" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
+      <c r="AV95" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AW95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY95" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
+      <c r="AZ95" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="BA95" s="2" t="n">
+        <v>0.00338</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:20:00-04:00</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0.06559915572240049</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>0.03491732589730101</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>1.846106650256659</v>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>0.006905648919721896</v>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>0.007270979299895944</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>-0.003381627769285966</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="2" t="n">
+        <v>3.943037073750131</v>
+      </c>
+      <c r="T96" s="2" t="n">
+        <v>-0.010089444381855</v>
+      </c>
+      <c r="U96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="2" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="AD96" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE96" s="2" t="n">
+        <v>51.575</v>
+      </c>
+      <c r="AF96" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AG96" s="2" t="n">
+        <v>0.6933</v>
+      </c>
+      <c r="AH96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI96" s="2" t="n">
+        <v>51.575</v>
+      </c>
+      <c r="AJ96" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK96" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL96" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM96" s="2" t="n">
+        <v>51.575</v>
+      </c>
+      <c r="AN96" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AO96" s="2" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="AP96" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ96" s="2" t="n">
+        <v>51.575</v>
+      </c>
+      <c r="AR96" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AS96" s="2" t="n">
+        <v>0.6933</v>
+      </c>
+      <c r="AT96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU96" s="2" t="n">
+        <v>51.575</v>
+      </c>
+      <c r="AV96" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AW96" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AX96" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY96" s="2" t="n">
+        <v>51.575</v>
+      </c>
+      <c r="AZ96" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BA96" s="2" t="n">
+        <v>0.00019</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:21:00-04:00</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0.04694256972277944</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>0.05558984489450847</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>2.150219565358524</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>0.00299167915179499</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>0.008849602134970018</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>-0.009351247323469369</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2" t="n">
+        <v>2.830267878837636</v>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>-0.01010231316831334</v>
+      </c>
+      <c r="U97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE97" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AF97" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI97" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AJ97" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK97" s="2" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="AL97" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM97" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AN97" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AO97" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AR97" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AV97" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW97" s="2" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="AX97" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY97" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AZ97" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA97" s="2" t="n">
+        <v>0.00059</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:25:00-04:00</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>failed_breakdown</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0.04941316928172124</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>0.05558984489450847</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>2.180068173952178</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0.005059466634929288</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>0.009417290951948947</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>-0.007013491230432711</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="2" t="n">
+        <v>2.832624922212279</v>
+      </c>
+      <c r="T98" s="2" t="n">
+        <v>-0.01116947504904153</v>
+      </c>
+      <c r="U98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE98" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AF98" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI98" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AJ98" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK98" s="2" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="AL98" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM98" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN98" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO98" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AR98" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AS98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AV98" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW98" s="2" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="AX98" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY98" s="2" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AZ98" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA98" s="2" t="n">
+        <v>0.00059</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:28:00-04:00</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>-1.222</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0.07283397929966906</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>0.04655870777517723</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>1.559026247000713</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>0.01743099765166201</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>0.03392579377939742</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>-0.01855558786470646</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="2" t="n">
+        <v>0.9745218881776941</v>
+      </c>
+      <c r="T99" s="2" t="n">
+        <v>-0.01249535480231134</v>
+      </c>
+      <c r="U99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD99" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE99" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AF99" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI99" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ99" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK99" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AL99" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM99" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AN99" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO99" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP99" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ99" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AR99" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV99" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW99" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AX99" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY99" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AZ99" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA99" s="2" t="n">
+        <v>0.01521</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>RTO</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0.08269960529488651</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>0.06368812675527735</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>1.33384734484748</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0.01311904041451961</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>0.008779661133318465</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="2" t="n">
+        <v>3.125882988161508</v>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>-0.01321971747566197</v>
+      </c>
+      <c r="U100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="2" t="n">
+        <v>0.6795</v>
+      </c>
+      <c r="AD100" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE100" s="2" t="n">
+        <v>22.775</v>
+      </c>
+      <c r="AF100" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AG100" s="2" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AH100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI100" s="2" t="n">
+        <v>22.775</v>
+      </c>
+      <c r="AJ100" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AK100" s="2" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="AL100" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM100" s="2" t="n">
+        <v>22.775</v>
+      </c>
+      <c r="AN100" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AO100" s="2" t="n">
+        <v>0.6795</v>
+      </c>
+      <c r="AP100" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ100" s="2" t="n">
+        <v>22.775</v>
+      </c>
+      <c r="AR100" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AS100" s="2" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AT100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" s="2" t="n">
+        <v>22.775</v>
+      </c>
+      <c r="AV100" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AW100" s="2" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="AX100" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY100" s="2" t="n">
+        <v>22.775</v>
+      </c>
+      <c r="AZ100" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="BA100" s="2" t="n">
+        <v>0.00044</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:34:00-04:00</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0.05713398434513328</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>0.05558984489450847</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>2.172976994488655</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0.01148756064725243</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>0.006719238834710825</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>-0.002622382091730158</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="2" t="n">
+        <v>2.839955258608977</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>-0.01367241454040236</v>
+      </c>
+      <c r="U101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD101" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE101" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AF101" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI101" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AJ101" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK101" s="2" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="AL101" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM101" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AN101" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AO101" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP101" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ101" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AR101" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AS101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AV101" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW101" s="2" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="AX101" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY101" s="2" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AZ101" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA101" s="2" t="n">
+        <v>0.00058</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>VLY</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:37:00-04:00</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0.04262667680403376</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>0.006144387165389897</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>1.273238616570152</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>0.0004915429308747221</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>0.001841606601576029</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>-0.009124087718268781</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="2" t="n">
+        <v>2.608229851769549</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>-0.01367241454040236</v>
+      </c>
+      <c r="U102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE102" s="2" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AF102" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="2" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AJ102" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK102" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL102" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM102" s="2" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AN102" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AO102" s="2" t="n"/>
+      <c r="AP102" s="2" t="n"/>
+      <c r="AQ102" s="2" t="n"/>
+      <c r="AR102" s="2" t="n"/>
+      <c r="AS102" s="2" t="n"/>
+      <c r="AT102" s="2" t="n"/>
+      <c r="AU102" s="2" t="n"/>
+      <c r="AV102" s="2" t="n"/>
+      <c r="AW102" s="2" t="n"/>
+      <c r="AX102" s="2" t="n"/>
+      <c r="AY102" s="2" t="n"/>
+      <c r="AZ102" s="2" t="n"/>
+      <c r="BA102" s="2" t="n">
+        <v>0.00074</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BHVN</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:37:00-04:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>failed_breakdown</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0.2982978820800781</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>0.3672340880049036</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>4.098100523283233</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>-0.03918622300510333</v>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>0.01737136102608478</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>-0.07769049153317154</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="2" t="n">
+        <v>2.724907325670496</v>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>-0.01367241454040236</v>
+      </c>
+      <c r="U103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD103" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE103" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AF103" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI103" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AJ103" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK103" s="2" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="AL103" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM103" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AN103" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AO103" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP103" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ103" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AR103" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AS103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AV103" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW103" s="2" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="AX103" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY103" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AZ103" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BA103" s="2" t="n">
+        <v>0.00262</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>HTZ</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:40:00-04:00</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0.1086957247861691</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-0.0193236536922804</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>2.005298242163168</v>
+      </c>
+      <c r="O104" s="2" t="n">
+        <v>0.0004689419197265732</v>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>0.02396517405906206</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>-0.06322700565659023</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="2" t="n">
+        <v>0.8307328767560571</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>-0.01365946680433372</v>
+      </c>
+      <c r="U104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE104" s="2" t="n">
+        <v>2.2999</v>
+      </c>
+      <c r="AF104" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AG104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI104" s="2" t="n">
+        <v>2.2999</v>
+      </c>
+      <c r="AJ104" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AK104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM104" s="2" t="n">
+        <v>2.2999</v>
+      </c>
+      <c r="AN104" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AO104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ104" s="2" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AR104" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AS104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU104" s="2" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AV104" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AW104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY104" s="2" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="AZ104" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BA104" s="2" t="n">
+        <v>0.00436</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>KSS</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:49:00-04:00</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0.07490974092249236</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>0.02617328193591062</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.9557035655127334</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>0.01594749083607083</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>0.01091518464127918</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>-0.002094727383796124</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="2" t="n">
+        <v>3.170525551115408</v>
+      </c>
+      <c r="T105" s="2" t="n">
+        <v>-0.01351980494393512</v>
+      </c>
+      <c r="U105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE105" s="2" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AF105" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AG105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI105" s="2" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AJ105" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AK105" s="2" t="n">
+        <v>1.1304</v>
+      </c>
+      <c r="AL105" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM105" s="2" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AN105" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AO105" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ105" s="2" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AR105" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AS105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" s="2" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AV105" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AW105" s="2" t="n">
+        <v>1.1304</v>
+      </c>
+      <c r="AX105" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY105" s="2" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AZ105" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BA105" s="2" t="n">
+        <v>0.00084</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0.1009311741555035</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>0.04655870777517723</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>1.877699736560318</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>0.02654607077632254</v>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>0.01812967715513763</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>-0.004320621866451324</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="2" t="n">
+        <v>1.000374505889212</v>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>-0.01332329936421084</v>
+      </c>
+      <c r="U106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC106" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD106" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE106" s="2" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="AF106" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI106" s="2" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="AJ106" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK106" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL106" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM106" s="2" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="AN106" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO106" s="2" t="n"/>
+      <c r="AP106" s="2" t="n"/>
+      <c r="AQ106" s="2" t="n"/>
+      <c r="AR106" s="2" t="n"/>
+      <c r="AS106" s="2" t="n"/>
+      <c r="AT106" s="2" t="n"/>
+      <c r="AU106" s="2" t="n"/>
+      <c r="AV106" s="2" t="n"/>
+      <c r="AW106" s="2" t="n"/>
+      <c r="AX106" s="2" t="n"/>
+      <c r="AY106" s="2" t="n"/>
+      <c r="AZ106" s="2" t="n"/>
+      <c r="BA106" s="2" t="n">
+        <v>0.01109</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:25:00-04:00</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0.06385447402425903</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>0.01934984508697557</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>1.560489282630104</v>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>0.001378320874990679</v>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>0.007639133243602101</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>-0.01115106023201318</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="2" t="n">
+        <v>2.620675113291206</v>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>-0.01134411158674742</v>
+      </c>
+      <c r="U107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD107" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE107" s="2" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="AF107" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AG107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI107" s="2" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="AJ107" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AK107" s="2" t="n">
+        <v>1.0476</v>
+      </c>
+      <c r="AL107" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM107" s="2" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="AN107" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AO107" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP107" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ107" s="2" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="AR107" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AS107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU107" s="2" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="AV107" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AW107" s="2" t="n">
+        <v>1.0476</v>
+      </c>
+      <c r="AX107" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY107" s="2" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="AZ107" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="BA107" s="2" t="n">
+        <v>0.00073</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:28:00-04:00</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0.07155612193522143</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>0.002923981500329909</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.663116037886393</v>
+      </c>
+      <c r="O108" s="2" t="n">
+        <v>0.01210467522892356</v>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>0.009323070901731767</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>-0.0102776469963366</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="n">
+        <v>4.189124242819792</v>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>-0.01212026520437248</v>
+      </c>
+      <c r="U108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="2" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="AD108" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE108" s="2" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="AF108" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AG108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI108" s="2" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="AJ108" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AK108" s="2" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="AL108" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM108" s="2" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="AN108" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AO108" s="2" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="AP108" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ108" s="2" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="AR108" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AS108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU108" s="2" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="AV108" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AW108" s="2" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="AX108" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY108" s="2" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="AZ108" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BA108" s="2" t="n">
+        <v>0.00197</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>RTO</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:31:00-04:00</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0.08174901323721651</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>0.06368812675527735</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>1.841381763075774</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>0.001300697417002894</v>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>0.0008787446696269248</v>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>-0.007197339745685705</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="2" t="n">
+        <v>3.12500461931445</v>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>-0.01312916227279193</v>
+      </c>
+      <c r="U109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="2" t="n"/>
+      <c r="AD109" s="2" t="n"/>
+      <c r="AE109" s="2" t="n"/>
+      <c r="AF109" s="2" t="n"/>
+      <c r="AG109" s="2" t="n"/>
+      <c r="AH109" s="2" t="n"/>
+      <c r="AI109" s="2" t="n"/>
+      <c r="AJ109" s="2" t="n"/>
+      <c r="AK109" s="2" t="n"/>
+      <c r="AL109" s="2" t="n"/>
+      <c r="AM109" s="2" t="n"/>
+      <c r="AN109" s="2" t="n"/>
+      <c r="AO109" s="2" t="n"/>
+      <c r="AP109" s="2" t="n"/>
+      <c r="AQ109" s="2" t="n"/>
+      <c r="AR109" s="2" t="n"/>
+      <c r="AS109" s="2" t="n"/>
+      <c r="AT109" s="2" t="n"/>
+      <c r="AU109" s="2" t="n"/>
+      <c r="AV109" s="2" t="n"/>
+      <c r="AW109" s="2" t="n"/>
+      <c r="AX109" s="2" t="n"/>
+      <c r="AY109" s="2" t="n"/>
+      <c r="AZ109" s="2" t="n"/>
+      <c r="BA109" s="2" t="n">
+        <v>0.00044</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>TCBI</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>97.06999999999999</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:43:00-04:00</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0.04433633936435522</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>0.01497488028525717</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>1.551001833580639</v>
+      </c>
+      <c r="O110" s="2" t="n">
+        <v>0.00274578530314229</v>
+      </c>
+      <c r="P110" s="2" t="n">
+        <v>0.005786880973711928</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>-0.01028889380586751</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="2" t="n">
+        <v>4.581236057572221</v>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>-0.01237890412730402</v>
+      </c>
+      <c r="U110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD110" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE110" s="2" t="n">
+        <v>97.63500000000001</v>
+      </c>
+      <c r="AF110" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AG110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI110" s="2" t="n">
+        <v>97.63500000000001</v>
+      </c>
+      <c r="AJ110" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AK110" s="2" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="AL110" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM110" s="2" t="n">
+        <v>97.63500000000001</v>
+      </c>
+      <c r="AN110" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AO110" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP110" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ110" s="2" t="n">
+        <v>97.63500000000001</v>
+      </c>
+      <c r="AR110" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AS110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU110" s="2" t="n">
+        <v>97.63500000000001</v>
+      </c>
+      <c r="AV110" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AW110" s="2" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="AX110" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY110" s="2" t="n">
+        <v>97.63500000000001</v>
+      </c>
+      <c r="AZ110" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="BA110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>BDN</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:56:00-04:00</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0.0999999911696825</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>0.06296290180483743</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>1.962294992086417</v>
+      </c>
+      <c r="O111" s="2" t="n">
+        <v>0.01676855767800345</v>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>0.01010101963678015</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>-0.01164728269476301</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="2" t="n">
+        <v>1.088561962447682</v>
+      </c>
+      <c r="T111" s="2" t="n">
+        <v>-0.01091723104453413</v>
+      </c>
+      <c r="U111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE111" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF111" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI111" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AJ111" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM111" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AN111" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AO111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ111" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AR111" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AS111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AV111" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY111" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AZ111" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA111" s="2" t="n">
+        <v>0.00337</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:13:00-04:00</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>-1.222</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0.03768846599210574</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>0.08793967410935988</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>1.447841584482257</v>
+      </c>
+      <c r="O112" s="2" t="n">
+        <v>0.004575237277089972</v>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>0.01694917978238224</v>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>-0.08425722730731022</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="2" t="n">
+        <v>1.418277434682606</v>
+      </c>
+      <c r="T112" s="2" t="n">
+        <v>-0.01054214144659527</v>
+      </c>
+      <c r="U112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE112" s="2" t="n">
+        <v>4.1299</v>
+      </c>
+      <c r="AF112" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="AG112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI112" s="2" t="n">
+        <v>4.1299</v>
+      </c>
+      <c r="AJ112" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="AK112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM112" s="2" t="n">
+        <v>4.1299</v>
+      </c>
+      <c r="AN112" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="AO112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ112" s="2" t="n">
+        <v>4.1299</v>
+      </c>
+      <c r="AR112" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="AS112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" s="2" t="n">
+        <v>4.1299</v>
+      </c>
+      <c r="AV112" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="AW112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY112" s="2" t="n">
+        <v>4.1299</v>
+      </c>
+      <c r="AZ112" s="2" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="BA112" s="2" t="n">
+        <v>0.00243</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>AVEX</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:05:00-04:00</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0.09039255913371691</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>0.1322313732042746</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>1.490026765659701</v>
+      </c>
+      <c r="O113" s="2" t="n">
+        <v>0.009991869428253475</v>
+      </c>
+      <c r="P113" s="2" t="n">
+        <v>0.0137375936507248</v>
+      </c>
+      <c r="Q113" s="2" t="n">
+        <v>-0.05674703297761596</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="2" t="n">
+        <v>2.356599710213195</v>
+      </c>
+      <c r="T113" s="2" t="n">
+        <v>-0.01341377561747081</v>
+      </c>
+      <c r="U113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE113" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AF113" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI113" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AJ113" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM113" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AN113" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AO113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ113" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AR113" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AS113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AV113" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY113" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AZ113" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA113" s="2" t="n">
+        <v>0.00284</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>AVEX</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:25:00-04:00</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0.08374994187315821</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>0.1322313732042746</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>1.44368951851306</v>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>0.00355659720427548</v>
+      </c>
+      <c r="P114" s="2" t="n">
+        <v>0.002926379435607833</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>-0.0624932831581877</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="2" t="n">
+        <v>2.350489128292605</v>
+      </c>
+      <c r="T114" s="2" t="n">
+        <v>-0.01294805186705172</v>
+      </c>
+      <c r="U114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE114" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AF114" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI114" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AJ114" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM114" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AN114" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AO114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ114" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AR114" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AS114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AV114" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY114" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AZ114" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA114" s="2" t="n">
+        <v>0.00095</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>HCSG</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:15:00-04:00</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0.1176877205399405</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>0.007369956771448249</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.7166637146787168</v>
+      </c>
+      <c r="O115" s="2" t="n">
+        <v>0.02444905365303418</v>
+      </c>
+      <c r="P115" s="2" t="n">
+        <v>0.01421798468272841</v>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="2" t="n">
+        <v>3.189034957703602</v>
+      </c>
+      <c r="T115" s="2" t="n">
+        <v>-0.01372420548467679</v>
+      </c>
+      <c r="U115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="2" t="n">
+        <v>1.2941</v>
+      </c>
+      <c r="AD115" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE115" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AF115" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG115" s="2" t="n">
+        <v>1.5882</v>
+      </c>
+      <c r="AH115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI115" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AJ115" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK115" s="2" t="n">
+        <v>1.2941</v>
+      </c>
+      <c r="AL115" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM115" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AN115" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AO115" s="2" t="n">
+        <v>1.2941</v>
+      </c>
+      <c r="AP115" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ115" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AR115" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS115" s="2" t="n">
+        <v>1.5882</v>
+      </c>
+      <c r="AT115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU115" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AV115" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AW115" s="2" t="n">
+        <v>1.2941</v>
+      </c>
+      <c r="AX115" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY115" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="AZ115" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BA115" s="2" t="n">
+        <v>0.00206</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>VLY</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:22:00-04:00</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>-1.286</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0.05491545113481378</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>0.006144387165389897</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.9082550678874798</v>
+      </c>
+      <c r="O116" s="2" t="n">
+        <v>0.008690651399738014</v>
+      </c>
+      <c r="P116" s="2" t="n">
+        <v>0.003276276505428967</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>-0.0003639093540181992</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" s="2" t="n">
+        <v>2.619947294551041</v>
+      </c>
+      <c r="T116" s="2" t="n">
+        <v>-0.01239185186337266</v>
+      </c>
+      <c r="U116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE116" s="2" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AF116" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI116" s="2" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AJ116" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM116" s="2" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AN116" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ116" s="2" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AR116" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" s="2" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AV116" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY116" s="2" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AZ116" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA116" s="2" t="n">
+        <v>0.00073</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>KSS</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:33:00-04:00</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>-1.533</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0.1096570542377311</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>0.02617328193591062</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>1.424018853415301</v>
+      </c>
+      <c r="O117" s="2" t="n">
+        <v>0.003009487157753954</v>
+      </c>
+      <c r="P117" s="2" t="n">
+        <v>0.001626683706371601</v>
+      </c>
+      <c r="Q117" s="2" t="n">
+        <v>-0.01639999389648439</v>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" s="2" t="n">
+        <v>3.202339862433384</v>
+      </c>
+      <c r="T117" s="2" t="n">
+        <v>-0.01442267268589026</v>
+      </c>
+      <c r="U117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="2" t="n"/>
+      <c r="AD117" s="2" t="n"/>
+      <c r="AE117" s="2" t="n"/>
+      <c r="AF117" s="2" t="n"/>
+      <c r="AG117" s="2" t="n"/>
+      <c r="AH117" s="2" t="n"/>
+      <c r="AI117" s="2" t="n"/>
+      <c r="AJ117" s="2" t="n"/>
+      <c r="AK117" s="2" t="n"/>
+      <c r="AL117" s="2" t="n"/>
+      <c r="AM117" s="2" t="n"/>
+      <c r="AN117" s="2" t="n"/>
+      <c r="AO117" s="2" t="n"/>
+      <c r="AP117" s="2" t="n"/>
+      <c r="AQ117" s="2" t="n"/>
+      <c r="AR117" s="2" t="n"/>
+      <c r="AS117" s="2" t="n"/>
+      <c r="AT117" s="2" t="n"/>
+      <c r="AU117" s="2" t="n"/>
+      <c r="AV117" s="2" t="n"/>
+      <c r="AW117" s="2" t="n"/>
+      <c r="AX117" s="2" t="n"/>
+      <c r="AY117" s="2" t="n"/>
+      <c r="AZ117" s="2" t="n"/>
+      <c r="BA117" s="2" t="n">
+        <v>0.00041</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>RTO</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0.08721478158864726</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>0.06368812675527735</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>1.899846484945523</v>
+      </c>
+      <c r="O118" s="2" t="n">
+        <v>0.00196498597372563</v>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>0.001092896174863326</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>-0.004569170771450359</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="2" t="n">
+        <v>3.130044611161585</v>
+      </c>
+      <c r="T118" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="2" t="n"/>
+      <c r="AB118" s="2" t="n"/>
+      <c r="AC118" s="2" t="n"/>
+      <c r="AD118" s="2" t="n"/>
+      <c r="AE118" s="2" t="n"/>
+      <c r="AF118" s="2" t="n"/>
+      <c r="AG118" s="2" t="n"/>
+      <c r="AH118" s="2" t="n"/>
+      <c r="AI118" s="2" t="n"/>
+      <c r="AJ118" s="2" t="n"/>
+      <c r="AK118" s="2" t="n"/>
+      <c r="AL118" s="2" t="n"/>
+      <c r="AM118" s="2" t="n"/>
+      <c r="AN118" s="2" t="n"/>
+      <c r="AO118" s="2" t="n"/>
+      <c r="AP118" s="2" t="n"/>
+      <c r="AQ118" s="2" t="n"/>
+      <c r="AR118" s="2" t="n"/>
+      <c r="AS118" s="2" t="n"/>
+      <c r="AT118" s="2" t="n"/>
+      <c r="AU118" s="2" t="n"/>
+      <c r="AV118" s="2" t="n"/>
+      <c r="AW118" s="2" t="n"/>
+      <c r="AX118" s="2" t="n"/>
+      <c r="AY118" s="2" t="n"/>
+      <c r="AZ118" s="2" t="n"/>
+      <c r="BA118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>TCBI</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:28:00-04:00</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0.04963097118057158</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>0.01497488028525717</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>1.966719065209498</v>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>0.003350397080115641</v>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>0.01202483732238019</v>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>-0.005271203896783816</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" s="2" t="n">
+        <v>4.586293102229183</v>
+      </c>
+      <c r="T119" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="2" t="n"/>
+      <c r="AB119" s="2" t="n"/>
+      <c r="AC119" s="2" t="n"/>
+      <c r="AD119" s="2" t="n"/>
+      <c r="AE119" s="2" t="n"/>
+      <c r="AF119" s="2" t="n"/>
+      <c r="AG119" s="2" t="n"/>
+      <c r="AH119" s="2" t="n"/>
+      <c r="AI119" s="2" t="n"/>
+      <c r="AJ119" s="2" t="n"/>
+      <c r="AK119" s="2" t="n"/>
+      <c r="AL119" s="2" t="n"/>
+      <c r="AM119" s="2" t="n"/>
+      <c r="AN119" s="2" t="n"/>
+      <c r="AO119" s="2" t="n"/>
+      <c r="AP119" s="2" t="n"/>
+      <c r="AQ119" s="2" t="n"/>
+      <c r="AR119" s="2" t="n"/>
+      <c r="AS119" s="2" t="n"/>
+      <c r="AT119" s="2" t="n"/>
+      <c r="AU119" s="2" t="n"/>
+      <c r="AV119" s="2" t="n"/>
+      <c r="AW119" s="2" t="n"/>
+      <c r="AX119" s="2" t="n"/>
+      <c r="AY119" s="2" t="n"/>
+      <c r="AZ119" s="2" t="n"/>
+      <c r="BA119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0.06694210251289223</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>0.03491732589730101</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>1.191250236513228</v>
+      </c>
+      <c r="O120" s="2" t="n">
+        <v>0.003273854371829588</v>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>0.00135552653903534</v>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>-0.00500770033796516</v>
+      </c>
+      <c r="R120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="2" t="n">
+        <v>3.944296554159085</v>
+      </c>
+      <c r="T120" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="2" t="n"/>
+      <c r="AB120" s="2" t="n"/>
+      <c r="AC120" s="2" t="n"/>
+      <c r="AD120" s="2" t="n"/>
+      <c r="AE120" s="2" t="n"/>
+      <c r="AF120" s="2" t="n"/>
+      <c r="AG120" s="2" t="n"/>
+      <c r="AH120" s="2" t="n"/>
+      <c r="AI120" s="2" t="n"/>
+      <c r="AJ120" s="2" t="n"/>
+      <c r="AK120" s="2" t="n"/>
+      <c r="AL120" s="2" t="n"/>
+      <c r="AM120" s="2" t="n"/>
+      <c r="AN120" s="2" t="n"/>
+      <c r="AO120" s="2" t="n"/>
+      <c r="AP120" s="2" t="n"/>
+      <c r="AQ120" s="2" t="n"/>
+      <c r="AR120" s="2" t="n"/>
+      <c r="AS120" s="2" t="n"/>
+      <c r="AT120" s="2" t="n"/>
+      <c r="AU120" s="2" t="n"/>
+      <c r="AV120" s="2" t="n"/>
+      <c r="AW120" s="2" t="n"/>
+      <c r="AX120" s="2" t="n"/>
+      <c r="AY120" s="2" t="n"/>
+      <c r="AZ120" s="2" t="n"/>
+      <c r="BA120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>KSS</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0.1297382680413577</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>0.02617328193591062</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>1.942968388584304</v>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>0.01749296276741319</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>0.01058517471648809</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>-0.0009975905452133116</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="2" t="n">
+        <v>3.220274839686926</v>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="2" t="n"/>
+      <c r="AB121" s="2" t="n"/>
+      <c r="AC121" s="2" t="n"/>
+      <c r="AD121" s="2" t="n"/>
+      <c r="AE121" s="2" t="n"/>
+      <c r="AF121" s="2" t="n"/>
+      <c r="AG121" s="2" t="n"/>
+      <c r="AH121" s="2" t="n"/>
+      <c r="AI121" s="2" t="n"/>
+      <c r="AJ121" s="2" t="n"/>
+      <c r="AK121" s="2" t="n"/>
+      <c r="AL121" s="2" t="n"/>
+      <c r="AM121" s="2" t="n"/>
+      <c r="AN121" s="2" t="n"/>
+      <c r="AO121" s="2" t="n"/>
+      <c r="AP121" s="2" t="n"/>
+      <c r="AQ121" s="2" t="n"/>
+      <c r="AR121" s="2" t="n"/>
+      <c r="AS121" s="2" t="n"/>
+      <c r="AT121" s="2" t="n"/>
+      <c r="AU121" s="2" t="n"/>
+      <c r="AV121" s="2" t="n"/>
+      <c r="AW121" s="2" t="n"/>
+      <c r="AX121" s="2" t="n"/>
+      <c r="AY121" s="2" t="n"/>
+      <c r="AZ121" s="2" t="n"/>
+      <c r="BA121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0.0753489864721979</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>0.05558984489450847</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>1.814398262325544</v>
+      </c>
+      <c r="O122" s="2" t="n">
+        <v>0.009661720392303508</v>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>0.003440609250726435</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>-0.002583744406758792</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="2" t="n">
+        <v>2.857039048151139</v>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="2" t="n"/>
+      <c r="AB122" s="2" t="n"/>
+      <c r="AC122" s="2" t="n"/>
+      <c r="AD122" s="2" t="n"/>
+      <c r="AE122" s="2" t="n"/>
+      <c r="AF122" s="2" t="n"/>
+      <c r="AG122" s="2" t="n"/>
+      <c r="AH122" s="2" t="n"/>
+      <c r="AI122" s="2" t="n"/>
+      <c r="AJ122" s="2" t="n"/>
+      <c r="AK122" s="2" t="n"/>
+      <c r="AL122" s="2" t="n"/>
+      <c r="AM122" s="2" t="n"/>
+      <c r="AN122" s="2" t="n"/>
+      <c r="AO122" s="2" t="n"/>
+      <c r="AP122" s="2" t="n"/>
+      <c r="AQ122" s="2" t="n"/>
+      <c r="AR122" s="2" t="n"/>
+      <c r="AS122" s="2" t="n"/>
+      <c r="AT122" s="2" t="n"/>
+      <c r="AU122" s="2" t="n"/>
+      <c r="AV122" s="2" t="n"/>
+      <c r="AW122" s="2" t="n"/>
+      <c r="AX122" s="2" t="n"/>
+      <c r="AY122" s="2" t="n"/>
+      <c r="AZ122" s="2" t="n"/>
+      <c r="BA122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>VLY</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0.05645158454959764</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>0.006144387165389897</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.9129924792523939</v>
+      </c>
+      <c r="O123" s="2" t="n">
+        <v>0.008477968767383492</v>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>0.002544537560866457</v>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>-0.002538060007899134</v>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="2" t="n">
+        <v>2.621402402696488</v>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="2" t="n"/>
+      <c r="AB123" s="2" t="n"/>
+      <c r="AC123" s="2" t="n"/>
+      <c r="AD123" s="2" t="n"/>
+      <c r="AE123" s="2" t="n"/>
+      <c r="AF123" s="2" t="n"/>
+      <c r="AG123" s="2" t="n"/>
+      <c r="AH123" s="2" t="n"/>
+      <c r="AI123" s="2" t="n"/>
+      <c r="AJ123" s="2" t="n"/>
+      <c r="AK123" s="2" t="n"/>
+      <c r="AL123" s="2" t="n"/>
+      <c r="AM123" s="2" t="n"/>
+      <c r="AN123" s="2" t="n"/>
+      <c r="AO123" s="2" t="n"/>
+      <c r="AP123" s="2" t="n"/>
+      <c r="AQ123" s="2" t="n"/>
+      <c r="AR123" s="2" t="n"/>
+      <c r="AS123" s="2" t="n"/>
+      <c r="AT123" s="2" t="n"/>
+      <c r="AU123" s="2" t="n"/>
+      <c r="AV123" s="2" t="n"/>
+      <c r="AW123" s="2" t="n"/>
+      <c r="AX123" s="2" t="n"/>
+      <c r="AY123" s="2" t="n"/>
+      <c r="AZ123" s="2" t="n"/>
+      <c r="BA123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>BDN</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0.1055554971773449</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>0.06296290180483743</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>1.979254496639822</v>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>0.01701000288994892</v>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>0.01507534227044944</v>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>-0.006655646783166214</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" s="2" t="n">
+        <v>1.093599711700788</v>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>-0.01288339213631884</v>
+      </c>
+      <c r="U124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="2" t="n"/>
+      <c r="AB124" s="2" t="n"/>
+      <c r="AC124" s="2" t="n"/>
+      <c r="AD124" s="2" t="n"/>
+      <c r="AE124" s="2" t="n"/>
+      <c r="AF124" s="2" t="n"/>
+      <c r="AG124" s="2" t="n"/>
+      <c r="AH124" s="2" t="n"/>
+      <c r="AI124" s="2" t="n"/>
+      <c r="AJ124" s="2" t="n"/>
+      <c r="AK124" s="2" t="n"/>
+      <c r="AL124" s="2" t="n"/>
+      <c r="AM124" s="2" t="n"/>
+      <c r="AN124" s="2" t="n"/>
+      <c r="AO124" s="2" t="n"/>
+      <c r="AP124" s="2" t="n"/>
+      <c r="AQ124" s="2" t="n"/>
+      <c r="AR124" s="2" t="n"/>
+      <c r="AS124" s="2" t="n"/>
+      <c r="AT124" s="2" t="n"/>
+      <c r="AU124" s="2" t="n"/>
+      <c r="AV124" s="2" t="n"/>
+      <c r="AW124" s="2" t="n"/>
+      <c r="AX124" s="2" t="n"/>
+      <c r="AY124" s="2" t="n"/>
+      <c r="AZ124" s="2" t="n"/>
+      <c r="BA124" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16259,7 +23505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17325,6 +24571,232 @@
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>VLY</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ZGN</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
         </is>
       </c>
     </row>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2903,6 +2903,372 @@
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>5-min ORB: green first 5 min, closed above range high 13.52 | news: [Benzinga] Ermenegildo Zegna Reports Q3 2026 Financial Resul</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Premarket-high break: closed above PM high 9.28, above VWAP | news: [Benzinga] Rithm Capital Reports Q3 2026 Financial Results E</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Premarket-high break: closed above PM high 9.28, above VWAP | news: [Benzinga] Rithm Capital Reports Q3 2026 Financial Results E</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +7.7%, dipped to VWAP 13.04, reclaimed with green bar | news: [Newswire] Hesai Group to Report Third Quarter 2026 Financia</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>73.42</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>5-min ORB: green first 5 min, closed above range high 75.50 | news: [Benzinga] The Gorman-Rupp Company Increases Quarterly Divid</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>hod_break</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Gap-and-go: +10.0%, based 21 min, broke HOD 1.26 on 1.5x vol | news: [Benzinga] UWM Holdings Reports Preliminary Q3 Net Income Of</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>15-min ORB: closed above 15-min high 13.18, above VWAP | news: [Newswire] Hesai Group to Report Third Quarter 2026 Financia</t>
         </is>
       </c>
     </row>
@@ -2917,7 +3283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA124"/>
+  <dimension ref="A1:BA171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22733,8 +23099,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
+      <c r="H118" s="2" t="n">
+        <v>-1.545</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -22788,8 +23160,12 @@
       <c r="Z118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA118" s="2" t="n"/>
-      <c r="AB118" s="2" t="n"/>
+      <c r="AA118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC118" s="2" t="n"/>
       <c r="AD118" s="2" t="n"/>
       <c r="AE118" s="2" t="n"/>
@@ -22814,7 +23190,9 @@
       <c r="AX118" s="2" t="n"/>
       <c r="AY118" s="2" t="n"/>
       <c r="AZ118" s="2" t="n"/>
-      <c r="BA118" s="2" t="n"/>
+      <c r="BA118" s="2" t="n">
+        <v>0.00044</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -22959,8 +23337,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="n"/>
+      <c r="H120" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -23014,8 +23398,12 @@
       <c r="Z120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA120" s="2" t="n"/>
-      <c r="AB120" s="2" t="n"/>
+      <c r="AA120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC120" s="2" t="n"/>
       <c r="AD120" s="2" t="n"/>
       <c r="AE120" s="2" t="n"/>
@@ -23040,7 +23428,9 @@
       <c r="AX120" s="2" t="n"/>
       <c r="AY120" s="2" t="n"/>
       <c r="AZ120" s="2" t="n"/>
-      <c r="BA120" s="2" t="n"/>
+      <c r="BA120" s="2" t="n">
+        <v>0.00019</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -23072,8 +23462,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="n"/>
+      <c r="H121" s="2" t="n">
+        <v>-1.133</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -23127,33 +23523,87 @@
       <c r="Z121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA121" s="2" t="n"/>
-      <c r="AB121" s="2" t="n"/>
-      <c r="AC121" s="2" t="n"/>
-      <c r="AD121" s="2" t="n"/>
-      <c r="AE121" s="2" t="n"/>
-      <c r="AF121" s="2" t="n"/>
-      <c r="AG121" s="2" t="n"/>
-      <c r="AH121" s="2" t="n"/>
-      <c r="AI121" s="2" t="n"/>
-      <c r="AJ121" s="2" t="n"/>
-      <c r="AK121" s="2" t="n"/>
-      <c r="AL121" s="2" t="n"/>
-      <c r="AM121" s="2" t="n"/>
-      <c r="AN121" s="2" t="n"/>
-      <c r="AO121" s="2" t="n"/>
-      <c r="AP121" s="2" t="n"/>
-      <c r="AQ121" s="2" t="n"/>
-      <c r="AR121" s="2" t="n"/>
-      <c r="AS121" s="2" t="n"/>
-      <c r="AT121" s="2" t="n"/>
-      <c r="AU121" s="2" t="n"/>
-      <c r="AV121" s="2" t="n"/>
-      <c r="AW121" s="2" t="n"/>
-      <c r="AX121" s="2" t="n"/>
-      <c r="AY121" s="2" t="n"/>
-      <c r="AZ121" s="2" t="n"/>
-      <c r="BA121" s="2" t="n"/>
+      <c r="AA121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" s="2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AF121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI121" s="2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AJ121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM121" s="2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AN121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AO121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ121" s="2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AR121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AS121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU121" s="2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AV121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY121" s="2" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AZ121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BA121" s="2" t="n">
+        <v>0.0004</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -23185,8 +23635,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H122" s="2" t="n"/>
-      <c r="I122" s="2" t="n"/>
+      <c r="H122" s="2" t="n">
+        <v>-4.176</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -23240,33 +23696,87 @@
       <c r="Z122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA122" s="2" t="n"/>
-      <c r="AB122" s="2" t="n"/>
-      <c r="AC122" s="2" t="n"/>
-      <c r="AD122" s="2" t="n"/>
-      <c r="AE122" s="2" t="n"/>
-      <c r="AF122" s="2" t="n"/>
-      <c r="AG122" s="2" t="n"/>
-      <c r="AH122" s="2" t="n"/>
-      <c r="AI122" s="2" t="n"/>
-      <c r="AJ122" s="2" t="n"/>
-      <c r="AK122" s="2" t="n"/>
-      <c r="AL122" s="2" t="n"/>
-      <c r="AM122" s="2" t="n"/>
-      <c r="AN122" s="2" t="n"/>
-      <c r="AO122" s="2" t="n"/>
-      <c r="AP122" s="2" t="n"/>
-      <c r="AQ122" s="2" t="n"/>
-      <c r="AR122" s="2" t="n"/>
-      <c r="AS122" s="2" t="n"/>
-      <c r="AT122" s="2" t="n"/>
-      <c r="AU122" s="2" t="n"/>
-      <c r="AV122" s="2" t="n"/>
-      <c r="AW122" s="2" t="n"/>
-      <c r="AX122" s="2" t="n"/>
-      <c r="AY122" s="2" t="n"/>
-      <c r="AZ122" s="2" t="n"/>
-      <c r="BA122" s="2" t="n"/>
+      <c r="AA122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="2" t="n">
+        <v>-2.1818</v>
+      </c>
+      <c r="AD122" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE122" s="2" t="n">
+        <v>17.405</v>
+      </c>
+      <c r="AF122" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AG122" s="2" t="n">
+        <v>-5.3636</v>
+      </c>
+      <c r="AH122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI122" s="2" t="n">
+        <v>17.405</v>
+      </c>
+      <c r="AJ122" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AK122" s="2" t="n">
+        <v>-2.1818</v>
+      </c>
+      <c r="AL122" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM122" s="2" t="n">
+        <v>17.405</v>
+      </c>
+      <c r="AN122" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AO122" s="2" t="n">
+        <v>-2.1818</v>
+      </c>
+      <c r="AP122" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ122" s="2" t="n">
+        <v>17.405</v>
+      </c>
+      <c r="AR122" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AS122" s="2" t="n">
+        <v>-5.3636</v>
+      </c>
+      <c r="AT122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" s="2" t="n">
+        <v>17.405</v>
+      </c>
+      <c r="AV122" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AW122" s="2" t="n">
+        <v>-2.1818</v>
+      </c>
+      <c r="AX122" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY122" s="2" t="n">
+        <v>17.405</v>
+      </c>
+      <c r="AZ122" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BA122" s="2" t="n">
+        <v>0.00057</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -23298,8 +23808,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H123" s="2" t="n"/>
-      <c r="I123" s="2" t="n"/>
+      <c r="H123" s="2" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -23353,33 +23869,87 @@
       <c r="Z123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA123" s="2" t="n"/>
-      <c r="AB123" s="2" t="n"/>
-      <c r="AC123" s="2" t="n"/>
-      <c r="AD123" s="2" t="n"/>
-      <c r="AE123" s="2" t="n"/>
-      <c r="AF123" s="2" t="n"/>
-      <c r="AG123" s="2" t="n"/>
-      <c r="AH123" s="2" t="n"/>
-      <c r="AI123" s="2" t="n"/>
-      <c r="AJ123" s="2" t="n"/>
-      <c r="AK123" s="2" t="n"/>
-      <c r="AL123" s="2" t="n"/>
-      <c r="AM123" s="2" t="n"/>
-      <c r="AN123" s="2" t="n"/>
-      <c r="AO123" s="2" t="n"/>
-      <c r="AP123" s="2" t="n"/>
-      <c r="AQ123" s="2" t="n"/>
-      <c r="AR123" s="2" t="n"/>
-      <c r="AS123" s="2" t="n"/>
-      <c r="AT123" s="2" t="n"/>
-      <c r="AU123" s="2" t="n"/>
-      <c r="AV123" s="2" t="n"/>
-      <c r="AW123" s="2" t="n"/>
-      <c r="AX123" s="2" t="n"/>
-      <c r="AY123" s="2" t="n"/>
-      <c r="AZ123" s="2" t="n"/>
-      <c r="BA123" s="2" t="n"/>
+      <c r="AA123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD123" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE123" s="2" t="n">
+        <v>13.755</v>
+      </c>
+      <c r="AF123" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG123" s="2" t="n">
+        <v>4.7143</v>
+      </c>
+      <c r="AH123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI123" s="2" t="n">
+        <v>13.755</v>
+      </c>
+      <c r="AJ123" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK123" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AL123" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM123" s="2" t="n">
+        <v>13.755</v>
+      </c>
+      <c r="AN123" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO123" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP123" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ123" s="2" t="n">
+        <v>13.755</v>
+      </c>
+      <c r="AR123" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS123" s="2" t="n">
+        <v>4.7143</v>
+      </c>
+      <c r="AT123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" s="2" t="n">
+        <v>13.755</v>
+      </c>
+      <c r="AV123" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW123" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AX123" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY123" s="2" t="n">
+        <v>13.755</v>
+      </c>
+      <c r="AZ123" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA123" s="2" t="n">
+        <v>0.00073</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -23411,8 +23981,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n"/>
+      <c r="H124" s="2" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -23466,33 +24042,7712 @@
       <c r="Z124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA124" s="2" t="n"/>
-      <c r="AB124" s="2" t="n"/>
-      <c r="AC124" s="2" t="n"/>
-      <c r="AD124" s="2" t="n"/>
-      <c r="AE124" s="2" t="n"/>
-      <c r="AF124" s="2" t="n"/>
-      <c r="AG124" s="2" t="n"/>
-      <c r="AH124" s="2" t="n"/>
-      <c r="AI124" s="2" t="n"/>
-      <c r="AJ124" s="2" t="n"/>
-      <c r="AK124" s="2" t="n"/>
-      <c r="AL124" s="2" t="n"/>
-      <c r="AM124" s="2" t="n"/>
-      <c r="AN124" s="2" t="n"/>
-      <c r="AO124" s="2" t="n"/>
-      <c r="AP124" s="2" t="n"/>
-      <c r="AQ124" s="2" t="n"/>
-      <c r="AR124" s="2" t="n"/>
-      <c r="AS124" s="2" t="n"/>
-      <c r="AT124" s="2" t="n"/>
-      <c r="AU124" s="2" t="n"/>
-      <c r="AV124" s="2" t="n"/>
-      <c r="AW124" s="2" t="n"/>
-      <c r="AX124" s="2" t="n"/>
-      <c r="AY124" s="2" t="n"/>
-      <c r="AZ124" s="2" t="n"/>
-      <c r="BA124" s="2" t="n"/>
+      <c r="AA124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AF124" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI124" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AJ124" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM124" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AN124" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ124" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AR124" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV124" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY124" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AZ124" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA124" s="2" t="n">
+        <v>0.00335</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:39:00-04:00</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>-1.068</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0.08170545531647422</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>0.03835737269011719</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>2.240065882881898</v>
+      </c>
+      <c r="O125" s="2" t="n">
+        <v>0.02028740046544519</v>
+      </c>
+      <c r="P125" s="2" t="n">
+        <v>0.03005537295026655</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="2" t="n">
+        <v>4.328889544306516</v>
+      </c>
+      <c r="T125" s="2" t="n">
+        <v>-0.006152170364746468</v>
+      </c>
+      <c r="U125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" s="2" t="n">
+        <v>-1.0215</v>
+      </c>
+      <c r="AD125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE125" s="2" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="AF125" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG125" s="2" t="n">
+        <v>-1.0215</v>
+      </c>
+      <c r="AH125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI125" s="2" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="AJ125" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK125" s="2" t="n">
+        <v>-1.0215</v>
+      </c>
+      <c r="AL125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM125" s="2" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="AN125" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO125" s="2" t="n">
+        <v>-1.0216</v>
+      </c>
+      <c r="AP125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ125" s="2" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="AR125" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS125" s="2" t="n">
+        <v>-1.0216</v>
+      </c>
+      <c r="AT125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" s="2" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="AV125" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW125" s="2" t="n">
+        <v>-1.0216</v>
+      </c>
+      <c r="AX125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY125" s="2" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="AZ125" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>AXTI</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:45:00-04:00</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>-1.048</v>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0.06322727375298198</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>0.02996505290524776</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>2.002347538073074</v>
+      </c>
+      <c r="O126" s="2" t="n">
+        <v>0.0350183913142208</v>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>0.02863917737256844</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>-0.006884077225780771</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="2" t="n">
+        <v>4.00405508530777</v>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>-0.004594494037216346</v>
+      </c>
+      <c r="U126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE126" s="2" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AF126" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI126" s="2" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AJ126" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM126" s="2" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AN126" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ126" s="2" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AR126" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" s="2" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AV126" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AW126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY126" s="2" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AZ126" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA126" s="2" t="n">
+        <v>0.00312</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:45:00-04:00</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>-1.182</v>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0.07192396095648701</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>0.05184329417555511</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>2.053400511750559</v>
+      </c>
+      <c r="O127" s="2" t="n">
+        <v>0.01522314860810869</v>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>0.01013513161695254</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>-0.001684483595573272</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="2" t="n">
+        <v>2.230476692020004</v>
+      </c>
+      <c r="T127" s="2" t="n">
+        <v>-0.004594494037216346</v>
+      </c>
+      <c r="U127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE127" s="2" t="n">
+        <v>9.3001</v>
+      </c>
+      <c r="AF127" s="2" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="AG127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI127" s="2" t="n">
+        <v>9.3001</v>
+      </c>
+      <c r="AJ127" s="2" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="AK127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM127" s="2" t="n">
+        <v>9.3001</v>
+      </c>
+      <c r="AN127" s="2" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="AO127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ127" s="2" t="n">
+        <v>9.3001</v>
+      </c>
+      <c r="AR127" s="2" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="AS127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" s="2" t="n">
+        <v>9.3001</v>
+      </c>
+      <c r="AV127" s="2" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="AW127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY127" s="2" t="n">
+        <v>9.3001</v>
+      </c>
+      <c r="AZ127" s="2" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="BA127" s="2" t="n">
+        <v>0.00107</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:49:00-04:00</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>-1.182</v>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0.08607908128015151</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>0.05024708726740346</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>1.867707050397807</v>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>0.01255454348340557</v>
+      </c>
+      <c r="P128" s="2" t="n">
+        <v>0.01630644010422784</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="2" t="n">
+        <v>2.579079851630559</v>
+      </c>
+      <c r="T128" s="2" t="n">
+        <v>-0.00424855679055236</v>
+      </c>
+      <c r="U128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AD128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE128" s="2" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AF128" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG128" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AH128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI128" s="2" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AJ128" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK128" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AL128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM128" s="2" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AN128" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AO128" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AP128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ128" s="2" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AR128" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS128" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AT128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" s="2" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AV128" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW128" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AX128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY128" s="2" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AZ128" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA128" s="2" t="n">
+        <v>0.00304</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:59:00-04:00</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0.07660620471176371</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>0.05024708726740346</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>1.668475589105892</v>
+      </c>
+      <c r="O129" s="2" t="n">
+        <v>0.00264536886330391</v>
+      </c>
+      <c r="P129" s="2" t="n">
+        <v>0.002295309527520465</v>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>-0.008722087306222703</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="2" t="n">
+        <v>2.570319504286797</v>
+      </c>
+      <c r="T129" s="2" t="n">
+        <v>-0.003926907054970674</v>
+      </c>
+      <c r="U129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" s="2" t="n"/>
+      <c r="AD129" s="2" t="n"/>
+      <c r="AE129" s="2" t="n"/>
+      <c r="AF129" s="2" t="n"/>
+      <c r="AG129" s="2" t="n"/>
+      <c r="AH129" s="2" t="n"/>
+      <c r="AI129" s="2" t="n"/>
+      <c r="AJ129" s="2" t="n"/>
+      <c r="AK129" s="2" t="n"/>
+      <c r="AL129" s="2" t="n"/>
+      <c r="AM129" s="2" t="n"/>
+      <c r="AN129" s="2" t="n"/>
+      <c r="AO129" s="2" t="n"/>
+      <c r="AP129" s="2" t="n"/>
+      <c r="AQ129" s="2" t="n"/>
+      <c r="AR129" s="2" t="n"/>
+      <c r="AS129" s="2" t="n"/>
+      <c r="AT129" s="2" t="n"/>
+      <c r="AU129" s="2" t="n"/>
+      <c r="AV129" s="2" t="n"/>
+      <c r="AW129" s="2" t="n"/>
+      <c r="AX129" s="2" t="n"/>
+      <c r="AY129" s="2" t="n"/>
+      <c r="AZ129" s="2" t="n"/>
+      <c r="BA129" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>failed_breakdown</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0.1268577160451956</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>1.7486248737368</v>
+      </c>
+      <c r="O130" s="2" t="n">
+        <v>-0.009807646571813544</v>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>0.02826187259413979</v>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>-0.05349981037060214</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" s="2" t="n">
+        <v>3.748562434712996</v>
+      </c>
+      <c r="T130" s="2" t="n">
+        <v>-0.00447673156571915</v>
+      </c>
+      <c r="U130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC130" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" s="2" t="n">
+        <v>42.695</v>
+      </c>
+      <c r="AF130" s="2" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AG130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI130" s="2" t="n">
+        <v>42.695</v>
+      </c>
+      <c r="AJ130" s="2" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AK130" s="2" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="AL130" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM130" s="2" t="n">
+        <v>42.695</v>
+      </c>
+      <c r="AN130" s="2" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AO130" s="2" t="n"/>
+      <c r="AP130" s="2" t="n"/>
+      <c r="AQ130" s="2" t="n"/>
+      <c r="AR130" s="2" t="n"/>
+      <c r="AS130" s="2" t="n"/>
+      <c r="AT130" s="2" t="n"/>
+      <c r="AU130" s="2" t="n"/>
+      <c r="AV130" s="2" t="n"/>
+      <c r="AW130" s="2" t="n"/>
+      <c r="AX130" s="2" t="n"/>
+      <c r="AY130" s="2" t="n"/>
+      <c r="AZ130" s="2" t="n"/>
+      <c r="BA130" s="2" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>ITG</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:01:00-04:00</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>-1.095</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>failed_breakdown</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0.07302234199787416</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>0.07505078606076299</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>1.730931329800667</v>
+      </c>
+      <c r="O131" s="2" t="n">
+        <v>0.001040524993883185</v>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>0.03969753560819812</v>
+      </c>
+      <c r="Q131" s="2" t="n">
+        <v>-0.08318891172620257</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="2" t="n">
+        <v>1.66581823865906</v>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>-0.003809144583473589</v>
+      </c>
+      <c r="U131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" s="2" t="n">
+        <v>5.2701</v>
+      </c>
+      <c r="AF131" s="2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AG131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI131" s="2" t="n">
+        <v>5.2701</v>
+      </c>
+      <c r="AJ131" s="2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AK131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM131" s="2" t="n">
+        <v>5.2701</v>
+      </c>
+      <c r="AN131" s="2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AO131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ131" s="2" t="n">
+        <v>5.2701</v>
+      </c>
+      <c r="AR131" s="2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AS131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" s="2" t="n">
+        <v>5.2701</v>
+      </c>
+      <c r="AV131" s="2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AW131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY131" s="2" t="n">
+        <v>5.2701</v>
+      </c>
+      <c r="AZ131" s="2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="BA131" s="2" t="n">
+        <v>0.00568</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:03:00-04:00</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>-1.444</v>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0.06105987492364018</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>0.05184329417555511</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>1.824424089497148</v>
+      </c>
+      <c r="O132" s="2" t="n">
+        <v>0.001079096960610704</v>
+      </c>
+      <c r="P132" s="2" t="n">
+        <v>0.003257333118644467</v>
+      </c>
+      <c r="Q132" s="2" t="n">
+        <v>-0.01180253865655523</v>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="2" t="n">
+        <v>2.220289854409124</v>
+      </c>
+      <c r="T132" s="2" t="n">
+        <v>-0.00407095436576399</v>
+      </c>
+      <c r="U132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE132" s="2" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="AF132" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AG132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI132" s="2" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="AJ132" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AK132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM132" s="2" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="AN132" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AO132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ132" s="2" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="AR132" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU132" s="2" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="AV132" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY132" s="2" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="AZ132" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA132" s="2" t="n">
+        <v>0.00109</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:06:00-04:00</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>hod_break</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0.1000000103660255</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>0.01739128812274293</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>1.324347268128761</v>
+      </c>
+      <c r="O133" s="2" t="n">
+        <v>0.03450911144232816</v>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>0.02766797319421249</v>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="2" t="n">
+        <v>0.2350721108710924</v>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>-0.004640352693009664</v>
+      </c>
+      <c r="U133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE133" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF133" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI133" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AJ133" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM133" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN133" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO133" s="2" t="n"/>
+      <c r="AP133" s="2" t="n"/>
+      <c r="AQ133" s="2" t="n"/>
+      <c r="AR133" s="2" t="n"/>
+      <c r="AS133" s="2" t="n"/>
+      <c r="AT133" s="2" t="n"/>
+      <c r="AU133" s="2" t="n"/>
+      <c r="AV133" s="2" t="n"/>
+      <c r="AW133" s="2" t="n"/>
+      <c r="AX133" s="2" t="n"/>
+      <c r="AY133" s="2" t="n"/>
+      <c r="AZ133" s="2" t="n"/>
+      <c r="BA133" s="2" t="n">
+        <v>0.00791</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>KOS</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:09:00-04:00</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0.06296290180483743</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>0.02222220063700142</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>1.466425607642042</v>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>0.01038391911978787</v>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>0.01393724291082677</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="2" t="n">
+        <v>1.054311989896645</v>
+      </c>
+      <c r="T134" s="2" t="n">
+        <v>-0.004398196620344907</v>
+      </c>
+      <c r="U134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD134" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE134" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AF134" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG134" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH134" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI134" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AJ134" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK134" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AL134" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM134" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AN134" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO134" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP134" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ134" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AR134" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS134" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AV134" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW134" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AX134" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY134" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AZ134" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA134" s="2" t="n">
+        <v>0.00349</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>KOS</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:09:00-04:00</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0.06296290180483743</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>0.02222220063700142</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>1.466425607642042</v>
+      </c>
+      <c r="O135" s="2" t="n">
+        <v>0.01038391911978787</v>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>0.01393724291082677</v>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="2" t="n">
+        <v>1.054311989896645</v>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>-0.004398196620344907</v>
+      </c>
+      <c r="U135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD135" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE135" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AF135" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG135" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI135" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AJ135" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK135" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AL135" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM135" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AN135" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO135" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP135" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ135" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AR135" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS135" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU135" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AV135" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW135" s="2" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="AX135" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY135" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AZ135" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA135" s="2" t="n">
+        <v>0.00349</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>TTMI</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0.04614973190251637</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>0.008120158060322735</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>1.645649785242395</v>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>0.01795103269937637</v>
+      </c>
+      <c r="P136" s="2" t="n">
+        <v>0.01047869365820676</v>
+      </c>
+      <c r="Q136" s="2" t="n">
+        <v>-0.01011644670483225</v>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="2" t="n">
+        <v>4.347693995072778</v>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>-0.004711936936199201</v>
+      </c>
+      <c r="U136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="2" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="AD136" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE136" s="2" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="AF136" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AG136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI136" s="2" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="AJ136" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AK136" s="2" t="n">
+        <v>0.7331</v>
+      </c>
+      <c r="AL136" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM136" s="2" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="AN136" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO136" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP136" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ136" s="2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AR136" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AS136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" s="2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AV136" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AW136" s="2" t="n">
+        <v>0.8056</v>
+      </c>
+      <c r="AX136" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY136" s="2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AZ136" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BA136" s="2" t="n">
+        <v>0.00259</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>-1.613</v>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0.06316840836550686</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>0.03835737269011719</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>1.917519589475938</v>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>0.004851645966196028</v>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>0.008181297995810343</v>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>-0.01726644445188574</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="2" t="n">
+        <v>4.311604137633153</v>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>-0.004711936936199201</v>
+      </c>
+      <c r="U137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="2" t="n">
+        <v>-1.5567</v>
+      </c>
+      <c r="AD137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE137" s="2" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AF137" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG137" s="2" t="n">
+        <v>-1.5567</v>
+      </c>
+      <c r="AH137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI137" s="2" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AJ137" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK137" s="2" t="n">
+        <v>-1.5567</v>
+      </c>
+      <c r="AL137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM137" s="2" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AN137" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO137" s="2" t="n">
+        <v>-1.6844</v>
+      </c>
+      <c r="AP137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ137" s="2" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="AR137" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AS137" s="2" t="n">
+        <v>-1.6844</v>
+      </c>
+      <c r="AT137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU137" s="2" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="AV137" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AW137" s="2" t="n">
+        <v>-1.6844</v>
+      </c>
+      <c r="AX137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY137" s="2" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="AZ137" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BA137" s="2" t="n">
+        <v>0.01277</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>CCI</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:11:00-04:00</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>-1.138</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>failed_breakdown</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0.1201305872030194</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>0.1546364902811601</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>2.156577206021235</v>
+      </c>
+      <c r="O138" s="2" t="n">
+        <v>-0.009341940488230338</v>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>0.009172108628881334</v>
+      </c>
+      <c r="Q138" s="2" t="n">
+        <v>-0.03444091833883689</v>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="2" t="n">
+        <v>4.480738932526941</v>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>-0.004830098873339073</v>
+      </c>
+      <c r="U138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE138" s="2" t="n">
+        <v>88.29989999999999</v>
+      </c>
+      <c r="AF138" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AG138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI138" s="2" t="n">
+        <v>88.29989999999999</v>
+      </c>
+      <c r="AJ138" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AK138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM138" s="2" t="n">
+        <v>88.29989999999999</v>
+      </c>
+      <c r="AN138" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AO138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ138" s="2" t="n">
+        <v>88.29989999999999</v>
+      </c>
+      <c r="AR138" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AS138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU138" s="2" t="n">
+        <v>88.29989999999999</v>
+      </c>
+      <c r="AV138" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="AW138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY138" s="2" t="n">
+        <v>88.29989999999999</v>
+      </c>
+      <c r="AZ138" s="2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="BA138" s="2" t="n">
+        <v>0.00136</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>BORR</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:14:00-04:00</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>-1.308</v>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0.06225494893868677</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>0.01470586860331125</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>1.055558607016438</v>
+      </c>
+      <c r="O139" s="2" t="n">
+        <v>0.03359401395490913</v>
+      </c>
+      <c r="P139" s="2" t="n">
+        <v>0.01015230953002054</v>
+      </c>
+      <c r="Q139" s="2" t="n">
+        <v>-0.0002306637859176286</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="2" t="n">
+        <v>1.466490928639368</v>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>-0.004816996400255347</v>
+      </c>
+      <c r="U139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE139" s="2" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AF139" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AG139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI139" s="2" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AJ139" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AK139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM139" s="2" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AN139" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AO139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ139" s="2" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AR139" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AS139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU139" s="2" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AV139" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AW139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY139" s="2" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AZ139" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BA139" s="2" t="n">
+        <v>0.00231</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>46.34</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:15:00-04:00</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0.06188844957425976</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>-0.0009101459575189264</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>1.040655524554645</v>
+      </c>
+      <c r="O140" s="2" t="n">
+        <v>0.0262157559838283</v>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>0.007070884548799772</v>
+      </c>
+      <c r="Q140" s="2" t="n">
+        <v>-0.0008563672941848122</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="2" t="n">
+        <v>3.84310152072764</v>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>-0.004947941237964826</v>
+      </c>
+      <c r="U140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AF140" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI140" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AJ140" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK140" s="2" t="n">
+        <v>1.6439</v>
+      </c>
+      <c r="AL140" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM140" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AN140" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO140" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ140" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AR140" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AS140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AV140" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW140" s="2" t="n">
+        <v>1.6439</v>
+      </c>
+      <c r="AX140" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY140" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AZ140" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA140" s="2" t="n">
+        <v>0.00257</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>TTMI</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:15:00-04:00</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0.05345780187941851</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>0.008120158060322735</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>1.636500856141109</v>
+      </c>
+      <c r="O141" s="2" t="n">
+        <v>0.0227847065587472</v>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>0.02800612076634257</v>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>-0.003201434392675173</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" s="2" t="n">
+        <v>4.354655390831122</v>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>-0.004947941237964826</v>
+      </c>
+      <c r="U141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="2" t="n">
+        <v>1.0505</v>
+      </c>
+      <c r="AD141" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE141" s="2" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AF141" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG141" s="2" t="n">
+        <v>1.1009</v>
+      </c>
+      <c r="AH141" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI141" s="2" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AJ141" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK141" s="2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="AL141" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM141" s="2" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AN141" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO141" s="2" t="n">
+        <v>1.0505</v>
+      </c>
+      <c r="AP141" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ141" s="2" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AR141" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS141" s="2" t="n">
+        <v>1.1009</v>
+      </c>
+      <c r="AT141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU141" s="2" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AV141" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW141" s="2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="AX141" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY141" s="2" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AZ141" s="2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA141" s="2" t="n">
+        <v>0.00193</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>TTMI</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:19:00-04:00</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>-1.106</v>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0.05758556352098254</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>0.008120158060322735</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>1.634534404851375</v>
+      </c>
+      <c r="O142" s="2" t="n">
+        <v>0.0249842383450547</v>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>0.01298863249943551</v>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>-0.003125433709524783</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="2" t="n">
+        <v>4.358566032336403</v>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>-0.006237256546662628</v>
+      </c>
+      <c r="U142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE142" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AF142" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AG142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI142" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AJ142" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM142" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AN142" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AO142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ142" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AR142" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AV142" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY142" s="2" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AZ142" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA142" s="2" t="n">
+        <v>0.00218</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:31:00-04:00</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0.06221197498472808</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>0.05184329417555511</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>1.632675467325416</v>
+      </c>
+      <c r="O143" s="2" t="n">
+        <v>0.002029517422592386</v>
+      </c>
+      <c r="P143" s="2" t="n">
+        <v>0.00759221963139554</v>
+      </c>
+      <c r="Q143" s="2" t="n">
+        <v>-0.01072955268989373</v>
+      </c>
+      <c r="R143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="2" t="n">
+        <v>2.221375066530412</v>
+      </c>
+      <c r="T143" s="2" t="n">
+        <v>-0.004856303819506746</v>
+      </c>
+      <c r="U143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE143" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AF143" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI143" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AJ143" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK143" s="2" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="AL143" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM143" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AN143" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO143" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ143" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AR143" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AV143" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW143" s="2" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="AX143" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY143" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AZ143" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA143" s="2" t="n">
+        <v>0.00108</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BORR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:36:00-04:00</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0.05514703648038077</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>0.01470586860331125</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>0.9510065460999992</v>
+      </c>
+      <c r="O144" s="2" t="n">
+        <v>0.02076703160961824</v>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>0.01045292221439867</v>
+      </c>
+      <c r="Q144" s="2" t="n">
+        <v>-0.008064590557306128</v>
+      </c>
+      <c r="R144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" s="2" t="n">
+        <v>1.459777098004809</v>
+      </c>
+      <c r="T144" s="2" t="n">
+        <v>-0.005137767311422903</v>
+      </c>
+      <c r="U144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE144" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AF144" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI144" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ144" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK144" s="2" t="n">
+        <v>1.1425</v>
+      </c>
+      <c r="AL144" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM144" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AN144" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO144" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ144" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR144" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV144" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW144" s="2" t="n">
+        <v>1.1425</v>
+      </c>
+      <c r="AX144" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY144" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ144" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA144" s="2" t="n">
+        <v>0.00232</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:40:00-04:00</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0.1545726860793721</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>1.441181975315832</v>
+      </c>
+      <c r="O145" s="2" t="n">
+        <v>0.01554876771767866</v>
+      </c>
+      <c r="P145" s="2" t="n">
+        <v>0.01021276453955318</v>
+      </c>
+      <c r="Q145" s="2" t="n">
+        <v>-0.03022071841480023</v>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="2" t="n">
+        <v>3.772859764563288</v>
+      </c>
+      <c r="T145" s="2" t="n">
+        <v>-0.004156040547680151</v>
+      </c>
+      <c r="U145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE145" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AF145" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AG145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI145" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AJ145" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AK145" s="2" t="n">
+        <v>1.0284</v>
+      </c>
+      <c r="AL145" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM145" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN145" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AO145" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ145" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AR145" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AS145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AV145" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AW145" s="2" t="n">
+        <v>1.0284</v>
+      </c>
+      <c r="AX145" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY145" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AZ145" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BA145" s="2" t="n">
+        <v>0.00368</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:44:00-04:00</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0.1042608614436618</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>0.01739128812274293</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>1.187777105864566</v>
+      </c>
+      <c r="O146" s="2" t="n">
+        <v>0.0279549043716858</v>
+      </c>
+      <c r="P146" s="2" t="n">
+        <v>0.0235451336108156</v>
+      </c>
+      <c r="Q146" s="2" t="n">
+        <v>-0.01558139388746493</v>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" s="2" t="n">
+        <v>0.2389381291260565</v>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>-0.003037376961586014</v>
+      </c>
+      <c r="U146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE146" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF146" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI146" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AJ146" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK146" s="2" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="AL146" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM146" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN146" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AO146" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ146" s="2" t="n">
+        <v>1.2698</v>
+      </c>
+      <c r="AR146" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AS146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" s="2" t="n">
+        <v>1.2698</v>
+      </c>
+      <c r="AV146" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AW146" s="2" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="AX146" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY146" s="2" t="n">
+        <v>1.2698</v>
+      </c>
+      <c r="AZ146" s="2" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="BA146" s="2" t="n">
+        <v>0.00791</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:46:00-04:00</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>-1.182</v>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0.07948922336269493</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>0.05024708726740346</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>1.291473361549941</v>
+      </c>
+      <c r="O147" s="2" t="n">
+        <v>0.003066266368584092</v>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>0.006486039313651409</v>
+      </c>
+      <c r="Q147" s="2" t="n">
+        <v>-0.007948561363166573</v>
+      </c>
+      <c r="R147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" s="2" t="n">
+        <v>2.572993801844909</v>
+      </c>
+      <c r="T147" s="2" t="n">
+        <v>-0.002722677928189032</v>
+      </c>
+      <c r="U147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE147" s="2" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AF147" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI147" s="2" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AJ147" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM147" s="2" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AN147" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ147" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AR147" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AS147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AV147" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY147" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AZ147" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA147" s="2" t="n">
+        <v>0.00229</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:47:00-04:00</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0.07430869601522372</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>0.05184329417555511</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>1.534977716766415</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>0.01264622330086329</v>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>0.01876673596188817</v>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>-0.0005359179508901413</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" s="2" t="n">
+        <v>2.232698945075738</v>
+      </c>
+      <c r="T148" s="2" t="n">
+        <v>-0.002356208147485273</v>
+      </c>
+      <c r="U148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="2" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AD148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE148" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AF148" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AG148" s="2" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AH148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI148" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AJ148" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK148" s="2" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AL148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM148" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AN148" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AO148" s="2" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AP148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ148" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AR148" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AS148" s="2" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AT148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU148" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AV148" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW148" s="2" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AX148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY148" s="2" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AZ148" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA148" s="2" t="n">
+        <v>0.00107</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>ENVX</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:47:00-04:00</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0.07843139271514366</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-0.02352938976529795</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>1.34735323685628</v>
+      </c>
+      <c r="O149" s="2" t="n">
+        <v>0.02097690302311928</v>
+      </c>
+      <c r="P149" s="2" t="n">
+        <v>0.01090909090909084</v>
+      </c>
+      <c r="Q149" s="2" t="n">
+        <v>-0.02482267195031562</v>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" s="2" t="n">
+        <v>1.01160091167848</v>
+      </c>
+      <c r="T149" s="2" t="n">
+        <v>-0.002356208147485273</v>
+      </c>
+      <c r="U149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE149" s="2" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AF149" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI149" s="2" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AJ149" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM149" s="2" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AN149" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO149" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP149" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ149" s="2" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AR149" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU149" s="2" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AV149" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AW149" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX149" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY149" s="2" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AZ149" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BA149" s="2" t="n">
+        <v>0.00363</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>AXTI</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:51:00-04:00</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>-1.172</v>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0.0479053014006583</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>0.02996505290524776</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>1.147488444542544</v>
+      </c>
+      <c r="O150" s="2" t="n">
+        <v>0.01251141478868867</v>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>0.007033107308573246</v>
+      </c>
+      <c r="Q150" s="2" t="n">
+        <v>-0.0211956878165136</v>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="2" t="n">
+        <v>3.989539425262913</v>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>-0.001858793529072034</v>
+      </c>
+      <c r="U150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE150" s="2" t="n">
+        <v>54.035</v>
+      </c>
+      <c r="AF150" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AG150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI150" s="2" t="n">
+        <v>54.035</v>
+      </c>
+      <c r="AJ150" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AK150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM150" s="2" t="n">
+        <v>54.035</v>
+      </c>
+      <c r="AN150" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AO150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ150" s="2" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="AR150" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AS150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" s="2" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="AV150" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AW150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY150" s="2" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="AZ150" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA150" s="2" t="n">
+        <v>0.00259</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>ITG</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:53:00-04:00</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>-1.154</v>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0.07910757746500408</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>0.07505078606076299</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>1.240761832639042</v>
+      </c>
+      <c r="O151" s="2" t="n">
+        <v>0.008281148762862456</v>
+      </c>
+      <c r="P151" s="2" t="n">
+        <v>0.02443612170425531</v>
+      </c>
+      <c r="Q151" s="2" t="n">
+        <v>-0.07798956858798434</v>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" s="2" t="n">
+        <v>1.671473335620729</v>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>-0.001466038909072154</v>
+      </c>
+      <c r="U151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE151" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AF151" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI151" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ151" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM151" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AN151" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AO151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ151" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR151" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AS151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV151" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY151" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ151" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA151" s="2" t="n">
+        <v>0.00567</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:05:00-04:00</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0.1906847482775649</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>1.321443806526047</v>
+      </c>
+      <c r="O152" s="2" t="n">
+        <v>0.04350268808953506</v>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>0.03265355229374557</v>
+      </c>
+      <c r="Q152" s="2" t="n">
+        <v>-0.002306020176828238</v>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" s="2" t="n">
+        <v>3.803658018161517</v>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>-0.001976556000569119</v>
+      </c>
+      <c r="U152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" s="2" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="AD152" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE152" s="2" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AF152" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG152" s="2" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="AH152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI152" s="2" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AJ152" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AK152" s="2" t="n">
+        <v>1.0065</v>
+      </c>
+      <c r="AL152" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM152" s="2" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AN152" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO152" s="2" t="n">
+        <v>1.0273</v>
+      </c>
+      <c r="AP152" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ152" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="AR152" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="AS152" s="2" t="n">
+        <v>1.0546</v>
+      </c>
+      <c r="AT152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU152" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="AV152" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="AW152" s="2" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="AX152" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY152" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="AZ152" s="2" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="BA152" s="2" t="n">
+        <v>0.00423</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:05:00-04:00</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>hod_break</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0.1906847482775649</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>1.321443806526047</v>
+      </c>
+      <c r="O153" s="2" t="n">
+        <v>0.04350268808953506</v>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>0.02128611707876428</v>
+      </c>
+      <c r="Q153" s="2" t="n">
+        <v>-0.002306020176828238</v>
+      </c>
+      <c r="R153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="2" t="n">
+        <v>3.803658018161517</v>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>-0.001976556000569119</v>
+      </c>
+      <c r="U153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE153" s="2" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AF153" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG153" s="2" t="n">
+        <v>1.4272</v>
+      </c>
+      <c r="AH153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI153" s="2" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AJ153" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK153" s="2" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="AL153" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM153" s="2" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AN153" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AO153" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ153" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="AR153" s="2" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="AS153" s="2" t="n">
+        <v>1.6178</v>
+      </c>
+      <c r="AT153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU153" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="AV153" s="2" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="AW153" s="2" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="AX153" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY153" s="2" t="n">
+        <v>44.865</v>
+      </c>
+      <c r="AZ153" s="2" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="BA153" s="2" t="n">
+        <v>0.00423</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:11:00-04:00</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>-1.148</v>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0.07390450116823555</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>0.06921733836914412</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>1.548865335531376</v>
+      </c>
+      <c r="O154" s="2" t="n">
+        <v>0.007673641853553015</v>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>0.01786435955172422</v>
+      </c>
+      <c r="Q154" s="2" t="n">
+        <v>-0.02696299611786268</v>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" s="2" t="n">
+        <v>4.590259539178711</v>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>-0.002081295892111035</v>
+      </c>
+      <c r="U154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="2" t="n">
+        <v>-1.0761</v>
+      </c>
+      <c r="AD154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE154" s="2" t="n">
+        <v>98.535</v>
+      </c>
+      <c r="AF154" s="2" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AG154" s="2" t="n">
+        <v>-1.0761</v>
+      </c>
+      <c r="AH154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI154" s="2" t="n">
+        <v>98.535</v>
+      </c>
+      <c r="AJ154" s="2" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AK154" s="2" t="n">
+        <v>-1.0761</v>
+      </c>
+      <c r="AL154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM154" s="2" t="n">
+        <v>98.535</v>
+      </c>
+      <c r="AN154" s="2" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="AO154" s="2" t="n">
+        <v>-1.0767</v>
+      </c>
+      <c r="AP154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ154" s="2" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="AR154" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS154" s="2" t="n">
+        <v>-1.0767</v>
+      </c>
+      <c r="AT154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" s="2" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="AV154" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AW154" s="2" t="n">
+        <v>-1.0767</v>
+      </c>
+      <c r="AX154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY154" s="2" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="AZ154" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BA154" s="2" t="n">
+        <v>0.01025</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:22:00-04:00</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0.08168373356696579</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>-0.0009101459575189264</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>0.8427848846925987</v>
+      </c>
+      <c r="O155" s="2" t="n">
+        <v>0.03080301272212593</v>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>0.008413986281533628</v>
+      </c>
+      <c r="Q155" s="2" t="n">
+        <v>-0.000525548447458668</v>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" s="2" t="n">
+        <v>3.86157148119009</v>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>-0.001623188692949196</v>
+      </c>
+      <c r="U155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" s="2" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AD155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE155" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="AF155" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG155" s="2" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AH155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI155" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="AJ155" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AK155" s="2" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AL155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM155" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="AN155" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AO155" s="2" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AP155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ155" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="AR155" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AS155" s="2" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AT155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="AV155" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AW155" s="2" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AX155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY155" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="AZ155" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BA155" s="2" t="n">
+        <v>0.00189</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:57:00-04:00</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0.2157643578096915</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>1.463658245805653</v>
+      </c>
+      <c r="O156" s="2" t="n">
+        <v>0.03698023611616708</v>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>0.008513454739130387</v>
+      </c>
+      <c r="Q156" s="2" t="n">
+        <v>-0.008870615244130686</v>
+      </c>
+      <c r="R156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" s="2" t="n">
+        <v>3.824502437876625</v>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>-0.001223882836407397</v>
+      </c>
+      <c r="U156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD156" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE156" s="2" t="n">
+        <v>45.7286</v>
+      </c>
+      <c r="AF156" s="2" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AG156" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI156" s="2" t="n">
+        <v>45.7286</v>
+      </c>
+      <c r="AJ156" s="2" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AK156" s="2" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="AL156" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM156" s="2" t="n">
+        <v>45.7286</v>
+      </c>
+      <c r="AN156" s="2" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AO156" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP156" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ156" s="2" t="n">
+        <v>45.7286</v>
+      </c>
+      <c r="AR156" s="2" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AS156" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU156" s="2" t="n">
+        <v>45.7286</v>
+      </c>
+      <c r="AV156" s="2" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AW156" s="2" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="AX156" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY156" s="2" t="n">
+        <v>45.7286</v>
+      </c>
+      <c r="AZ156" s="2" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="BA156" s="2" t="n">
+        <v>0.00372</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>ZLAB</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:32:00-04:00</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0.07350267080721684</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>0.05217783896370398</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>1.779514319952711</v>
+      </c>
+      <c r="O157" s="2" t="n">
+        <v>0.02118543027746944</v>
+      </c>
+      <c r="P157" s="2" t="n">
+        <v>0.01098900461068892</v>
+      </c>
+      <c r="Q157" s="2" t="n">
+        <v>-0.02392738981776399</v>
+      </c>
+      <c r="R157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" s="2" t="n">
+        <v>3.163785852101048</v>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>-0.002892850292021354</v>
+      </c>
+      <c r="U157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD157" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE157" s="2" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AF157" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AG157" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH157" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI157" s="2" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AJ157" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AK157" s="2" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="AL157" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM157" s="2" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AN157" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AO157" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP157" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ157" s="2" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AR157" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AS157" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" s="2" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AV157" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AW157" s="2" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="AX157" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY157" s="2" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AZ157" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BA157" s="2" t="n">
+        <v>0.00466</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:41:00-04:00</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0.1173912984887682</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>0.01739128812274293</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>0.9077176692016408</v>
+      </c>
+      <c r="O158" s="2" t="n">
+        <v>0.0311693133520814</v>
+      </c>
+      <c r="P158" s="2" t="n">
+        <v>0.02723732881754308</v>
+      </c>
+      <c r="Q158" s="2" t="n">
+        <v>-0.003875965410453319</v>
+      </c>
+      <c r="R158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" s="2" t="n">
+        <v>0.2507586923716177</v>
+      </c>
+      <c r="T158" s="2" t="n">
+        <v>-0.001937328474446276</v>
+      </c>
+      <c r="U158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AF158" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG158" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI158" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AJ158" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK158" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="AL158" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM158" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AN158" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO158" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ158" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AR158" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS158" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AV158" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW158" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="AX158" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY158" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AZ158" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA158" s="2" t="n">
+        <v>0.00778</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>ENVX</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:01:00-04:00</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0.1254901722457393</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>-0.02352938976529795</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>1.089284832695714</v>
+      </c>
+      <c r="O159" s="2" t="n">
+        <v>0.04695959745761069</v>
+      </c>
+      <c r="P159" s="2" t="n">
+        <v>0.01742156360725503</v>
+      </c>
+      <c r="Q159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" s="2" t="n">
+        <v>1.054311989896645</v>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>-0.003207149859775549</v>
+      </c>
+      <c r="U159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE159" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AF159" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AG159" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH159" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI159" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AJ159" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AK159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL159" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM159" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AN159" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AO159" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ159" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AR159" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AS159" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AV159" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AW159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX159" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY159" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="AZ159" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BA159" s="2" t="n">
+        <v>0.00349</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>ENVX</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:14:00-04:00</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0.1509803912402208</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>-0.02352938976529795</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>1.110269522723758</v>
+      </c>
+      <c r="O160" s="2" t="n">
+        <v>0.06526434032967554</v>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>0.01873933350998786</v>
+      </c>
+      <c r="Q160" s="2" t="n">
+        <v>-0.001021109944805865</v>
+      </c>
+      <c r="R160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" s="2" t="n">
+        <v>1.076707433784162</v>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>-0.004411219200300187</v>
+      </c>
+      <c r="U160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE160" s="2" t="n">
+        <v>2.9399</v>
+      </c>
+      <c r="AF160" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AG160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI160" s="2" t="n">
+        <v>2.9399</v>
+      </c>
+      <c r="AJ160" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AK160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM160" s="2" t="n">
+        <v>2.9399</v>
+      </c>
+      <c r="AN160" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AO160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ160" s="2" t="n">
+        <v>2.935</v>
+      </c>
+      <c r="AR160" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AS160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" s="2" t="n">
+        <v>2.935</v>
+      </c>
+      <c r="AV160" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AW160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY160" s="2" t="n">
+        <v>2.935</v>
+      </c>
+      <c r="AZ160" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BA160" s="2" t="n">
+        <v>0.00342</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0.06333121128491759</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>0.06921733836914412</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>1.304097634768349</v>
+      </c>
+      <c r="O161" s="2" t="n">
+        <v>0.0002261435294226288</v>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>0.001947750341504364</v>
+      </c>
+      <c r="Q161" s="2" t="n">
+        <v>-0.0365431797357253</v>
+      </c>
+      <c r="R161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="2" t="n">
+        <v>4.580365098353157</v>
+      </c>
+      <c r="T161" s="2" t="n">
+        <v>-0.004103630655344914</v>
+      </c>
+      <c r="U161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" s="2" t="n"/>
+      <c r="AD161" s="2" t="n"/>
+      <c r="AE161" s="2" t="n"/>
+      <c r="AF161" s="2" t="n"/>
+      <c r="AG161" s="2" t="n"/>
+      <c r="AH161" s="2" t="n"/>
+      <c r="AI161" s="2" t="n"/>
+      <c r="AJ161" s="2" t="n"/>
+      <c r="AK161" s="2" t="n"/>
+      <c r="AL161" s="2" t="n"/>
+      <c r="AM161" s="2" t="n"/>
+      <c r="AN161" s="2" t="n"/>
+      <c r="AO161" s="2" t="n"/>
+      <c r="AP161" s="2" t="n"/>
+      <c r="AQ161" s="2" t="n"/>
+      <c r="AR161" s="2" t="n"/>
+      <c r="AS161" s="2" t="n"/>
+      <c r="AT161" s="2" t="n"/>
+      <c r="AU161" s="2" t="n"/>
+      <c r="AV161" s="2" t="n"/>
+      <c r="AW161" s="2" t="n"/>
+      <c r="AX161" s="2" t="n"/>
+      <c r="AY161" s="2" t="n"/>
+      <c r="AZ161" s="2" t="n"/>
+      <c r="BA161" s="2" t="n">
+        <v>0.0038</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>ZLAB</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:17:00-04:00</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="n"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0.1011796483486205</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>0.05217783896370398</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>1.652613487836664</v>
+      </c>
+      <c r="O162" s="2" t="n">
+        <v>0.04128616782348549</v>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>0.01895345896528505</v>
+      </c>
+      <c r="Q162" s="2" t="n">
+        <v>-0.0004118710296139305</v>
+      </c>
+      <c r="R162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" s="2" t="n">
+        <v>3.189241038599806</v>
+      </c>
+      <c r="T162" s="2" t="n">
+        <v>-0.003663579303237685</v>
+      </c>
+      <c r="U162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE162" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AF162" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AG162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI162" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AJ162" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AK162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM162" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AN162" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AO162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ162" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AR162" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU162" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AV162" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AW162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY162" s="2" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AZ162" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BA162" s="2" t="n">
+        <v>0.00165</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>BORR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:20:00-04:00</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>-1.333</v>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0.08578429195524273</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>0.01470586860331125</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>1.369924278837187</v>
+      </c>
+      <c r="O163" s="2" t="n">
+        <v>0.01918255020743564</v>
+      </c>
+      <c r="P163" s="2" t="n">
+        <v>0.009029306972597434</v>
+      </c>
+      <c r="Q163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="2" t="n">
+        <v>1.488399545307297</v>
+      </c>
+      <c r="T163" s="2" t="n">
+        <v>-0.003901421146960127</v>
+      </c>
+      <c r="U163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE163" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AF163" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI163" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AJ163" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM163" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AN163" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ163" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AR163" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU163" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AV163" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY163" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AZ163" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA163" s="2" t="n">
+        <v>0.00226</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:24:00-04:00</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>-1.115</v>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0.2354033667740276</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>1.294127235034394</v>
+      </c>
+      <c r="O164" s="2" t="n">
+        <v>0.04003807721992225</v>
+      </c>
+      <c r="P164" s="2" t="n">
+        <v>0.01009665402285036</v>
+      </c>
+      <c r="Q164" s="2" t="n">
+        <v>-0.001672795696725515</v>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" s="2" t="n">
+        <v>3.840526987333399</v>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>-0.004358889201093508</v>
+      </c>
+      <c r="U164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE164" s="2" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="AF164" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AG164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI164" s="2" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="AJ164" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AK164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM164" s="2" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="AN164" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AO164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ164" s="2" t="n">
+        <v>46.545</v>
+      </c>
+      <c r="AR164" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AS164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU164" s="2" t="n">
+        <v>46.545</v>
+      </c>
+      <c r="AV164" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AW164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY164" s="2" t="n">
+        <v>46.545</v>
+      </c>
+      <c r="AZ164" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="BA164" s="2" t="n">
+        <v>0.00236</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>-0.127</v>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0.2000000207320507</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>0.01739128812274293</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>1.210270332559717</v>
+      </c>
+      <c r="O165" s="2" t="n">
+        <v>0.08416889377196557</v>
+      </c>
+      <c r="P165" s="2" t="n">
+        <v>0.02898550389118985</v>
+      </c>
+      <c r="Q165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" s="2" t="n">
+        <v>0.3220834957137716</v>
+      </c>
+      <c r="T165" s="2" t="n">
+        <v>-0.004493029763945389</v>
+      </c>
+      <c r="U165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE165" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF165" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG165" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AH165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI165" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AJ165" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK165" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AL165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM165" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN165" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO165" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ165" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR165" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS165" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV165" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW165" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AX165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY165" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ165" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA165" s="2" t="n">
+        <v>0.00727</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>TTMI</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2" t="n"/>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0.0801868060725397</v>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>0.008120158060322735</v>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>1.044961139284935</v>
+      </c>
+      <c r="O166" s="2" t="n">
+        <v>0.02015359741088352</v>
+      </c>
+      <c r="P166" s="2" t="n">
+        <v>0.002317890568782084</v>
+      </c>
+      <c r="Q166" s="2" t="n">
+        <v>-0.009370699469749</v>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" s="2" t="n">
+        <v>4.379711487304755</v>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>-0.004529061564925829</v>
+      </c>
+      <c r="U166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="2" t="n"/>
+      <c r="AB166" s="2" t="n"/>
+      <c r="AC166" s="2" t="n"/>
+      <c r="AD166" s="2" t="n"/>
+      <c r="AE166" s="2" t="n"/>
+      <c r="AF166" s="2" t="n"/>
+      <c r="AG166" s="2" t="n"/>
+      <c r="AH166" s="2" t="n"/>
+      <c r="AI166" s="2" t="n"/>
+      <c r="AJ166" s="2" t="n"/>
+      <c r="AK166" s="2" t="n"/>
+      <c r="AL166" s="2" t="n"/>
+      <c r="AM166" s="2" t="n"/>
+      <c r="AN166" s="2" t="n"/>
+      <c r="AO166" s="2" t="n"/>
+      <c r="AP166" s="2" t="n"/>
+      <c r="AQ166" s="2" t="n"/>
+      <c r="AR166" s="2" t="n"/>
+      <c r="AS166" s="2" t="n"/>
+      <c r="AT166" s="2" t="n"/>
+      <c r="AU166" s="2" t="n"/>
+      <c r="AV166" s="2" t="n"/>
+      <c r="AW166" s="2" t="n"/>
+      <c r="AX166" s="2" t="n"/>
+      <c r="AY166" s="2" t="n"/>
+      <c r="AZ166" s="2" t="n"/>
+      <c r="BA166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n"/>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0.213043486824108</v>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>0.01739128812274293</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>1.16443461098486</v>
+      </c>
+      <c r="O167" s="2" t="n">
+        <v>0.09183110039668807</v>
+      </c>
+      <c r="P167" s="2" t="n">
+        <v>0.03225805128443519</v>
+      </c>
+      <c r="Q167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="2" t="n">
+        <v>0.3328944016005788</v>
+      </c>
+      <c r="T167" s="2" t="n">
+        <v>-0.004529061564925829</v>
+      </c>
+      <c r="U167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" s="2" t="n"/>
+      <c r="AB167" s="2" t="n"/>
+      <c r="AC167" s="2" t="n"/>
+      <c r="AD167" s="2" t="n"/>
+      <c r="AE167" s="2" t="n"/>
+      <c r="AF167" s="2" t="n"/>
+      <c r="AG167" s="2" t="n"/>
+      <c r="AH167" s="2" t="n"/>
+      <c r="AI167" s="2" t="n"/>
+      <c r="AJ167" s="2" t="n"/>
+      <c r="AK167" s="2" t="n"/>
+      <c r="AL167" s="2" t="n"/>
+      <c r="AM167" s="2" t="n"/>
+      <c r="AN167" s="2" t="n"/>
+      <c r="AO167" s="2" t="n"/>
+      <c r="AP167" s="2" t="n"/>
+      <c r="AQ167" s="2" t="n"/>
+      <c r="AR167" s="2" t="n"/>
+      <c r="AS167" s="2" t="n"/>
+      <c r="AT167" s="2" t="n"/>
+      <c r="AU167" s="2" t="n"/>
+      <c r="AV167" s="2" t="n"/>
+      <c r="AW167" s="2" t="n"/>
+      <c r="AX167" s="2" t="n"/>
+      <c r="AY167" s="2" t="n"/>
+      <c r="AZ167" s="2" t="n"/>
+      <c r="BA167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0.08737201560701546</v>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>-0.0009101459575189264</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>0.822706145499829</v>
+      </c>
+      <c r="O168" s="2" t="n">
+        <v>0.01496316907453954</v>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>0.007742224491297841</v>
+      </c>
+      <c r="Q168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" s="2" t="n">
+        <v>3.866816431747366</v>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>-0.004529061564925829</v>
+      </c>
+      <c r="U168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA168" s="2" t="n"/>
+      <c r="AB168" s="2" t="n"/>
+      <c r="AC168" s="2" t="n"/>
+      <c r="AD168" s="2" t="n"/>
+      <c r="AE168" s="2" t="n"/>
+      <c r="AF168" s="2" t="n"/>
+      <c r="AG168" s="2" t="n"/>
+      <c r="AH168" s="2" t="n"/>
+      <c r="AI168" s="2" t="n"/>
+      <c r="AJ168" s="2" t="n"/>
+      <c r="AK168" s="2" t="n"/>
+      <c r="AL168" s="2" t="n"/>
+      <c r="AM168" s="2" t="n"/>
+      <c r="AN168" s="2" t="n"/>
+      <c r="AO168" s="2" t="n"/>
+      <c r="AP168" s="2" t="n"/>
+      <c r="AQ168" s="2" t="n"/>
+      <c r="AR168" s="2" t="n"/>
+      <c r="AS168" s="2" t="n"/>
+      <c r="AT168" s="2" t="n"/>
+      <c r="AU168" s="2" t="n"/>
+      <c r="AV168" s="2" t="n"/>
+      <c r="AW168" s="2" t="n"/>
+      <c r="AX168" s="2" t="n"/>
+      <c r="AY168" s="2" t="n"/>
+      <c r="AZ168" s="2" t="n"/>
+      <c r="BA168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BORR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0.08210785402237852</v>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>0.01470586860331125</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>0.8532158892735024</v>
+      </c>
+      <c r="O169" s="2" t="n">
+        <v>0.01733733414636074</v>
+      </c>
+      <c r="P169" s="2" t="n">
+        <v>0.007927511246984825</v>
+      </c>
+      <c r="Q169" s="2" t="n">
+        <v>-0.00897866723637375</v>
+      </c>
+      <c r="R169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" s="2" t="n">
+        <v>1.485007825415612</v>
+      </c>
+      <c r="T169" s="2" t="n">
+        <v>-0.004529061564925829</v>
+      </c>
+      <c r="U169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" s="2" t="n"/>
+      <c r="AB169" s="2" t="n"/>
+      <c r="AC169" s="2" t="n"/>
+      <c r="AD169" s="2" t="n"/>
+      <c r="AE169" s="2" t="n"/>
+      <c r="AF169" s="2" t="n"/>
+      <c r="AG169" s="2" t="n"/>
+      <c r="AH169" s="2" t="n"/>
+      <c r="AI169" s="2" t="n"/>
+      <c r="AJ169" s="2" t="n"/>
+      <c r="AK169" s="2" t="n"/>
+      <c r="AL169" s="2" t="n"/>
+      <c r="AM169" s="2" t="n"/>
+      <c r="AN169" s="2" t="n"/>
+      <c r="AO169" s="2" t="n"/>
+      <c r="AP169" s="2" t="n"/>
+      <c r="AQ169" s="2" t="n"/>
+      <c r="AR169" s="2" t="n"/>
+      <c r="AS169" s="2" t="n"/>
+      <c r="AT169" s="2" t="n"/>
+      <c r="AU169" s="2" t="n"/>
+      <c r="AV169" s="2" t="n"/>
+      <c r="AW169" s="2" t="n"/>
+      <c r="AX169" s="2" t="n"/>
+      <c r="AY169" s="2" t="n"/>
+      <c r="AZ169" s="2" t="n"/>
+      <c r="BA169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>RHI</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="n"/>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0.2292993450019063</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>0.1279193114592978</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>2.067759785635806</v>
+      </c>
+      <c r="O170" s="2" t="n">
+        <v>0.02404080377456785</v>
+      </c>
+      <c r="P170" s="2" t="n">
+        <v>0.009930908848335324</v>
+      </c>
+      <c r="Q170" s="2" t="n">
+        <v>-0.009087660395259656</v>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" s="2" t="n">
+        <v>3.835573826676316</v>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>-0.004646903929551471</v>
+      </c>
+      <c r="U170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" s="2" t="n"/>
+      <c r="AB170" s="2" t="n"/>
+      <c r="AC170" s="2" t="n"/>
+      <c r="AD170" s="2" t="n"/>
+      <c r="AE170" s="2" t="n"/>
+      <c r="AF170" s="2" t="n"/>
+      <c r="AG170" s="2" t="n"/>
+      <c r="AH170" s="2" t="n"/>
+      <c r="AI170" s="2" t="n"/>
+      <c r="AJ170" s="2" t="n"/>
+      <c r="AK170" s="2" t="n"/>
+      <c r="AL170" s="2" t="n"/>
+      <c r="AM170" s="2" t="n"/>
+      <c r="AN170" s="2" t="n"/>
+      <c r="AO170" s="2" t="n"/>
+      <c r="AP170" s="2" t="n"/>
+      <c r="AQ170" s="2" t="n"/>
+      <c r="AR170" s="2" t="n"/>
+      <c r="AS170" s="2" t="n"/>
+      <c r="AT170" s="2" t="n"/>
+      <c r="AU170" s="2" t="n"/>
+      <c r="AV170" s="2" t="n"/>
+      <c r="AW170" s="2" t="n"/>
+      <c r="AX170" s="2" t="n"/>
+      <c r="AY170" s="2" t="n"/>
+      <c r="AZ170" s="2" t="n"/>
+      <c r="BA170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:34:00-04:00</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n"/>
+      <c r="I171" s="2" t="n"/>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0.07811053832056647</v>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>0.05184329417555511</v>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>1.048981272888149</v>
+      </c>
+      <c r="O171" s="2" t="n">
+        <v>0.01000093500521593</v>
+      </c>
+      <c r="P171" s="2" t="n">
+        <v>0.01047230217066391</v>
+      </c>
+      <c r="Q171" s="2" t="n">
+        <v>-0.008161167414562298</v>
+      </c>
+      <c r="R171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" s="2" t="n">
+        <v>2.236231571246732</v>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>-0.004686131455674425</v>
+      </c>
+      <c r="U171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" s="2" t="n"/>
+      <c r="AB171" s="2" t="n"/>
+      <c r="AC171" s="2" t="n"/>
+      <c r="AD171" s="2" t="n"/>
+      <c r="AE171" s="2" t="n"/>
+      <c r="AF171" s="2" t="n"/>
+      <c r="AG171" s="2" t="n"/>
+      <c r="AH171" s="2" t="n"/>
+      <c r="AI171" s="2" t="n"/>
+      <c r="AJ171" s="2" t="n"/>
+      <c r="AK171" s="2" t="n"/>
+      <c r="AL171" s="2" t="n"/>
+      <c r="AM171" s="2" t="n"/>
+      <c r="AN171" s="2" t="n"/>
+      <c r="AO171" s="2" t="n"/>
+      <c r="AP171" s="2" t="n"/>
+      <c r="AQ171" s="2" t="n"/>
+      <c r="AR171" s="2" t="n"/>
+      <c r="AS171" s="2" t="n"/>
+      <c r="AT171" s="2" t="n"/>
+      <c r="AU171" s="2" t="n"/>
+      <c r="AV171" s="2" t="n"/>
+      <c r="AW171" s="2" t="n"/>
+      <c r="AX171" s="2" t="n"/>
+      <c r="AY171" s="2" t="n"/>
+      <c r="AZ171" s="2" t="n"/>
+      <c r="BA171" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23505,7 +31760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24797,6 +33052,242 @@
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>RITM</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>75.87</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-10.39</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>hod_break</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>UWMC</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>HSAI</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
         </is>
       </c>
     </row>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3269,6 +3269,311 @@
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>15-min ORB: closed above 15-min high 13.18, above VWAP | news: [Newswire] Hesai Group to Report Third Quarter 2026 Financia</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>EAF</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bull flag: 3.2% pole, 1.0% flag on light vol, broke 10.16 | news: [Google News] Where GrafTech International Goes After A 50% </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>-9.42</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15-min ORB: closed above 15-min high 91.12, above VWAP | news: [Benzinga] Corcept Therapeutics Announces Results From Part </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>MLCO</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>15-min ORB: closed above 15-min high 3.94, above VWAP | news: [Google News] EPrivateClient - Jersey makes changes to relia</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>BWMX</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>5-min ORB: green first 5 min, closed above range high 16.90 | news: [Google News] Betterware de México, S.A.P.I. de C.V. Just Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>53.02</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>Premarket-high break: closed above PM high 52.78, above VWAP | news: [Benzinga] EQT, Range Resources Mega-Merger Set to Create US</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA171"/>
+  <dimension ref="A1:BA193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31101,8 +31406,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="n"/>
+      <c r="H166" s="2" t="n">
+        <v>-1.364</v>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -31156,33 +31467,87 @@
       <c r="Z166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA166" s="2" t="n"/>
-      <c r="AB166" s="2" t="n"/>
-      <c r="AC166" s="2" t="n"/>
-      <c r="AD166" s="2" t="n"/>
-      <c r="AE166" s="2" t="n"/>
-      <c r="AF166" s="2" t="n"/>
-      <c r="AG166" s="2" t="n"/>
-      <c r="AH166" s="2" t="n"/>
-      <c r="AI166" s="2" t="n"/>
-      <c r="AJ166" s="2" t="n"/>
-      <c r="AK166" s="2" t="n"/>
-      <c r="AL166" s="2" t="n"/>
-      <c r="AM166" s="2" t="n"/>
-      <c r="AN166" s="2" t="n"/>
-      <c r="AO166" s="2" t="n"/>
-      <c r="AP166" s="2" t="n"/>
-      <c r="AQ166" s="2" t="n"/>
-      <c r="AR166" s="2" t="n"/>
-      <c r="AS166" s="2" t="n"/>
-      <c r="AT166" s="2" t="n"/>
-      <c r="AU166" s="2" t="n"/>
-      <c r="AV166" s="2" t="n"/>
-      <c r="AW166" s="2" t="n"/>
-      <c r="AX166" s="2" t="n"/>
-      <c r="AY166" s="2" t="n"/>
-      <c r="AZ166" s="2" t="n"/>
-      <c r="BA166" s="2" t="n"/>
+      <c r="AA166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE166" s="2" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="AF166" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AG166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI166" s="2" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="AJ166" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AK166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM166" s="2" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="AN166" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AO166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ166" s="2" t="n">
+        <v>79.815</v>
+      </c>
+      <c r="AR166" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AS166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU166" s="2" t="n">
+        <v>79.815</v>
+      </c>
+      <c r="AV166" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AW166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY166" s="2" t="n">
+        <v>79.815</v>
+      </c>
+      <c r="AZ166" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="BA166" s="2" t="n">
+        <v>0.00063</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -31214,8 +31579,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H167" s="2" t="n"/>
-      <c r="I167" s="2" t="n"/>
+      <c r="H167" s="2" t="n">
+        <v>-0.138</v>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -31269,33 +31640,87 @@
       <c r="Z167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA167" s="2" t="n"/>
-      <c r="AB167" s="2" t="n"/>
-      <c r="AC167" s="2" t="n"/>
-      <c r="AD167" s="2" t="n"/>
-      <c r="AE167" s="2" t="n"/>
-      <c r="AF167" s="2" t="n"/>
-      <c r="AG167" s="2" t="n"/>
-      <c r="AH167" s="2" t="n"/>
-      <c r="AI167" s="2" t="n"/>
-      <c r="AJ167" s="2" t="n"/>
-      <c r="AK167" s="2" t="n"/>
-      <c r="AL167" s="2" t="n"/>
-      <c r="AM167" s="2" t="n"/>
-      <c r="AN167" s="2" t="n"/>
-      <c r="AO167" s="2" t="n"/>
-      <c r="AP167" s="2" t="n"/>
-      <c r="AQ167" s="2" t="n"/>
-      <c r="AR167" s="2" t="n"/>
-      <c r="AS167" s="2" t="n"/>
-      <c r="AT167" s="2" t="n"/>
-      <c r="AU167" s="2" t="n"/>
-      <c r="AV167" s="2" t="n"/>
-      <c r="AW167" s="2" t="n"/>
-      <c r="AX167" s="2" t="n"/>
-      <c r="AY167" s="2" t="n"/>
-      <c r="AZ167" s="2" t="n"/>
-      <c r="BA167" s="2" t="n"/>
+      <c r="AA167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" s="2" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="AD167" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE167" s="2" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="AF167" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AG167" s="2" t="n">
+        <v>0.6889</v>
+      </c>
+      <c r="AH167" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI167" s="2" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="AJ167" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AK167" s="2" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="AL167" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM167" s="2" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="AN167" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AO167" s="2" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="AP167" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ167" s="2" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="AR167" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AS167" s="2" t="n">
+        <v>0.6889</v>
+      </c>
+      <c r="AT167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU167" s="2" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="AV167" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AW167" s="2" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="AX167" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY167" s="2" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="AZ167" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BA167" s="2" t="n">
+        <v>0.00717</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -31327,8 +31752,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
+      <c r="H168" s="2" t="n">
+        <v>-2.024</v>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -31382,33 +31813,87 @@
       <c r="Z168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA168" s="2" t="n"/>
-      <c r="AB168" s="2" t="n"/>
-      <c r="AC168" s="2" t="n"/>
-      <c r="AD168" s="2" t="n"/>
-      <c r="AE168" s="2" t="n"/>
-      <c r="AF168" s="2" t="n"/>
-      <c r="AG168" s="2" t="n"/>
-      <c r="AH168" s="2" t="n"/>
-      <c r="AI168" s="2" t="n"/>
-      <c r="AJ168" s="2" t="n"/>
-      <c r="AK168" s="2" t="n"/>
-      <c r="AL168" s="2" t="n"/>
-      <c r="AM168" s="2" t="n"/>
-      <c r="AN168" s="2" t="n"/>
-      <c r="AO168" s="2" t="n"/>
-      <c r="AP168" s="2" t="n"/>
-      <c r="AQ168" s="2" t="n"/>
-      <c r="AR168" s="2" t="n"/>
-      <c r="AS168" s="2" t="n"/>
-      <c r="AT168" s="2" t="n"/>
-      <c r="AU168" s="2" t="n"/>
-      <c r="AV168" s="2" t="n"/>
-      <c r="AW168" s="2" t="n"/>
-      <c r="AX168" s="2" t="n"/>
-      <c r="AY168" s="2" t="n"/>
-      <c r="AZ168" s="2" t="n"/>
-      <c r="BA168" s="2" t="n"/>
+      <c r="AA168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" s="2" t="n">
+        <v>-2.0286</v>
+      </c>
+      <c r="AD168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE168" s="2" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="AF168" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AG168" s="2" t="n">
+        <v>-2.0286</v>
+      </c>
+      <c r="AH168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI168" s="2" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="AJ168" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK168" s="2" t="n">
+        <v>-2.0286</v>
+      </c>
+      <c r="AL168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM168" s="2" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="AN168" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AO168" s="2" t="n">
+        <v>-2.0588</v>
+      </c>
+      <c r="AP168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ168" s="2" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="AR168" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS168" s="2" t="n">
+        <v>-2.0588</v>
+      </c>
+      <c r="AT168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU168" s="2" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="AV168" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AW168" s="2" t="n">
+        <v>-2.0588</v>
+      </c>
+      <c r="AX168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY168" s="2" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="AZ168" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BA168" s="2" t="n">
+        <v>0.00105</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -31440,8 +31925,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H169" s="2" t="n"/>
-      <c r="I169" s="2" t="n"/>
+      <c r="H169" s="2" t="n">
+        <v>-10.089</v>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -31495,33 +31986,87 @@
       <c r="Z169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA169" s="2" t="n"/>
-      <c r="AB169" s="2" t="n"/>
-      <c r="AC169" s="2" t="n"/>
-      <c r="AD169" s="2" t="n"/>
-      <c r="AE169" s="2" t="n"/>
-      <c r="AF169" s="2" t="n"/>
-      <c r="AG169" s="2" t="n"/>
-      <c r="AH169" s="2" t="n"/>
-      <c r="AI169" s="2" t="n"/>
-      <c r="AJ169" s="2" t="n"/>
-      <c r="AK169" s="2" t="n"/>
-      <c r="AL169" s="2" t="n"/>
-      <c r="AM169" s="2" t="n"/>
-      <c r="AN169" s="2" t="n"/>
-      <c r="AO169" s="2" t="n"/>
-      <c r="AP169" s="2" t="n"/>
-      <c r="AQ169" s="2" t="n"/>
-      <c r="AR169" s="2" t="n"/>
-      <c r="AS169" s="2" t="n"/>
-      <c r="AT169" s="2" t="n"/>
-      <c r="AU169" s="2" t="n"/>
-      <c r="AV169" s="2" t="n"/>
-      <c r="AW169" s="2" t="n"/>
-      <c r="AX169" s="2" t="n"/>
-      <c r="AY169" s="2" t="n"/>
-      <c r="AZ169" s="2" t="n"/>
-      <c r="BA169" s="2" t="n"/>
+      <c r="AA169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" s="2" t="n">
+        <v>-14.7114</v>
+      </c>
+      <c r="AD169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE169" s="2" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AF169" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG169" s="2" t="n">
+        <v>-14.7114</v>
+      </c>
+      <c r="AH169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI169" s="2" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AJ169" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AK169" s="2" t="n">
+        <v>-14.7114</v>
+      </c>
+      <c r="AL169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM169" s="2" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AN169" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AO169" s="2" t="n">
+        <v>-14.7114</v>
+      </c>
+      <c r="AP169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ169" s="2" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AR169" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AS169" s="2" t="n">
+        <v>-14.7114</v>
+      </c>
+      <c r="AT169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU169" s="2" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AV169" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AW169" s="2" t="n">
+        <v>-14.7114</v>
+      </c>
+      <c r="AX169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY169" s="2" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AZ169" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA169" s="2" t="n">
+        <v>0.00227</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -31553,8 +32098,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H170" s="2" t="n"/>
-      <c r="I170" s="2" t="n"/>
+      <c r="H170" s="2" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -31608,33 +32159,87 @@
       <c r="Z170" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA170" s="2" t="n"/>
-      <c r="AB170" s="2" t="n"/>
-      <c r="AC170" s="2" t="n"/>
-      <c r="AD170" s="2" t="n"/>
-      <c r="AE170" s="2" t="n"/>
-      <c r="AF170" s="2" t="n"/>
-      <c r="AG170" s="2" t="n"/>
-      <c r="AH170" s="2" t="n"/>
-      <c r="AI170" s="2" t="n"/>
-      <c r="AJ170" s="2" t="n"/>
-      <c r="AK170" s="2" t="n"/>
-      <c r="AL170" s="2" t="n"/>
-      <c r="AM170" s="2" t="n"/>
-      <c r="AN170" s="2" t="n"/>
-      <c r="AO170" s="2" t="n"/>
-      <c r="AP170" s="2" t="n"/>
-      <c r="AQ170" s="2" t="n"/>
-      <c r="AR170" s="2" t="n"/>
-      <c r="AS170" s="2" t="n"/>
-      <c r="AT170" s="2" t="n"/>
-      <c r="AU170" s="2" t="n"/>
-      <c r="AV170" s="2" t="n"/>
-      <c r="AW170" s="2" t="n"/>
-      <c r="AX170" s="2" t="n"/>
-      <c r="AY170" s="2" t="n"/>
-      <c r="AZ170" s="2" t="n"/>
-      <c r="BA170" s="2" t="n"/>
+      <c r="AA170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD170" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE170" s="2" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AF170" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AG170" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI170" s="2" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AJ170" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AK170" s="2" t="n">
+        <v>0.8022</v>
+      </c>
+      <c r="AL170" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM170" s="2" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AN170" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AO170" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP170" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ170" s="2" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AR170" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AS170" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU170" s="2" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AV170" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AW170" s="2" t="n">
+        <v>0.8022</v>
+      </c>
+      <c r="AX170" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY170" s="2" t="n">
+        <v>46.315</v>
+      </c>
+      <c r="AZ170" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="BA170" s="2" t="n">
+        <v>0.00108</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -31666,8 +32271,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H171" s="2" t="n"/>
-      <c r="I171" s="2" t="n"/>
+      <c r="H171" s="2" t="n">
+        <v>-0.826</v>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -31721,33 +32332,3607 @@
       <c r="Z171" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA171" s="2" t="n"/>
-      <c r="AB171" s="2" t="n"/>
-      <c r="AC171" s="2" t="n"/>
-      <c r="AD171" s="2" t="n"/>
-      <c r="AE171" s="2" t="n"/>
-      <c r="AF171" s="2" t="n"/>
-      <c r="AG171" s="2" t="n"/>
-      <c r="AH171" s="2" t="n"/>
-      <c r="AI171" s="2" t="n"/>
-      <c r="AJ171" s="2" t="n"/>
-      <c r="AK171" s="2" t="n"/>
-      <c r="AL171" s="2" t="n"/>
-      <c r="AM171" s="2" t="n"/>
-      <c r="AN171" s="2" t="n"/>
-      <c r="AO171" s="2" t="n"/>
-      <c r="AP171" s="2" t="n"/>
-      <c r="AQ171" s="2" t="n"/>
-      <c r="AR171" s="2" t="n"/>
-      <c r="AS171" s="2" t="n"/>
-      <c r="AT171" s="2" t="n"/>
-      <c r="AU171" s="2" t="n"/>
-      <c r="AV171" s="2" t="n"/>
-      <c r="AW171" s="2" t="n"/>
-      <c r="AX171" s="2" t="n"/>
-      <c r="AY171" s="2" t="n"/>
-      <c r="AZ171" s="2" t="n"/>
-      <c r="BA171" s="2" t="n"/>
+      <c r="AA171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" s="2" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="AD171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE171" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="AF171" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AG171" s="2" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="AH171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI171" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="AJ171" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AK171" s="2" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="AL171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM171" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="AN171" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AO171" s="2" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="AP171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ171" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="AR171" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AS171" s="2" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="AT171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU171" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="AV171" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AW171" s="2" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="AX171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY171" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="AZ171" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="BA171" s="2" t="n">
+        <v>0.00107</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:47:00-04:00</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>-1.043</v>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0.0620195307522533</v>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>0.002795223178004402</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>1.645299068053378</v>
+      </c>
+      <c r="O172" s="2" t="n">
+        <v>0.02000658251783816</v>
+      </c>
+      <c r="P172" s="2" t="n">
+        <v>0.02878760354088921</v>
+      </c>
+      <c r="Q172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" s="2" t="n">
+        <v>4.512890383094586</v>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>0.003921262179805707</v>
+      </c>
+      <c r="U172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE172" s="2" t="n">
+        <v>91.435</v>
+      </c>
+      <c r="AF172" s="2" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AG172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI172" s="2" t="n">
+        <v>91.435</v>
+      </c>
+      <c r="AJ172" s="2" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AK172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM172" s="2" t="n">
+        <v>91.435</v>
+      </c>
+      <c r="AN172" s="2" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AO172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ172" s="2" t="n">
+        <v>91.185</v>
+      </c>
+      <c r="AR172" s="2" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AS172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU172" s="2" t="n">
+        <v>91.185</v>
+      </c>
+      <c r="AV172" s="2" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AW172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY172" s="2" t="n">
+        <v>91.185</v>
+      </c>
+      <c r="AZ172" s="2" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="BA172" s="2" t="n">
+        <v>0.00691</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0.1614674516741468</v>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>3.463741271091359</v>
+      </c>
+      <c r="O173" s="2" t="n">
+        <v>0.02214554056517049</v>
+      </c>
+      <c r="P173" s="2" t="n">
+        <v>0.03007374624564008</v>
+      </c>
+      <c r="Q173" s="2" t="n">
+        <v>-0.0005482018481800521</v>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" s="2" t="n">
+        <v>3.967836050044687</v>
+      </c>
+      <c r="T173" s="2" t="n">
+        <v>0.004135054292916829</v>
+      </c>
+      <c r="U173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC173" s="2" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AD173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE173" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AF173" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG173" s="2" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AH173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI173" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AJ173" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AK173" s="2" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AL173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM173" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AN173" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO173" s="2" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AP173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ173" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AR173" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS173" s="2" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AT173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU173" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AV173" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AW173" s="2" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AX173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY173" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AZ173" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BA173" s="2" t="n">
+        <v>0.00076</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0.1614674516741468</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>3.463741271091359</v>
+      </c>
+      <c r="O174" s="2" t="n">
+        <v>0.02214554056517049</v>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>0.02780402802312603</v>
+      </c>
+      <c r="Q174" s="2" t="n">
+        <v>-0.0005482018481800521</v>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" s="2" t="n">
+        <v>3.967836050044687</v>
+      </c>
+      <c r="T174" s="2" t="n">
+        <v>0.004135054292916829</v>
+      </c>
+      <c r="U174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC174" s="2" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AD174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE174" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AF174" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG174" s="2" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AH174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI174" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AJ174" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK174" s="2" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AL174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM174" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AN174" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO174" s="2" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AP174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ174" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AR174" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS174" s="2" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AT174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU174" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AV174" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AW174" s="2" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AX174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY174" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AZ174" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA174" s="2" t="n">
+        <v>0.00076</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0.1614674516741468</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>3.463741271091359</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>0.02214554056517049</v>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>0.02345373476330725</v>
+      </c>
+      <c r="Q175" s="2" t="n">
+        <v>-0.0005482018481800521</v>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" s="2" t="n">
+        <v>3.967836050044687</v>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>0.004135054292916829</v>
+      </c>
+      <c r="U175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="2" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AD175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE175" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AF175" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AG175" s="2" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AH175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI175" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AJ175" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK175" s="2" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AL175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM175" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AN175" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO175" s="2" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AP175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ175" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AR175" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS175" s="2" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AT175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU175" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AV175" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AW175" s="2" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AX175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY175" s="2" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AZ175" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA175" s="2" t="n">
+        <v>0.00076</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>BWMX</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:52:00-04:00</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>-0.639</v>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0.08659399411523605</v>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>0.06542658420656622</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>2.682873388415721</v>
+      </c>
+      <c r="O176" s="2" t="n">
+        <v>0.01399564768118866</v>
+      </c>
+      <c r="P176" s="2" t="n">
+        <v>0.03010628795626476</v>
+      </c>
+      <c r="Q176" s="2" t="n">
+        <v>-0.007615651030504655</v>
+      </c>
+      <c r="R176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" s="2" t="n">
+        <v>2.829677720750332</v>
+      </c>
+      <c r="T176" s="2" t="n">
+        <v>0.004842367268186543</v>
+      </c>
+      <c r="U176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD176" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE176" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AF176" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AG176" s="2" t="n">
+        <v>-0.5784</v>
+      </c>
+      <c r="AH176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI176" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AJ176" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AK176" s="2" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="AL176" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM176" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AN176" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AO176" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP176" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ176" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AR176" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AS176" s="2" t="n">
+        <v>-0.5784</v>
+      </c>
+      <c r="AT176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU176" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AV176" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AW176" s="2" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="AX176" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY176" s="2" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AZ176" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BA176" s="2" t="n">
+        <v>0.01353</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>MLCO</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:54:00-04:00</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>-0.829</v>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0.05898124061266796</v>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>0.01072385030790524</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>1.416064361519773</v>
+      </c>
+      <c r="O177" s="2" t="n">
+        <v>0.02066411134925517</v>
+      </c>
+      <c r="P177" s="2" t="n">
+        <v>0.02784811300147201</v>
+      </c>
+      <c r="Q177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" s="2" t="n">
+        <v>1.373715590984857</v>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>0.005131813840557609</v>
+      </c>
+      <c r="U177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC177" s="2" t="n">
+        <v>-0.6443</v>
+      </c>
+      <c r="AD177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE177" s="2" t="n">
+        <v>3.9665</v>
+      </c>
+      <c r="AF177" s="2" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="AG177" s="2" t="n">
+        <v>-0.6443</v>
+      </c>
+      <c r="AH177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI177" s="2" t="n">
+        <v>3.9665</v>
+      </c>
+      <c r="AJ177" s="2" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="AK177" s="2" t="n">
+        <v>-0.6443</v>
+      </c>
+      <c r="AL177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM177" s="2" t="n">
+        <v>3.9665</v>
+      </c>
+      <c r="AN177" s="2" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="AO177" s="2" t="n">
+        <v>-0.5755</v>
+      </c>
+      <c r="AP177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ177" s="2" t="n">
+        <v>3.946</v>
+      </c>
+      <c r="AR177" s="2" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AS177" s="2" t="n">
+        <v>-0.5755</v>
+      </c>
+      <c r="AT177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU177" s="2" t="n">
+        <v>3.946</v>
+      </c>
+      <c r="AV177" s="2" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AW177" s="2" t="n">
+        <v>-0.5755</v>
+      </c>
+      <c r="AX177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY177" s="2" t="n">
+        <v>3.946</v>
+      </c>
+      <c r="AZ177" s="2" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="BA177" s="2" t="n">
+        <v>0.00252</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>BWMX</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:55:00-04:00</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>-1.071</v>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0.09653618640387096</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>0.06542658420656622</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>2.604121511266614</v>
+      </c>
+      <c r="O178" s="2" t="n">
+        <v>0.02292279163854838</v>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>0.02427606493264366</v>
+      </c>
+      <c r="Q178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" s="2" t="n">
+        <v>2.838785982924811</v>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>0.005592326228453404</v>
+      </c>
+      <c r="U178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE178" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="AF178" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI178" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="AJ178" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AK178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM178" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="AN178" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AO178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ178" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="AR178" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AS178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU178" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="AV178" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AW178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY178" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="AZ178" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BA178" s="2" t="n">
+        <v>0.00586</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:59:00-04:00</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0.1680579445134187</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>3.326273929797391</v>
+      </c>
+      <c r="O179" s="2" t="n">
+        <v>0.02384568736697346</v>
+      </c>
+      <c r="P179" s="2" t="n">
+        <v>0.01335336079360627</v>
+      </c>
+      <c r="Q179" s="2" t="n">
+        <v>-0.0007517556138996184</v>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" s="2" t="n">
+        <v>3.973494293078506</v>
+      </c>
+      <c r="T179" s="2" t="n">
+        <v>0.003789629845700304</v>
+      </c>
+      <c r="U179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE179" s="2" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="AF179" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AG179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI179" s="2" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="AJ179" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AK179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM179" s="2" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="AN179" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AO179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ179" s="2" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="AR179" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AS179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU179" s="2" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="AV179" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AW179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY179" s="2" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="AZ179" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BA179" s="2" t="n">
+        <v>0.00056</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0.1705843433998488</v>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>3.303193779805128</v>
+      </c>
+      <c r="O180" s="2" t="n">
+        <v>0.0258179085421042</v>
+      </c>
+      <c r="P180" s="2" t="n">
+        <v>0.02467861220189111</v>
+      </c>
+      <c r="Q180" s="2" t="n">
+        <v>-9.384627564867909e-05</v>
+      </c>
+      <c r="R180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" s="2" t="n">
+        <v>3.975654862809301</v>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>0.004842367268186543</v>
+      </c>
+      <c r="U180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="2" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AD180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE180" s="2" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AF180" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG180" s="2" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AH180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI180" s="2" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AJ180" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK180" s="2" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AL180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM180" s="2" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AN180" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO180" s="2" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="AP180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ180" s="2" t="n">
+        <v>53.285</v>
+      </c>
+      <c r="AR180" s="2" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AS180" s="2" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="AT180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU180" s="2" t="n">
+        <v>53.285</v>
+      </c>
+      <c r="AV180" s="2" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AW180" s="2" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="AX180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY180" s="2" t="n">
+        <v>53.285</v>
+      </c>
+      <c r="AZ180" s="2" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="BA180" s="2" t="n">
+        <v>0.00056</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>90.06999999999999</v>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:04:00-04:00</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0.05095504273118467</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>0.002795223178004402</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>1.55359037437974</v>
+      </c>
+      <c r="O181" s="2" t="n">
+        <v>0.002227835160107716</v>
+      </c>
+      <c r="P181" s="2" t="n">
+        <v>0.001828565514883377</v>
+      </c>
+      <c r="Q181" s="2" t="n">
+        <v>-0.01624418521184179</v>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" s="2" t="n">
+        <v>4.502417385177284</v>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>0.004987090554372076</v>
+      </c>
+      <c r="U181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="2" t="n"/>
+      <c r="AD181" s="2" t="n"/>
+      <c r="AE181" s="2" t="n"/>
+      <c r="AF181" s="2" t="n"/>
+      <c r="AG181" s="2" t="n"/>
+      <c r="AH181" s="2" t="n"/>
+      <c r="AI181" s="2" t="n"/>
+      <c r="AJ181" s="2" t="n"/>
+      <c r="AK181" s="2" t="n"/>
+      <c r="AL181" s="2" t="n"/>
+      <c r="AM181" s="2" t="n"/>
+      <c r="AN181" s="2" t="n"/>
+      <c r="AO181" s="2" t="n"/>
+      <c r="AP181" s="2" t="n"/>
+      <c r="AQ181" s="2" t="n"/>
+      <c r="AR181" s="2" t="n"/>
+      <c r="AS181" s="2" t="n"/>
+      <c r="AT181" s="2" t="n"/>
+      <c r="AU181" s="2" t="n"/>
+      <c r="AV181" s="2" t="n"/>
+      <c r="AW181" s="2" t="n"/>
+      <c r="AX181" s="2" t="n"/>
+      <c r="AY181" s="2" t="n"/>
+      <c r="AZ181" s="2" t="n"/>
+      <c r="BA181" s="2" t="n">
+        <v>0.00477</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>EAF</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:10:00-04:00</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>-1.144</v>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0.2056404175008981</v>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>0.03407755041754346</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>1.817857295002203</v>
+      </c>
+      <c r="O182" s="2" t="n">
+        <v>0.04825944069406329</v>
+      </c>
+      <c r="P182" s="2" t="n">
+        <v>0.02046785810888054</v>
+      </c>
+      <c r="Q182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" s="2" t="n">
+        <v>2.328252862050794</v>
+      </c>
+      <c r="T182" s="2" t="n">
+        <v>0.005473945471606845</v>
+      </c>
+      <c r="U182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC182" s="2" t="n">
+        <v>-1.0647</v>
+      </c>
+      <c r="AD182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE182" s="2" t="n">
+        <v>10.2665</v>
+      </c>
+      <c r="AF182" s="2" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="AG182" s="2" t="n">
+        <v>-1.0647</v>
+      </c>
+      <c r="AH182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI182" s="2" t="n">
+        <v>10.2665</v>
+      </c>
+      <c r="AJ182" s="2" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="AK182" s="2" t="n">
+        <v>-1.0647</v>
+      </c>
+      <c r="AL182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM182" s="2" t="n">
+        <v>10.2665</v>
+      </c>
+      <c r="AN182" s="2" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="AO182" s="2" t="n"/>
+      <c r="AP182" s="2" t="n"/>
+      <c r="AQ182" s="2" t="n"/>
+      <c r="AR182" s="2" t="n"/>
+      <c r="AS182" s="2" t="n"/>
+      <c r="AT182" s="2" t="n"/>
+      <c r="AU182" s="2" t="n"/>
+      <c r="AV182" s="2" t="n"/>
+      <c r="AW182" s="2" t="n"/>
+      <c r="AX182" s="2" t="n"/>
+      <c r="AY182" s="2" t="n"/>
+      <c r="AZ182" s="2" t="n"/>
+      <c r="BA182" s="2" t="n">
+        <v>0.00489</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:11:00-04:00</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>-1.071</v>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>failed_breakdown</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0.08428031255431723</v>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>0.1178659751621098</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>1.723891825146658</v>
+      </c>
+      <c r="O183" s="2" t="n">
+        <v>0.002908591995585574</v>
+      </c>
+      <c r="P183" s="2" t="n">
+        <v>0.03310331281059654</v>
+      </c>
+      <c r="Q183" s="2" t="n">
+        <v>-0.0300444448207865</v>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" s="2" t="n">
+        <v>2.167830069086014</v>
+      </c>
+      <c r="T183" s="2" t="n">
+        <v>0.005460774206937247</v>
+      </c>
+      <c r="U183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE183" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="AF183" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AG183" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI183" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="AJ183" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AK183" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM183" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="AN183" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AO183" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ183" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="AR183" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AS183" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU183" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="AV183" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AW183" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY183" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="AZ183" s="2" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="BA183" s="2" t="n">
+        <v>0.0046</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:15:00-04:00</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>-1.133</v>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>0.06646969136380299</v>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>-0.01033975950643906</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>0.7201696580534914</v>
+      </c>
+      <c r="O184" s="2" t="n">
+        <v>0.03651768772269892</v>
+      </c>
+      <c r="P184" s="2" t="n">
+        <v>0.01939055322159976</v>
+      </c>
+      <c r="Q184" s="2" t="n">
+        <v>-0.0006920573711997058</v>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" s="2" t="n">
+        <v>1.976854923845406</v>
+      </c>
+      <c r="T184" s="2" t="n">
+        <v>0.006500260052164641</v>
+      </c>
+      <c r="U184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD184" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE184" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AF184" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG184" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH184" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI184" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AJ184" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AK184" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL184" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM184" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AN184" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AO184" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ184" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AR184" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS184" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU184" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AV184" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AW184" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY184" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AZ184" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BA184" s="2" t="n">
+        <v>0.00277</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:17:00-04:00</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>-1.162</v>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="L185" s="2" t="n">
+        <v>0.104185188159343</v>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>0.0331254985771825</v>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>1.149831571205187</v>
+      </c>
+      <c r="O185" s="2" t="n">
+        <v>0.01936109462953683</v>
+      </c>
+      <c r="P185" s="2" t="n">
+        <v>0.01387096774193547</v>
+      </c>
+      <c r="Q185" s="2" t="n">
+        <v>-0.0157168066691008</v>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" s="2" t="n">
+        <v>4.127134385045092</v>
+      </c>
+      <c r="T185" s="2" t="n">
+        <v>0.006724010926367097</v>
+      </c>
+      <c r="U185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC185" s="2" t="n">
+        <v>-1.0646</v>
+      </c>
+      <c r="AD185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE185" s="2" t="n">
+        <v>61.9135</v>
+      </c>
+      <c r="AF185" s="2" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="AG185" s="2" t="n">
+        <v>-1.0646</v>
+      </c>
+      <c r="AH185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI185" s="2" t="n">
+        <v>61.9135</v>
+      </c>
+      <c r="AJ185" s="2" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="AK185" s="2" t="n">
+        <v>-1.0646</v>
+      </c>
+      <c r="AL185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM185" s="2" t="n">
+        <v>61.9135</v>
+      </c>
+      <c r="AN185" s="2" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="AO185" s="2" t="n">
+        <v>-1.0646</v>
+      </c>
+      <c r="AP185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ185" s="2" t="n">
+        <v>61.9135</v>
+      </c>
+      <c r="AR185" s="2" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="AS185" s="2" t="n">
+        <v>-1.0646</v>
+      </c>
+      <c r="AT185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU185" s="2" t="n">
+        <v>61.9135</v>
+      </c>
+      <c r="AV185" s="2" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="AW185" s="2" t="n">
+        <v>-1.0646</v>
+      </c>
+      <c r="AX185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY185" s="2" t="n">
+        <v>61.9135</v>
+      </c>
+      <c r="AZ185" s="2" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="BA185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>ORKA</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>88.95999999999999</v>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:27:00-04:00</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>-1.222</v>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="L186" s="2" t="n">
+        <v>0.120024890006788</v>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>0.02283221205509034</v>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>1.404396649159392</v>
+      </c>
+      <c r="O186" s="2" t="n">
+        <v>0.01355336678127106</v>
+      </c>
+      <c r="P186" s="2" t="n">
+        <v>0.009023021870960206</v>
+      </c>
+      <c r="Q186" s="2" t="n">
+        <v>-0.01976419689669096</v>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" s="2" t="n">
+        <v>4.49725080637377</v>
+      </c>
+      <c r="T186" s="2" t="n">
+        <v>0.006171299685785003</v>
+      </c>
+      <c r="U186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC186" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD186" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE186" s="2" t="n">
+        <v>89.41500000000001</v>
+      </c>
+      <c r="AF186" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AG186" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH186" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI186" s="2" t="n">
+        <v>89.41500000000001</v>
+      </c>
+      <c r="AJ186" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AK186" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL186" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM186" s="2" t="n">
+        <v>89.41500000000001</v>
+      </c>
+      <c r="AN186" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AO186" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ186" s="2" t="n">
+        <v>89.41500000000001</v>
+      </c>
+      <c r="AR186" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AS186" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU186" s="2" t="n">
+        <v>89.41500000000001</v>
+      </c>
+      <c r="AV186" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AW186" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY186" s="2" t="n">
+        <v>89.41500000000001</v>
+      </c>
+      <c r="AZ186" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="BA186" s="2" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:53:00-04:00</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>-1.195</v>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="L187" s="2" t="n">
+        <v>0.1750878985183271</v>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>2.2519033723006</v>
+      </c>
+      <c r="O187" s="2" t="n">
+        <v>0.01757123318532017</v>
+      </c>
+      <c r="P187" s="2" t="n">
+        <v>0.005982457813150838</v>
+      </c>
+      <c r="Q187" s="2" t="n">
+        <v>-0.001493336136142442</v>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" s="2" t="n">
+        <v>3.979494751922235</v>
+      </c>
+      <c r="T187" s="2" t="n">
+        <v>0.006895076741891826</v>
+      </c>
+      <c r="U187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC187" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE187" s="2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AF187" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG187" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI187" s="2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AJ187" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK187" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM187" s="2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AN187" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO187" s="2" t="n"/>
+      <c r="AP187" s="2" t="n"/>
+      <c r="AQ187" s="2" t="n"/>
+      <c r="AR187" s="2" t="n"/>
+      <c r="AS187" s="2" t="n"/>
+      <c r="AT187" s="2" t="n"/>
+      <c r="AU187" s="2" t="n"/>
+      <c r="AV187" s="2" t="n"/>
+      <c r="AW187" s="2" t="n"/>
+      <c r="AX187" s="2" t="n"/>
+      <c r="AY187" s="2" t="n"/>
+      <c r="AZ187" s="2" t="n"/>
+      <c r="BA187" s="2" t="n">
+        <v>0.00019</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:53:00-04:00</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="L188" s="2" t="n">
+        <v>0.4726983933221727</v>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>0.4622222658187625</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>3.638482627395722</v>
+      </c>
+      <c r="O188" s="2" t="n">
+        <v>0.006791416851420262</v>
+      </c>
+      <c r="P188" s="2" t="n">
+        <v>0.005820206794585307</v>
+      </c>
+      <c r="Q188" s="2" t="n">
+        <v>-0.003646918750202732</v>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" s="2" t="n">
+        <v>3.143936725046743</v>
+      </c>
+      <c r="T188" s="2" t="n">
+        <v>0.006895076741891826</v>
+      </c>
+      <c r="U188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" s="2" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="AD188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE188" s="2" t="n">
+        <v>23.195</v>
+      </c>
+      <c r="AF188" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AG188" s="2" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="AH188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI188" s="2" t="n">
+        <v>23.195</v>
+      </c>
+      <c r="AJ188" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AK188" s="2" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="AL188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM188" s="2" t="n">
+        <v>23.195</v>
+      </c>
+      <c r="AN188" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AO188" s="2" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="AP188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ188" s="2" t="n">
+        <v>23.195</v>
+      </c>
+      <c r="AR188" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AS188" s="2" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="AT188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU188" s="2" t="n">
+        <v>23.195</v>
+      </c>
+      <c r="AV188" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AW188" s="2" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="AX188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY188" s="2" t="n">
+        <v>23.195</v>
+      </c>
+      <c r="AZ188" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="BA188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>LQDA</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:55:00-04:00</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="n"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>-1.169</v>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="L189" s="2" t="n">
+        <v>0.04337628154593531</v>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>0.002813573917739509</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>0.3896937488550453</v>
+      </c>
+      <c r="O189" s="2" t="n">
+        <v>0.004703027740371679</v>
+      </c>
+      <c r="P189" s="2" t="n">
+        <v>0.007865168539325874</v>
+      </c>
+      <c r="Q189" s="2" t="n">
+        <v>-0.02668419046652781</v>
+      </c>
+      <c r="R189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" s="2" t="n">
+        <v>3.795489189172195</v>
+      </c>
+      <c r="T189" s="2" t="n">
+        <v>0.006770030040121</v>
+      </c>
+      <c r="U189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD189" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE189" s="2" t="n">
+        <v>44.495</v>
+      </c>
+      <c r="AF189" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AG189" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH189" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI189" s="2" t="n">
+        <v>44.495</v>
+      </c>
+      <c r="AJ189" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK189" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL189" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM189" s="2" t="n">
+        <v>44.495</v>
+      </c>
+      <c r="AN189" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AO189" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ189" s="2" t="n">
+        <v>44.495</v>
+      </c>
+      <c r="AR189" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS189" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU189" s="2" t="n">
+        <v>44.495</v>
+      </c>
+      <c r="AV189" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AW189" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY189" s="2" t="n">
+        <v>44.495</v>
+      </c>
+      <c r="AZ189" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BA189" s="2" t="n">
+        <v>0.00157</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:56:00-04:00</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="n"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>-1.235</v>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>0.1775043483106851</v>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N190" s="2" t="n">
+        <v>2.249088733348406</v>
+      </c>
+      <c r="O190" s="2" t="n">
+        <v>0.01954759665499672</v>
+      </c>
+      <c r="P190" s="2" t="n">
+        <v>0.004850717938856316</v>
+      </c>
+      <c r="Q190" s="2" t="n">
+        <v>-0.0009301052993533343</v>
+      </c>
+      <c r="R190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" s="2" t="n">
+        <v>3.981549039608866</v>
+      </c>
+      <c r="T190" s="2" t="n">
+        <v>0.00655294511084259</v>
+      </c>
+      <c r="U190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD190" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE190" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AF190" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG190" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH190" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI190" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AJ190" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK190" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL190" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM190" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AN190" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AO190" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ190" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AR190" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AS190" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU190" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AV190" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AW190" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY190" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AZ190" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BA190" s="2" t="n">
+        <v>0.00037</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:29:00-04:00</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n"/>
+      <c r="I191" s="2" t="n"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>0.4752381339905754</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>0.4622222658187625</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>3.550366544529863</v>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>0.008413839157334513</v>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>0.002797529961010717</v>
+      </c>
+      <c r="Q191" s="2" t="n">
+        <v>-0.00192865895443417</v>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" s="2" t="n">
+        <v>3.145659788805569</v>
+      </c>
+      <c r="T191" s="2" t="n">
+        <v>0.007145089832843787</v>
+      </c>
+      <c r="U191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA191" s="2" t="n"/>
+      <c r="AB191" s="2" t="n"/>
+      <c r="AC191" s="2" t="n"/>
+      <c r="AD191" s="2" t="n"/>
+      <c r="AE191" s="2" t="n"/>
+      <c r="AF191" s="2" t="n"/>
+      <c r="AG191" s="2" t="n"/>
+      <c r="AH191" s="2" t="n"/>
+      <c r="AI191" s="2" t="n"/>
+      <c r="AJ191" s="2" t="n"/>
+      <c r="AK191" s="2" t="n"/>
+      <c r="AL191" s="2" t="n"/>
+      <c r="AM191" s="2" t="n"/>
+      <c r="AN191" s="2" t="n"/>
+      <c r="AO191" s="2" t="n"/>
+      <c r="AP191" s="2" t="n"/>
+      <c r="AQ191" s="2" t="n"/>
+      <c r="AR191" s="2" t="n"/>
+      <c r="AS191" s="2" t="n"/>
+      <c r="AT191" s="2" t="n"/>
+      <c r="AU191" s="2" t="n"/>
+      <c r="AV191" s="2" t="n"/>
+      <c r="AW191" s="2" t="n"/>
+      <c r="AX191" s="2" t="n"/>
+      <c r="AY191" s="2" t="n"/>
+      <c r="AZ191" s="2" t="n"/>
+      <c r="BA191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:33:00-04:00</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="n"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n"/>
+      <c r="I192" s="2" t="n"/>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="L192" s="2" t="n">
+        <v>0.1673989203702904</v>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>0.1161028074311174</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>2.255532732504951</v>
+      </c>
+      <c r="O192" s="2" t="n">
+        <v>0.009491641027011388</v>
+      </c>
+      <c r="P192" s="2" t="n">
+        <v>0.006962728526498807</v>
+      </c>
+      <c r="Q192" s="2" t="n">
+        <v>-0.009506097329456065</v>
+      </c>
+      <c r="R192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" s="2" t="n">
+        <v>3.97292992884594</v>
+      </c>
+      <c r="T192" s="2" t="n">
+        <v>0.007460878934553827</v>
+      </c>
+      <c r="U192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA192" s="2" t="n"/>
+      <c r="AB192" s="2" t="n"/>
+      <c r="AC192" s="2" t="n"/>
+      <c r="AD192" s="2" t="n"/>
+      <c r="AE192" s="2" t="n"/>
+      <c r="AF192" s="2" t="n"/>
+      <c r="AG192" s="2" t="n"/>
+      <c r="AH192" s="2" t="n"/>
+      <c r="AI192" s="2" t="n"/>
+      <c r="AJ192" s="2" t="n"/>
+      <c r="AK192" s="2" t="n"/>
+      <c r="AL192" s="2" t="n"/>
+      <c r="AM192" s="2" t="n"/>
+      <c r="AN192" s="2" t="n"/>
+      <c r="AO192" s="2" t="n"/>
+      <c r="AP192" s="2" t="n"/>
+      <c r="AQ192" s="2" t="n"/>
+      <c r="AR192" s="2" t="n"/>
+      <c r="AS192" s="2" t="n"/>
+      <c r="AT192" s="2" t="n"/>
+      <c r="AU192" s="2" t="n"/>
+      <c r="AV192" s="2" t="n"/>
+      <c r="AW192" s="2" t="n"/>
+      <c r="AX192" s="2" t="n"/>
+      <c r="AY192" s="2" t="n"/>
+      <c r="AZ192" s="2" t="n"/>
+      <c r="BA192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>HHH</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:34:00-04:00</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="n"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="n"/>
+      <c r="I193" s="2" t="n"/>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="L193" s="2" t="n">
+        <v>0.0564894742837565</v>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>0.0423137358227399</v>
+      </c>
+      <c r="N193" s="2" t="n">
+        <v>1.552916954684296</v>
+      </c>
+      <c r="O193" s="2" t="n">
+        <v>0.008070308029459294</v>
+      </c>
+      <c r="P193" s="2" t="n">
+        <v>0.004247842822226776</v>
+      </c>
+      <c r="Q193" s="2" t="n">
+        <v>-0.009946631927966298</v>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" s="2" t="n">
+        <v>4.306157480732418</v>
+      </c>
+      <c r="T193" s="2" t="n">
+        <v>0.007579259691400386</v>
+      </c>
+      <c r="U193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" s="2" t="n"/>
+      <c r="AB193" s="2" t="n"/>
+      <c r="AC193" s="2" t="n"/>
+      <c r="AD193" s="2" t="n"/>
+      <c r="AE193" s="2" t="n"/>
+      <c r="AF193" s="2" t="n"/>
+      <c r="AG193" s="2" t="n"/>
+      <c r="AH193" s="2" t="n"/>
+      <c r="AI193" s="2" t="n"/>
+      <c r="AJ193" s="2" t="n"/>
+      <c r="AK193" s="2" t="n"/>
+      <c r="AL193" s="2" t="n"/>
+      <c r="AM193" s="2" t="n"/>
+      <c r="AN193" s="2" t="n"/>
+      <c r="AO193" s="2" t="n"/>
+      <c r="AP193" s="2" t="n"/>
+      <c r="AQ193" s="2" t="n"/>
+      <c r="AR193" s="2" t="n"/>
+      <c r="AS193" s="2" t="n"/>
+      <c r="AT193" s="2" t="n"/>
+      <c r="AU193" s="2" t="n"/>
+      <c r="AV193" s="2" t="n"/>
+      <c r="AW193" s="2" t="n"/>
+      <c r="AX193" s="2" t="n"/>
+      <c r="AY193" s="2" t="n"/>
+      <c r="AZ193" s="2" t="n"/>
+      <c r="BA193" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31760,7 +35945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33288,6 +37473,194 @@
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>EAF</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>-9.42</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>MLCO</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>partially open</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>BWMX</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>pm_high_break</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>52.885</v>
+      </c>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>partially open</t>
         </is>
       </c>
     </row>

--- a/reports/Paper Bot Live.xlsx
+++ b/reports/Paper Bot Live.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4672,6 +4672,372 @@
       <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>5-min ORB: green first 5 min, closed above range high 17.77 | news: [Benzinga] Norwegian Cruise Line Holdings Announces CFO Tran</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>CPRI</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 18.73, closed back over 9 EMA | news: [Benzinga] Capri Holdings Sees Q3 GAAP EPS $0.95 vs $0.94 Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>CPRI</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>9/21 EMA bounce: tagged 21 EMA 18.73, closed back over 9 EMA | news: [Benzinga] Capri Holdings Sees Q3 GAAP EPS $0.95 vs $0.94 Es</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>STRZ</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 6.6% pole, 1.2% flag on light vol, broke 23.44 | news: [Benzinga] Starz Entertainment Q3 2026 Earnings Call Transcr</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>Bull flag: 6.2% pole, 0.5% flag on light vol, broke 42.83 | news: [Benzinga] Standard Motor Products, Inc. Reports Third Quart</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>-10.43</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>5-min ORB: green first 5 min, closed above range high 42.50 | news: [Benzinga] Standard Motor Products, Inc. Reports Third Quart</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>ACCO</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>VWAP pullback: +20.9%, dipped to VWAP 5.26, reclaimed with green bar | news: [Benzinga] ACCO Brands Q3 2026 Earnings Call Transcript +8-K</t>
         </is>
       </c>
     </row>
@@ -4686,7 +5052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA369"/>
+  <dimension ref="A1:BA393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66182,8 +66548,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H364" s="2" t="n"/>
-      <c r="I364" s="2" t="n"/>
+      <c r="H364" s="2" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -66237,20 +66609,48 @@
       <c r="Z364" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA364" s="2" t="n"/>
-      <c r="AB364" s="2" t="n"/>
-      <c r="AC364" s="2" t="n"/>
-      <c r="AD364" s="2" t="n"/>
-      <c r="AE364" s="2" t="n"/>
-      <c r="AF364" s="2" t="n"/>
-      <c r="AG364" s="2" t="n"/>
-      <c r="AH364" s="2" t="n"/>
-      <c r="AI364" s="2" t="n"/>
-      <c r="AJ364" s="2" t="n"/>
-      <c r="AK364" s="2" t="n"/>
-      <c r="AL364" s="2" t="n"/>
-      <c r="AM364" s="2" t="n"/>
-      <c r="AN364" s="2" t="n"/>
+      <c r="AA364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC364" s="2" t="n">
+        <v>1.3261</v>
+      </c>
+      <c r="AD364" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE364" s="2" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AF364" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AG364" s="2" t="n">
+        <v>1.6522</v>
+      </c>
+      <c r="AH364" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI364" s="2" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AJ364" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AK364" s="2" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="AL364" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM364" s="2" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN364" s="2" t="n">
+        <v>0.23</v>
+      </c>
       <c r="AO364" s="2" t="n"/>
       <c r="AP364" s="2" t="n"/>
       <c r="AQ364" s="2" t="n"/>
@@ -66263,7 +66663,9 @@
       <c r="AX364" s="2" t="n"/>
       <c r="AY364" s="2" t="n"/>
       <c r="AZ364" s="2" t="n"/>
-      <c r="BA364" s="2" t="n"/>
+      <c r="BA364" s="2" t="n">
+        <v>0.00152</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -66295,8 +66697,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H365" s="2" t="n"/>
-      <c r="I365" s="2" t="n"/>
+      <c r="H365" s="2" t="n">
+        <v>-1.139</v>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J365" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -66350,33 +66758,87 @@
       <c r="Z365" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA365" s="2" t="n"/>
-      <c r="AB365" s="2" t="n"/>
-      <c r="AC365" s="2" t="n"/>
-      <c r="AD365" s="2" t="n"/>
-      <c r="AE365" s="2" t="n"/>
-      <c r="AF365" s="2" t="n"/>
-      <c r="AG365" s="2" t="n"/>
-      <c r="AH365" s="2" t="n"/>
-      <c r="AI365" s="2" t="n"/>
-      <c r="AJ365" s="2" t="n"/>
-      <c r="AK365" s="2" t="n"/>
-      <c r="AL365" s="2" t="n"/>
-      <c r="AM365" s="2" t="n"/>
-      <c r="AN365" s="2" t="n"/>
-      <c r="AO365" s="2" t="n"/>
-      <c r="AP365" s="2" t="n"/>
-      <c r="AQ365" s="2" t="n"/>
-      <c r="AR365" s="2" t="n"/>
-      <c r="AS365" s="2" t="n"/>
-      <c r="AT365" s="2" t="n"/>
-      <c r="AU365" s="2" t="n"/>
-      <c r="AV365" s="2" t="n"/>
-      <c r="AW365" s="2" t="n"/>
-      <c r="AX365" s="2" t="n"/>
-      <c r="AY365" s="2" t="n"/>
-      <c r="AZ365" s="2" t="n"/>
-      <c r="BA365" s="2" t="n"/>
+      <c r="AA365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC365" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE365" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AF365" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AG365" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI365" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AJ365" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AK365" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL365" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM365" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AN365" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AO365" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ365" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AR365" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AS365" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU365" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AV365" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AW365" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX365" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY365" s="2" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AZ365" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BA365" s="2" t="n">
+        <v>0.00029</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -66408,8 +66870,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H366" s="2" t="n"/>
-      <c r="I366" s="2" t="n"/>
+      <c r="H366" s="2" t="n">
+        <v>-1.222</v>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -66463,33 +66931,87 @@
       <c r="Z366" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA366" s="2" t="n"/>
-      <c r="AB366" s="2" t="n"/>
-      <c r="AC366" s="2" t="n"/>
-      <c r="AD366" s="2" t="n"/>
-      <c r="AE366" s="2" t="n"/>
-      <c r="AF366" s="2" t="n"/>
-      <c r="AG366" s="2" t="n"/>
-      <c r="AH366" s="2" t="n"/>
-      <c r="AI366" s="2" t="n"/>
-      <c r="AJ366" s="2" t="n"/>
-      <c r="AK366" s="2" t="n"/>
-      <c r="AL366" s="2" t="n"/>
-      <c r="AM366" s="2" t="n"/>
-      <c r="AN366" s="2" t="n"/>
-      <c r="AO366" s="2" t="n"/>
-      <c r="AP366" s="2" t="n"/>
-      <c r="AQ366" s="2" t="n"/>
-      <c r="AR366" s="2" t="n"/>
-      <c r="AS366" s="2" t="n"/>
-      <c r="AT366" s="2" t="n"/>
-      <c r="AU366" s="2" t="n"/>
-      <c r="AV366" s="2" t="n"/>
-      <c r="AW366" s="2" t="n"/>
-      <c r="AX366" s="2" t="n"/>
-      <c r="AY366" s="2" t="n"/>
-      <c r="AZ366" s="2" t="n"/>
-      <c r="BA366" s="2" t="n"/>
+      <c r="AA366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC366" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD366" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE366" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AF366" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG366" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH366" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI366" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AJ366" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK366" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL366" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM366" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AN366" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO366" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ366" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AR366" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS366" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU366" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AV366" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW366" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX366" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY366" s="2" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AZ366" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA366" s="2" t="n">
+        <v>0.00063</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -66521,8 +67043,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H367" s="2" t="n"/>
-      <c r="I367" s="2" t="n"/>
+      <c r="H367" s="2" t="n">
+        <v>-1.105</v>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J367" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -66576,33 +67104,87 @@
       <c r="Z367" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA367" s="2" t="n"/>
-      <c r="AB367" s="2" t="n"/>
-      <c r="AC367" s="2" t="n"/>
-      <c r="AD367" s="2" t="n"/>
-      <c r="AE367" s="2" t="n"/>
-      <c r="AF367" s="2" t="n"/>
-      <c r="AG367" s="2" t="n"/>
-      <c r="AH367" s="2" t="n"/>
-      <c r="AI367" s="2" t="n"/>
-      <c r="AJ367" s="2" t="n"/>
-      <c r="AK367" s="2" t="n"/>
-      <c r="AL367" s="2" t="n"/>
-      <c r="AM367" s="2" t="n"/>
-      <c r="AN367" s="2" t="n"/>
-      <c r="AO367" s="2" t="n"/>
-      <c r="AP367" s="2" t="n"/>
-      <c r="AQ367" s="2" t="n"/>
-      <c r="AR367" s="2" t="n"/>
-      <c r="AS367" s="2" t="n"/>
-      <c r="AT367" s="2" t="n"/>
-      <c r="AU367" s="2" t="n"/>
-      <c r="AV367" s="2" t="n"/>
-      <c r="AW367" s="2" t="n"/>
-      <c r="AX367" s="2" t="n"/>
-      <c r="AY367" s="2" t="n"/>
-      <c r="AZ367" s="2" t="n"/>
-      <c r="BA367" s="2" t="n"/>
+      <c r="AA367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC367" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD367" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE367" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AF367" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AG367" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH367" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI367" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AJ367" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK367" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL367" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM367" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AN367" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AO367" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ367" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AR367" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS367" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU367" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AV367" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW367" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY367" s="2" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="AZ367" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA367" s="2" t="n">
+        <v>0.00112</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -66634,8 +67216,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H368" s="2" t="n"/>
-      <c r="I368" s="2" t="n"/>
+      <c r="H368" s="2" t="n">
+        <v>-1.207</v>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -66689,33 +67277,87 @@
       <c r="Z368" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA368" s="2" t="n"/>
-      <c r="AB368" s="2" t="n"/>
-      <c r="AC368" s="2" t="n"/>
-      <c r="AD368" s="2" t="n"/>
-      <c r="AE368" s="2" t="n"/>
-      <c r="AF368" s="2" t="n"/>
-      <c r="AG368" s="2" t="n"/>
-      <c r="AH368" s="2" t="n"/>
-      <c r="AI368" s="2" t="n"/>
-      <c r="AJ368" s="2" t="n"/>
-      <c r="AK368" s="2" t="n"/>
-      <c r="AL368" s="2" t="n"/>
-      <c r="AM368" s="2" t="n"/>
-      <c r="AN368" s="2" t="n"/>
-      <c r="AO368" s="2" t="n"/>
-      <c r="AP368" s="2" t="n"/>
-      <c r="AQ368" s="2" t="n"/>
-      <c r="AR368" s="2" t="n"/>
-      <c r="AS368" s="2" t="n"/>
-      <c r="AT368" s="2" t="n"/>
-      <c r="AU368" s="2" t="n"/>
-      <c r="AV368" s="2" t="n"/>
-      <c r="AW368" s="2" t="n"/>
-      <c r="AX368" s="2" t="n"/>
-      <c r="AY368" s="2" t="n"/>
-      <c r="AZ368" s="2" t="n"/>
-      <c r="BA368" s="2" t="n"/>
+      <c r="AA368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC368" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD368" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE368" s="2" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="AF368" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AG368" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH368" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI368" s="2" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="AJ368" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AK368" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL368" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM368" s="2" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="AN368" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AO368" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ368" s="2" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="AR368" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AS368" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU368" s="2" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="AV368" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AW368" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX368" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY368" s="2" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="AZ368" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="BA368" s="2" t="n">
+        <v>0.00055</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -66747,8 +67389,14 @@
           <t>off</t>
         </is>
       </c>
-      <c r="H369" s="2" t="n"/>
-      <c r="I369" s="2" t="n"/>
+      <c r="H369" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>next open</t>
+        </is>
+      </c>
       <c r="J369" s="2" t="inlineStr">
         <is>
           <t>eod_squeeze</t>
@@ -66802,33 +67450,4051 @@
       <c r="Z369" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA369" s="2" t="n"/>
-      <c r="AB369" s="2" t="n"/>
-      <c r="AC369" s="2" t="n"/>
-      <c r="AD369" s="2" t="n"/>
-      <c r="AE369" s="2" t="n"/>
-      <c r="AF369" s="2" t="n"/>
-      <c r="AG369" s="2" t="n"/>
-      <c r="AH369" s="2" t="n"/>
-      <c r="AI369" s="2" t="n"/>
-      <c r="AJ369" s="2" t="n"/>
-      <c r="AK369" s="2" t="n"/>
-      <c r="AL369" s="2" t="n"/>
-      <c r="AM369" s="2" t="n"/>
-      <c r="AN369" s="2" t="n"/>
-      <c r="AO369" s="2" t="n"/>
-      <c r="AP369" s="2" t="n"/>
-      <c r="AQ369" s="2" t="n"/>
-      <c r="AR369" s="2" t="n"/>
-      <c r="AS369" s="2" t="n"/>
-      <c r="AT369" s="2" t="n"/>
-      <c r="AU369" s="2" t="n"/>
-      <c r="AV369" s="2" t="n"/>
-      <c r="AW369" s="2" t="n"/>
-      <c r="AX369" s="2" t="n"/>
-      <c r="AY369" s="2" t="n"/>
-      <c r="AZ369" s="2" t="n"/>
-      <c r="BA369" s="2" t="n"/>
+      <c r="AA369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC369" s="2" t="n">
+        <v>-0.9167</v>
+      </c>
+      <c r="AD369" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE369" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AF369" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AG369" s="2" t="n">
+        <v>-0.9167</v>
+      </c>
+      <c r="AH369" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI369" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AJ369" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AK369" s="2" t="n">
+        <v>-0.9167</v>
+      </c>
+      <c r="AL369" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM369" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AN369" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AO369" s="2" t="n">
+        <v>-0.9167</v>
+      </c>
+      <c r="AP369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ369" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AR369" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AS369" s="2" t="n">
+        <v>-0.9167</v>
+      </c>
+      <c r="AT369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU369" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AV369" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AW369" s="2" t="n">
+        <v>-0.9167</v>
+      </c>
+      <c r="AX369" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY369" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AZ369" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BA369" s="2" t="n">
+        <v>0.00112</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>ULH</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:46:00-04:00</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="n"/>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="n"/>
+      <c r="I370" s="2" t="n"/>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L370" s="2" t="n">
+        <v>0.1613088090491102</v>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>0.1067738577615018</v>
+      </c>
+      <c r="N370" s="2" t="n">
+        <v>1.327647305131664</v>
+      </c>
+      <c r="O370" s="2" t="n">
+        <v>0.06997978500869895</v>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>0.03015321582003826</v>
+      </c>
+      <c r="Q370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S370" s="2" t="n">
+        <v>3.007166628551692</v>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>-0.01160704071670771</v>
+      </c>
+      <c r="U370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V370" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC370" s="2" t="n"/>
+      <c r="AD370" s="2" t="n"/>
+      <c r="AE370" s="2" t="n"/>
+      <c r="AF370" s="2" t="n"/>
+      <c r="AG370" s="2" t="n"/>
+      <c r="AH370" s="2" t="n"/>
+      <c r="AI370" s="2" t="n"/>
+      <c r="AJ370" s="2" t="n"/>
+      <c r="AK370" s="2" t="n"/>
+      <c r="AL370" s="2" t="n"/>
+      <c r="AM370" s="2" t="n"/>
+      <c r="AN370" s="2" t="n"/>
+      <c r="AO370" s="2" t="n"/>
+      <c r="AP370" s="2" t="n"/>
+      <c r="AQ370" s="2" t="n"/>
+      <c r="AR370" s="2" t="n"/>
+      <c r="AS370" s="2" t="n"/>
+      <c r="AT370" s="2" t="n"/>
+      <c r="AU370" s="2" t="n"/>
+      <c r="AV370" s="2" t="n"/>
+      <c r="AW370" s="2" t="n"/>
+      <c r="AX370" s="2" t="n"/>
+      <c r="AY370" s="2" t="n"/>
+      <c r="AZ370" s="2" t="n"/>
+      <c r="BA370" s="2" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="n"/>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="n">
+        <v>-1.043</v>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L371" s="2" t="n">
+        <v>0.1160783954695159</v>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>0.08235298106872957</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>1.893194004187156</v>
+      </c>
+      <c r="O371" s="2" t="n">
+        <v>0.03295156335987248</v>
+      </c>
+      <c r="P371" s="2" t="n">
+        <v>0.02998357151288726</v>
+      </c>
+      <c r="Q371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S371" s="2" t="n">
+        <v>3.753964668600954</v>
+      </c>
+      <c r="T371" s="2" t="n">
+        <v>-0.0116850244430986</v>
+      </c>
+      <c r="U371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC371" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD371" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE371" s="2" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AF371" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG371" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH371" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI371" s="2" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AJ371" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK371" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL371" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM371" s="2" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="AN371" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO371" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ371" s="2" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="AR371" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS371" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU371" s="2" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="AV371" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AW371" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX371" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY371" s="2" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="AZ371" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA371" s="2" t="n">
+        <v>0.02221</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="n"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L372" s="2" t="n">
+        <v>0.1016571261750054</v>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>0.06692162006477331</v>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>2.492412067778248</v>
+      </c>
+      <c r="O372" s="2" t="n">
+        <v>0.02210995360624834</v>
+      </c>
+      <c r="P372" s="2" t="n">
+        <v>0.02993924512470219</v>
+      </c>
+      <c r="Q372" s="2" t="n">
+        <v>-0.001300071687431736</v>
+      </c>
+      <c r="R372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S372" s="2" t="n">
+        <v>4.236133425665715</v>
+      </c>
+      <c r="T372" s="2" t="n">
+        <v>-0.01106115463197155</v>
+      </c>
+      <c r="U372" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC372" s="2" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="AD372" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE372" s="2" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AF372" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG372" s="2" t="n">
+        <v>0.9481000000000001</v>
+      </c>
+      <c r="AH372" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI372" s="2" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AJ372" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK372" s="2" t="n">
+        <v>0.9646</v>
+      </c>
+      <c r="AL372" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM372" s="2" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AN372" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO372" s="2" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="AP372" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ372" s="2" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="AR372" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS372" s="2" t="n">
+        <v>0.9952</v>
+      </c>
+      <c r="AT372" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU372" s="2" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="AV372" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW372" s="2" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="AX372" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY372" s="2" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="AZ372" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BA372" s="2" t="n">
+        <v>0.00317</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="n">
+        <v>67.52</v>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="n"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>orb15</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L373" s="2" t="n">
+        <v>0.1016571261750054</v>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>0.06692162006477331</v>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>2.492412067778248</v>
+      </c>
+      <c r="O373" s="2" t="n">
+        <v>0.02210995360624834</v>
+      </c>
+      <c r="P373" s="2" t="n">
+        <v>0.02343071165677485</v>
+      </c>
+      <c r="Q373" s="2" t="n">
+        <v>-0.001300071687431736</v>
+      </c>
+      <c r="R373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S373" s="2" t="n">
+        <v>4.236133425665715</v>
+      </c>
+      <c r="T373" s="2" t="n">
+        <v>-0.01106115463197155</v>
+      </c>
+      <c r="U373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC373" s="2" t="n">
+        <v>1.1018</v>
+      </c>
+      <c r="AD373" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE373" s="2" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AF373" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG373" s="2" t="n">
+        <v>1.2036</v>
+      </c>
+      <c r="AH373" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI373" s="2" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AJ373" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK373" s="2" t="n">
+        <v>1.0898</v>
+      </c>
+      <c r="AL373" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM373" s="2" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="AN373" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO373" s="2" t="n">
+        <v>1.1358</v>
+      </c>
+      <c r="AP373" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ373" s="2" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="AR373" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS373" s="2" t="n">
+        <v>1.2716</v>
+      </c>
+      <c r="AT373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU373" s="2" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="AV373" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AW373" s="2" t="n">
+        <v>1.1235</v>
+      </c>
+      <c r="AX373" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY373" s="2" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="AZ373" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA373" s="2" t="n">
+        <v>0.00317</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>CPRI</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:14:00-04:00</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="n"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="n">
+        <v>-1.143</v>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L374" s="2" t="n">
+        <v>0.1712328824064897</v>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>0.09962642806201605</v>
+      </c>
+      <c r="N374" s="2" t="n">
+        <v>3.033467013148281</v>
+      </c>
+      <c r="O374" s="2" t="n">
+        <v>0.01107661648694469</v>
+      </c>
+      <c r="P374" s="2" t="n">
+        <v>0.009569349869907921</v>
+      </c>
+      <c r="Q374" s="2" t="n">
+        <v>-0.01737484225907426</v>
+      </c>
+      <c r="R374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S374" s="2" t="n">
+        <v>2.934388614920721</v>
+      </c>
+      <c r="T374" s="2" t="n">
+        <v>-0.01399216862509212</v>
+      </c>
+      <c r="U374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC374" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD374" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE374" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AF374" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AG374" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH374" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI374" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AJ374" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK374" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL374" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM374" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AN374" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AO374" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ374" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AR374" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AS374" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU374" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AV374" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW374" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY374" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AZ374" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA374" s="2" t="n">
+        <v>0.00106</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:18:00-04:00</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="n"/>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="L375" s="2" t="n">
+        <v>0.1257516698899612</v>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>0.08235298106872957</v>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>1.515888576934257</v>
+      </c>
+      <c r="O375" s="2" t="n">
+        <v>0.02987671448355167</v>
+      </c>
+      <c r="P375" s="2" t="n">
+        <v>0.01091503386673233</v>
+      </c>
+      <c r="Q375" s="2" t="n">
+        <v>-0.0104561191023631</v>
+      </c>
+      <c r="R375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S375" s="2" t="n">
+        <v>3.762594523828716</v>
+      </c>
+      <c r="T375" s="2" t="n">
+        <v>-0.01424555623657997</v>
+      </c>
+      <c r="U375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC375" s="2" t="n">
+        <v>-1.0085</v>
+      </c>
+      <c r="AD375" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE375" s="2" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AF375" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AG375" s="2" t="n">
+        <v>-1.0085</v>
+      </c>
+      <c r="AH375" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI375" s="2" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AJ375" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AK375" s="2" t="n">
+        <v>-1.0085</v>
+      </c>
+      <c r="AL375" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM375" s="2" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AN375" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AO375" s="2" t="n">
+        <v>-1.0106</v>
+      </c>
+      <c r="AP375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ375" s="2" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="AR375" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AS375" s="2" t="n">
+        <v>-1.0106</v>
+      </c>
+      <c r="AT375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU375" s="2" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="AV375" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AW375" s="2" t="n">
+        <v>-1.0106</v>
+      </c>
+      <c r="AX375" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY375" s="2" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="AZ375" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BA375" s="2" t="n">
+        <v>0.01182</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>STRZ</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:22:00-04:00</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="n"/>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="n">
+        <v>-1.047</v>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="L376" s="2" t="n">
+        <v>0.09245631324946668</v>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>0.1214351157977336</v>
+      </c>
+      <c r="N376" s="2" t="n">
+        <v>1.885050017535282</v>
+      </c>
+      <c r="O376" s="2" t="n">
+        <v>0.0003999976689654794</v>
+      </c>
+      <c r="P376" s="2" t="n">
+        <v>0.0252631578947369</v>
+      </c>
+      <c r="Q376" s="2" t="n">
+        <v>-0.03807211477217154</v>
+      </c>
+      <c r="R376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S376" s="2" t="n">
+        <v>3.16758253048065</v>
+      </c>
+      <c r="T376" s="2" t="n">
+        <v>-0.01499945181327633</v>
+      </c>
+      <c r="U376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB376" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC376" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD376" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE376" s="2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AF376" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG376" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH376" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI376" s="2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AJ376" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK376" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL376" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM376" s="2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AN376" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO376" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ376" s="2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AR376" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AS376" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU376" s="2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AV376" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AW376" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX376" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY376" s="2" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AZ376" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:25:00-04:00</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="n"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="L377" s="2" t="n">
+        <v>0.09894842360184142</v>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>0.06692162006477331</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>2.193811627484095</v>
+      </c>
+      <c r="O377" s="2" t="n">
+        <v>0.01455106009607743</v>
+      </c>
+      <c r="P377" s="2" t="n">
+        <v>0.006814574632224916</v>
+      </c>
+      <c r="Q377" s="2" t="n">
+        <v>-0.008054042405081896</v>
+      </c>
+      <c r="R377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S377" s="2" t="n">
+        <v>4.233671645142245</v>
+      </c>
+      <c r="T377" s="2" t="n">
+        <v>-0.0153048814639426</v>
+      </c>
+      <c r="U377" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC377" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD377" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE377" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AF377" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG377" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH377" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI377" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AJ377" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK377" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL377" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM377" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN377" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO377" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ377" s="2" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="AR377" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AS377" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU377" s="2" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="AV377" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AW377" s="2" t="n">
+        <v>1.2872</v>
+      </c>
+      <c r="AX377" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY377" s="2" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="AZ377" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BA377" s="2" t="n">
+        <v>0.00246</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>NFE</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="n"/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L378" s="2" t="n">
+        <v>0.2024802829720316</v>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>-0.02374667943936026</v>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>2.459443216555639</v>
+      </c>
+      <c r="O378" s="2" t="n">
+        <v>0.02612773579453487</v>
+      </c>
+      <c r="P378" s="2" t="n">
+        <v>0.01040071624967923</v>
+      </c>
+      <c r="Q378" s="2" t="n">
+        <v>-0.0445701792837746</v>
+      </c>
+      <c r="R378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S378" s="2" t="n">
+        <v>1.516752335195667</v>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>-0.01464848537832897</v>
+      </c>
+      <c r="U378" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC378" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD378" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE378" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AF378" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG378" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH378" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI378" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AJ378" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK378" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL378" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM378" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AN378" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AO378" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ378" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AR378" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS378" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT378" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU378" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AV378" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW378" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX378" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY378" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AZ378" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BA378" s="2" t="n">
+        <v>0.00881</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>NFE</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:31:00-04:00</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="n"/>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="L379" s="2" t="n">
+        <v>0.2084432638006615</v>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>-0.02374667943936026</v>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>2.444583067704754</v>
+      </c>
+      <c r="O379" s="2" t="n">
+        <v>0.03121620177848028</v>
+      </c>
+      <c r="P379" s="2" t="n">
+        <v>0.0174672325412006</v>
+      </c>
+      <c r="Q379" s="2" t="n">
+        <v>-0.0398322972704821</v>
+      </c>
+      <c r="R379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" s="2" t="n">
+        <v>1.521698981468027</v>
+      </c>
+      <c r="T379" s="2" t="n">
+        <v>-0.01449902318044449</v>
+      </c>
+      <c r="U379" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB379" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC379" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD379" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE379" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AF379" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG379" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH379" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI379" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AJ379" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK379" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL379" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM379" s="2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AN379" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO379" s="2" t="n"/>
+      <c r="AP379" s="2" t="n"/>
+      <c r="AQ379" s="2" t="n"/>
+      <c r="AR379" s="2" t="n"/>
+      <c r="AS379" s="2" t="n"/>
+      <c r="AT379" s="2" t="n"/>
+      <c r="AU379" s="2" t="n"/>
+      <c r="AV379" s="2" t="n"/>
+      <c r="AW379" s="2" t="n"/>
+      <c r="AX379" s="2" t="n"/>
+      <c r="AY379" s="2" t="n"/>
+      <c r="AZ379" s="2" t="n"/>
+      <c r="BA379" s="2" t="n">
+        <v>0.00657</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>CDNA</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:34:00-04:00</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="n"/>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>-1.224</v>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="L380" s="2" t="n">
+        <v>0.228466240941027</v>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>0.147930681314991</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>1.877007819272986</v>
+      </c>
+      <c r="O380" s="2" t="n">
+        <v>0.006180758097872996</v>
+      </c>
+      <c r="P380" s="2" t="n">
+        <v>0.007169384645135889</v>
+      </c>
+      <c r="Q380" s="2" t="n">
+        <v>-0.03312535740484057</v>
+      </c>
+      <c r="R380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S380" s="2" t="n">
+        <v>4.4757435166283</v>
+      </c>
+      <c r="T380" s="2" t="n">
+        <v>-0.01447958674812944</v>
+      </c>
+      <c r="U380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC380" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD380" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE380" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="AF380" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG380" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH380" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI380" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="AJ380" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AK380" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL380" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM380" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="AN380" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AO380" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ380" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="AR380" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AS380" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU380" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="AV380" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AW380" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX380" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY380" s="2" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="AZ380" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BA380" s="2" t="n">
+        <v>0.00399</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>CDNA</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:36:00-04:00</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="n"/>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>-1.207</v>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="L381" s="2" t="n">
+        <v>0.229516242813173</v>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>0.147930681314991</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>1.857360081122414</v>
+      </c>
+      <c r="O381" s="2" t="n">
+        <v>0.007012836796119526</v>
+      </c>
+      <c r="P381" s="2" t="n">
+        <v>0.008358419048161069</v>
+      </c>
+      <c r="Q381" s="2" t="n">
+        <v>-0.03229894463823679</v>
+      </c>
+      <c r="R381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S381" s="2" t="n">
+        <v>4.476597877424567</v>
+      </c>
+      <c r="T381" s="2" t="n">
+        <v>-0.01412211505828476</v>
+      </c>
+      <c r="U381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC381" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD381" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE381" s="2" t="n">
+        <v>87.6979</v>
+      </c>
+      <c r="AF381" s="2" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="AG381" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH381" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI381" s="2" t="n">
+        <v>87.6979</v>
+      </c>
+      <c r="AJ381" s="2" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="AK381" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL381" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM381" s="2" t="n">
+        <v>87.6979</v>
+      </c>
+      <c r="AN381" s="2" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="AO381" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ381" s="2" t="n">
+        <v>87.6979</v>
+      </c>
+      <c r="AR381" s="2" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="AS381" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU381" s="2" t="n">
+        <v>87.6979</v>
+      </c>
+      <c r="AV381" s="2" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="AW381" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX381" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY381" s="2" t="n">
+        <v>87.6979</v>
+      </c>
+      <c r="AZ381" s="2" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="BA381" s="2" t="n">
+        <v>0.00444</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>BTSG</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:38:00-04:00</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="n"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="L382" s="2" t="n">
+        <v>0.1232978291573104</v>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>0.08751239681567169</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>1.671394564290995</v>
+      </c>
+      <c r="O382" s="2" t="n">
+        <v>0.001387626381596174</v>
+      </c>
+      <c r="P382" s="2" t="n">
+        <v>0.01574390858034834</v>
+      </c>
+      <c r="Q382" s="2" t="n">
+        <v>-0.04886116379800942</v>
+      </c>
+      <c r="R382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S382" s="2" t="n">
+        <v>4.214273392429576</v>
+      </c>
+      <c r="T382" s="2" t="n">
+        <v>-0.01250389323639134</v>
+      </c>
+      <c r="U382" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V382" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC382" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD382" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE382" s="2" t="n">
+        <v>67.1801</v>
+      </c>
+      <c r="AF382" s="2" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="AG382" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH382" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI382" s="2" t="n">
+        <v>67.1801</v>
+      </c>
+      <c r="AJ382" s="2" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="AK382" s="2" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="AL382" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM382" s="2" t="n">
+        <v>67.1801</v>
+      </c>
+      <c r="AN382" s="2" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="AO382" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP382" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ382" s="2" t="n">
+        <v>67.1801</v>
+      </c>
+      <c r="AR382" s="2" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="AS382" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT382" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU382" s="2" t="n">
+        <v>67.1801</v>
+      </c>
+      <c r="AV382" s="2" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="AW382" s="2" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="AX382" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY382" s="2" t="n">
+        <v>67.1801</v>
+      </c>
+      <c r="AZ382" s="2" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="BA382" s="2" t="n">
+        <v>0.00444</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>XPOF</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:39:00-04:00</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="n"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>-1.357</v>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="L383" s="2" t="n">
+        <v>0.1631015758129324</v>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>-0.01604276540816718</v>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>1.957152285170923</v>
+      </c>
+      <c r="O383" s="2" t="n">
+        <v>0.01951087600439472</v>
+      </c>
+      <c r="P383" s="2" t="n">
+        <v>0.009195380576898523</v>
+      </c>
+      <c r="Q383" s="2" t="n">
+        <v>-0.07051280679708982</v>
+      </c>
+      <c r="R383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S383" s="2" t="n">
+        <v>1.470175823177045</v>
+      </c>
+      <c r="T383" s="2" t="n">
+        <v>-0.01286779084875644</v>
+      </c>
+      <c r="U383" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB383" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC383" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AD383" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE383" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AF383" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG383" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AH383" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI383" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AJ383" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK383" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AL383" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM383" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AN383" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO383" s="2" t="n"/>
+      <c r="AP383" s="2" t="n"/>
+      <c r="AQ383" s="2" t="n"/>
+      <c r="AR383" s="2" t="n"/>
+      <c r="AS383" s="2" t="n"/>
+      <c r="AT383" s="2" t="n"/>
+      <c r="AU383" s="2" t="n"/>
+      <c r="AV383" s="2" t="n"/>
+      <c r="AW383" s="2" t="n"/>
+      <c r="AX383" s="2" t="n"/>
+      <c r="AY383" s="2" t="n"/>
+      <c r="AZ383" s="2" t="n"/>
+      <c r="BA383" s="2" t="n">
+        <v>0.00459</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>CURV</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:41:00-04:00</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="n"/>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>-1.286</v>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="L384" s="2" t="n">
+        <v>0.08108111010696084</v>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>-0.009009000301245074</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>1.732618482126286</v>
+      </c>
+      <c r="O384" s="2" t="n">
+        <v>0.01789087084425312</v>
+      </c>
+      <c r="P384" s="2" t="n">
+        <v>0.01666670574082119</v>
+      </c>
+      <c r="Q384" s="2" t="n">
+        <v>-0.01635305845931112</v>
+      </c>
+      <c r="R384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S384" s="2" t="n">
+        <v>0.875468777090329</v>
+      </c>
+      <c r="T384" s="2" t="n">
+        <v>-0.01233491527381492</v>
+      </c>
+      <c r="U384" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB384" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC384" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD384" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE384" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF384" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG384" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH384" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI384" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AJ384" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK384" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL384" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM384" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AN384" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO384" s="2" t="n"/>
+      <c r="AP384" s="2" t="n"/>
+      <c r="AQ384" s="2" t="n"/>
+      <c r="AR384" s="2" t="n"/>
+      <c r="AS384" s="2" t="n"/>
+      <c r="AT384" s="2" t="n"/>
+      <c r="AU384" s="2" t="n"/>
+      <c r="AV384" s="2" t="n"/>
+      <c r="AW384" s="2" t="n"/>
+      <c r="AX384" s="2" t="n"/>
+      <c r="AY384" s="2" t="n"/>
+      <c r="AZ384" s="2" t="n"/>
+      <c r="BA384" s="2" t="n">
+        <v>0.0083</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>XPOF</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:43:00-04:00</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="n"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>-1.278</v>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="L385" s="2" t="n">
+        <v>0.1711230222652991</v>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>-0.01604276540816718</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>1.867072371191064</v>
+      </c>
+      <c r="O385" s="2" t="n">
+        <v>0.02718119261883345</v>
+      </c>
+      <c r="P385" s="2" t="n">
+        <v>0.01598176087030844</v>
+      </c>
+      <c r="Q385" s="2" t="n">
+        <v>-0.06410250532086104</v>
+      </c>
+      <c r="R385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S385" s="2" t="n">
+        <v>1.477048750516418</v>
+      </c>
+      <c r="T385" s="2" t="n">
+        <v>-0.01203599087804597</v>
+      </c>
+      <c r="U385" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC385" s="2" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="AD385" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE385" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AF385" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG385" s="2" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="AH385" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI385" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AJ385" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK385" s="2" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="AL385" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM385" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AN385" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO385" s="2" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="AP385" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ385" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AR385" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS385" s="2" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="AT385" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU385" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AV385" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW385" s="2" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="AX385" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY385" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AZ385" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA385" s="2" t="n">
+        <v>0.00457</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:15:00-04:00</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="n"/>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>-1.267</v>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="L386" s="2" t="n">
+        <v>0.2305262716192948</v>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>0.1094736801950555</v>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>1.160107512252212</v>
+      </c>
+      <c r="O386" s="2" t="n">
+        <v>0.03698747500483823</v>
+      </c>
+      <c r="P386" s="2" t="n">
+        <v>0.00940971636713215</v>
+      </c>
+      <c r="Q386" s="2" t="n">
+        <v>-0.004258960111555576</v>
+      </c>
+      <c r="R386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" s="2" t="n">
+        <v>1.765586559028676</v>
+      </c>
+      <c r="T386" s="2" t="n">
+        <v>-0.01388165862421475</v>
+      </c>
+      <c r="U386" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC386" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD386" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE386" s="2" t="n">
+        <v>5.8449</v>
+      </c>
+      <c r="AF386" s="2" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AG386" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH386" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI386" s="2" t="n">
+        <v>5.8449</v>
+      </c>
+      <c r="AJ386" s="2" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AK386" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL386" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM386" s="2" t="n">
+        <v>5.8449</v>
+      </c>
+      <c r="AN386" s="2" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AO386" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP386" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ386" s="2" t="n">
+        <v>5.8449</v>
+      </c>
+      <c r="AR386" s="2" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AS386" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT386" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU386" s="2" t="n">
+        <v>5.8449</v>
+      </c>
+      <c r="AV386" s="2" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AW386" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX386" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY386" s="2" t="n">
+        <v>5.8449</v>
+      </c>
+      <c r="AZ386" s="2" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="BA386" s="2" t="n">
+        <v>0.00171</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:16:00-04:00</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="n"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>hod_break</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="L387" s="2" t="n">
+        <v>0.236842105263158</v>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>0.1094736801950555</v>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>1.122878040049733</v>
+      </c>
+      <c r="O387" s="2" t="n">
+        <v>0.04294693427772467</v>
+      </c>
+      <c r="P387" s="2" t="n">
+        <v>0.01446808510638297</v>
+      </c>
+      <c r="Q387" s="2" t="n">
+        <v>-0.003392702458222985</v>
+      </c>
+      <c r="R387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S387" s="2" t="n">
+        <v>1.770706060030223</v>
+      </c>
+      <c r="T387" s="2" t="n">
+        <v>-0.01381018015272117</v>
+      </c>
+      <c r="U387" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC387" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD387" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE387" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AF387" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AG387" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH387" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI387" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AJ387" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AK387" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL387" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM387" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AN387" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AO387" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP387" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ387" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AR387" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AS387" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT387" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU387" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AV387" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AW387" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX387" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY387" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AZ387" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="BA387" s="2" t="n">
+        <v>0.0017</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:04:00-04:00</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="n"/>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>breakeven</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K388" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="L388" s="2" t="n">
+        <v>0.2294737163342928</v>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>0.1094736801950555</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>1.062296098470216</v>
+      </c>
+      <c r="O388" s="2" t="n">
+        <v>0.02965179727265621</v>
+      </c>
+      <c r="P388" s="2" t="n">
+        <v>0.01027399846236346</v>
+      </c>
+      <c r="Q388" s="2" t="n">
+        <v>-0.009329911538011326</v>
+      </c>
+      <c r="R388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S388" s="2" t="n">
+        <v>1.764730822968199</v>
+      </c>
+      <c r="T388" s="2" t="n">
+        <v>-0.01601331958873464</v>
+      </c>
+      <c r="U388" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC388" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD388" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE388" s="2" t="n">
+        <v>5.8399</v>
+      </c>
+      <c r="AF388" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AG388" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH388" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI388" s="2" t="n">
+        <v>5.8399</v>
+      </c>
+      <c r="AJ388" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AK388" s="2" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="AL388" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM388" s="2" t="n">
+        <v>5.8399</v>
+      </c>
+      <c r="AN388" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AO388" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP388" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ388" s="2" t="n">
+        <v>5.8399</v>
+      </c>
+      <c r="AR388" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AS388" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU388" s="2" t="n">
+        <v>5.8399</v>
+      </c>
+      <c r="AV388" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AW388" s="2" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="AX388" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY388" s="2" t="n">
+        <v>5.8399</v>
+      </c>
+      <c r="AZ388" s="2" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="BA388" s="2" t="n">
+        <v>0.00171</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:50:00-04:00</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="n"/>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="L389" s="2" t="n">
+        <v>0.09673204608992036</v>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>0.08235298106872957</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>1.446618941044143</v>
+      </c>
+      <c r="O389" s="2" t="n">
+        <v>0.001156310096765534</v>
+      </c>
+      <c r="P389" s="2" t="n">
+        <v>0.007151388736194945</v>
+      </c>
+      <c r="Q389" s="2" t="n">
+        <v>-0.03596457885005222</v>
+      </c>
+      <c r="R389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S389" s="2" t="n">
+        <v>3.736478451100091</v>
+      </c>
+      <c r="T389" s="2" t="n">
+        <v>-0.01971116033596942</v>
+      </c>
+      <c r="U389" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V389" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC389" s="2" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="AD389" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE389" s="2" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AF389" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AG389" s="2" t="n">
+        <v>1.0741</v>
+      </c>
+      <c r="AH389" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI389" s="2" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AJ389" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AK389" s="2" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="AL389" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM389" s="2" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AN389" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AO389" s="2" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="AP389" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ389" s="2" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AR389" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AS389" s="2" t="n">
+        <v>1.0741</v>
+      </c>
+      <c r="AT389" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU389" s="2" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AV389" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW389" s="2" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="AX389" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY389" s="2" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="AZ389" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA389" s="2" t="n">
+        <v>0.00357</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>CURV</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:33:00-04:00</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="n"/>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>-0.526</v>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>afternoon_hod</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="L390" s="2" t="n">
+        <v>0.1126126111613186</v>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>-0.009009000301245074</v>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>1.395093918691368</v>
+      </c>
+      <c r="O390" s="2" t="n">
+        <v>0.03594335193707887</v>
+      </c>
+      <c r="P390" s="2" t="n">
+        <v>0.02834009222648301</v>
+      </c>
+      <c r="Q390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S390" s="2" t="n">
+        <v>0.9042181622229746</v>
+      </c>
+      <c r="T390" s="2" t="n">
+        <v>-0.02405897124629741</v>
+      </c>
+      <c r="U390" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC390" s="2" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="AD390" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE390" s="2" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AF390" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AG390" s="2" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="AH390" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI390" s="2" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AJ390" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AK390" s="2" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="AL390" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM390" s="2" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="AN390" s="2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AO390" s="2" t="n">
+        <v>-0.07140000000000001</v>
+      </c>
+      <c r="AP390" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ390" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AR390" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AS390" s="2" t="n">
+        <v>-0.07140000000000001</v>
+      </c>
+      <c r="AT390" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU390" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV390" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW390" s="2" t="n">
+        <v>-0.07140000000000001</v>
+      </c>
+      <c r="AX390" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY390" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AZ390" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA390" s="2" t="n">
+        <v>0.00404</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>ACCO</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:42:00-04:00</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="n"/>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>-1.571</v>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="L391" s="2" t="n">
+        <v>0.2087385218682873</v>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>0.1399081738526353</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>2.043249615595623</v>
+      </c>
+      <c r="O391" s="2" t="n">
+        <v>0.002131862041182098</v>
+      </c>
+      <c r="P391" s="2" t="n">
+        <v>0.003813991439352216</v>
+      </c>
+      <c r="Q391" s="2" t="n">
+        <v>-0.03478020514477598</v>
+      </c>
+      <c r="R391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S391" s="2" t="n">
+        <v>1.662049359854745</v>
+      </c>
+      <c r="T391" s="2" t="n">
+        <v>-0.02335703837640257</v>
+      </c>
+      <c r="U391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC391" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD391" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE391" s="2" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="AF391" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AG391" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH391" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI391" s="2" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="AJ391" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AK391" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL391" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM391" s="2" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="AN391" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AO391" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ391" s="2" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="AR391" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AS391" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU391" s="2" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="AV391" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AW391" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX391" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY391" s="2" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="AZ391" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="BA391" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>ACCO</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:54:00-04:00</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="n"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>-1.235</v>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="L392" s="2" t="n">
+        <v>0.2213301940825605</v>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>0.1399081738526353</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>2.060724254844242</v>
+      </c>
+      <c r="O392" s="2" t="n">
+        <v>0.01224768184904912</v>
+      </c>
+      <c r="P392" s="2" t="n">
+        <v>0.01220653738842238</v>
+      </c>
+      <c r="Q392" s="2" t="n">
+        <v>-0.02472531647227838</v>
+      </c>
+      <c r="R392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S392" s="2" t="n">
+        <v>1.672412675776735</v>
+      </c>
+      <c r="T392" s="2" t="n">
+        <v>-0.02407063310568647</v>
+      </c>
+      <c r="U392" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V392" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB392" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC392" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD392" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE392" s="2" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="AF392" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AG392" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH392" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI392" s="2" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="AJ392" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AK392" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL392" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM392" s="2" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="AN392" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AO392" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP392" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ392" s="2" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="AR392" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AS392" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT392" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU392" s="2" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="AV392" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AW392" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX392" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY392" s="2" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="AZ392" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="BA392" s="2" t="n">
+        <v>0.00188</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="n"/>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="n"/>
+      <c r="I393" s="2" t="n"/>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>eod_squeeze</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="L393" s="2" t="n">
+        <v>0.274736805966026</v>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>0.1094736801950555</v>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>1.170790962605523</v>
+      </c>
+      <c r="O393" s="2" t="n">
+        <v>0.04372105616476074</v>
+      </c>
+      <c r="P393" s="2" t="n">
+        <v>0.02229559573342953</v>
+      </c>
+      <c r="Q393" s="2" t="n">
+        <v>-0.005747179535684377</v>
+      </c>
+      <c r="R393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S393" s="2" t="n">
+        <v>1.800884348654704</v>
+      </c>
+      <c r="T393" s="2" t="n">
+        <v>-0.021836316045592</v>
+      </c>
+      <c r="U393" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z393" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA393" s="2" t="n"/>
+      <c r="AB393" s="2" t="n"/>
+      <c r="AC393" s="2" t="n"/>
+      <c r="AD393" s="2" t="n"/>
+      <c r="AE393" s="2" t="n"/>
+      <c r="AF393" s="2" t="n"/>
+      <c r="AG393" s="2" t="n"/>
+      <c r="AH393" s="2" t="n"/>
+      <c r="AI393" s="2" t="n"/>
+      <c r="AJ393" s="2" t="n"/>
+      <c r="AK393" s="2" t="n"/>
+      <c r="AL393" s="2" t="n"/>
+      <c r="AM393" s="2" t="n"/>
+      <c r="AN393" s="2" t="n"/>
+      <c r="AO393" s="2" t="n"/>
+      <c r="AP393" s="2" t="n"/>
+      <c r="AQ393" s="2" t="n"/>
+      <c r="AR393" s="2" t="n"/>
+      <c r="AS393" s="2" t="n"/>
+      <c r="AT393" s="2" t="n"/>
+      <c r="AU393" s="2" t="n"/>
+      <c r="AV393" s="2" t="n"/>
+      <c r="AW393" s="2" t="n"/>
+      <c r="AX393" s="2" t="n"/>
+      <c r="AY393" s="2" t="n"/>
+      <c r="AZ393" s="2" t="n"/>
+      <c r="BA393" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -66841,7 +71507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69259,6 +73925,242 @@
       <c r="J62" s="2" t="inlineStr">
         <is>
           <t>partially open</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>CPRI</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>18.7909</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>ema_bounce</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>CPRI</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>STRZ</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>bull_flag</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>42.849</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>orb5</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>SMP</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>-10.43</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>no fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>vwap_pullback</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>ACCO</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
         </is>
       </c>
     </row>
